--- a/calottino_categoria_gestione.xlsx
+++ b/calottino_categoria_gestione.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/angelo.losito/Desktop/Codex cartella Lavoro/Calottino Avionici/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{185FC19D-A221-CA4B-A46F-2E2B146718F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0E9454D-9084-0B4D-9E7A-1C6497B890DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="19900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1523" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1528" uniqueCount="231">
   <si>
     <t>Dashboard calottino di categoria</t>
   </si>
@@ -731,6 +731,12 @@
   <si>
     <t>Scuotto</t>
   </si>
+  <si>
+    <t>31/07/2026</t>
+  </si>
+  <si>
+    <t>Manzi</t>
+  </si>
 </sst>
 </file>
 
@@ -1140,26 +1146,26 @@
     <xf numFmtId="0" fontId="14" fillId="13" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1435,6 +1441,35 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+      <numFmt numFmtId="164" formatCode="\€\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="\€\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="\€\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <color rgb="FF0070C0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="\€\ #,##0.00"/>
     </dxf>
     <dxf>
       <font>
@@ -1595,35 +1630,6 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="164" formatCode="\€\ #,##0.00"/>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="\€\ #,##0.00"/>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="\€\ #,##0.00"/>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <color rgb="FF0070C0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="\€\ #,##0.00"/>
     </dxf>
     <dxf>
       <font>
@@ -1750,7 +1756,7 @@
                   <c:v>375</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>365</c:v>
+                  <c:v>389</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>540</c:v>
@@ -2072,63 +2078,63 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="QuoteTable" displayName="QuoteTable" ref="A3:I18" dataDxfId="47">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="QuoteTable" displayName="QuoteTable" ref="A3:I18" dataDxfId="59">
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID" dataDxfId="46"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Nome / Cognome" dataDxfId="45"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Quota dovuta" dataDxfId="44"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Quota pagata" dataDxfId="43"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Saldo" dataDxfId="42">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID" dataDxfId="58"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Nome / Cognome" dataDxfId="57"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Quota dovuta" dataDxfId="56"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Quota pagata" dataDxfId="55"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Saldo" dataDxfId="54">
       <calculatedColumnFormula>D4-C4</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Stato" dataDxfId="41">
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Stato" dataDxfId="53">
       <calculatedColumnFormula>IF(D4&gt;=C4,"Pagata",IF(D4&gt;0,"Parziale","Da pagare"))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Data pagamento" dataDxfId="40"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Metodo" dataDxfId="39"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Note" dataDxfId="38"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Data pagamento" dataDxfId="52"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Metodo" dataDxfId="51"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Note" dataDxfId="50"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="AcquistiPatchTable" displayName="AcquistiPatchTable" ref="A3:I203" dataDxfId="37">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="AcquistiPatchTable" displayName="AcquistiPatchTable" ref="A3:I203" dataDxfId="49">
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Data" dataDxfId="36"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Fornitore" dataDxfId="35"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Lotto / Descrizione" dataDxfId="34"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Quantità" dataDxfId="33"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Costo unitario" dataDxfId="32"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Costo totale" dataDxfId="31"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Pagato da" dataDxfId="30"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Stato pagamento" dataDxfId="29"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Note" dataDxfId="28"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Data" dataDxfId="48"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Fornitore" dataDxfId="47"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Lotto / Descrizione" dataDxfId="46"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Quantità" dataDxfId="45"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Costo unitario" dataDxfId="44"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Costo totale" dataDxfId="43"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Pagato da" dataDxfId="42"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Stato pagamento" dataDxfId="41"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Note" dataDxfId="40"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="VenditePatchTable" displayName="VenditePatchTable" ref="A3:K303" dataDxfId="59">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="VenditePatchTable" displayName="VenditePatchTable" ref="A3:K303" dataDxfId="39">
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Data" dataDxfId="58"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Acquirente" dataDxfId="57"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Descrizione" dataDxfId="56"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Quantità" dataDxfId="55"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Prezzo unitario" dataDxfId="54"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Ricavo" dataDxfId="53">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Data" dataDxfId="38"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Acquirente" dataDxfId="37"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Descrizione" dataDxfId="36"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Quantità" dataDxfId="35"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Prezzo unitario" dataDxfId="34"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Ricavo" dataDxfId="33">
       <calculatedColumnFormula>IF(OR(D4="",E4=""),"",D4*E4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="Costo stimato" dataDxfId="52">
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="Costo stimato" dataDxfId="32">
       <calculatedColumnFormula>IF(D4="","",D4*Parametri!$B$6)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0200-000008000000}" name="Utile lordo" dataDxfId="51">
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0200-000008000000}" name="Utile lordo" dataDxfId="31">
       <calculatedColumnFormula>IF(F4="","",F4-G4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0200-000009000000}" name="Incassato?" dataDxfId="50"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0200-00000A000000}" name="Metodo" dataDxfId="49"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0200-00000B000000}" name="Note" dataDxfId="48"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0200-000009000000}" name="Incassato?" dataDxfId="30"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0200-00000A000000}" name="Metodo" dataDxfId="29"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0200-00000B000000}" name="Note" dataDxfId="28"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2345,7 +2351,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="49.75" customHeight="1">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="43" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="39"/>
@@ -2361,7 +2367,7 @@
       <c r="L1" s="39"/>
     </row>
     <row r="2" spans="1:12" ht="26.75" customHeight="1">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="44" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="39"/>
@@ -2378,49 +2384,49 @@
     </row>
     <row r="3" spans="1:12" ht="42.75" customHeight="1"/>
     <row r="4" spans="1:12" ht="26.75" customHeight="1">
-      <c r="A4" s="41" t="s">
+      <c r="A4" s="40" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="39"/>
       <c r="C4" s="39"/>
-      <c r="D4" s="41" t="s">
+      <c r="D4" s="40" t="s">
         <v>3</v>
       </c>
       <c r="E4" s="39"/>
       <c r="F4" s="39"/>
-      <c r="G4" s="41" t="s">
+      <c r="G4" s="40" t="s">
         <v>4</v>
       </c>
       <c r="H4" s="39"/>
       <c r="I4" s="39"/>
-      <c r="J4" s="41" t="s">
+      <c r="J4" s="40" t="s">
         <v>5</v>
       </c>
       <c r="K4" s="39"/>
       <c r="L4" s="39"/>
     </row>
     <row r="5" spans="1:12" ht="34" customHeight="1">
-      <c r="A5" s="42">
+      <c r="A5" s="41">
         <f>Magazzino_Cassa!B16</f>
-        <v>120</v>
+        <v>144</v>
       </c>
       <c r="B5" s="39"/>
       <c r="C5" s="39"/>
-      <c r="D5" s="42">
+      <c r="D5" s="41">
         <f>Magazzino_Cassa!B6</f>
         <v>375</v>
       </c>
       <c r="E5" s="39"/>
       <c r="F5" s="39"/>
-      <c r="G5" s="43">
+      <c r="G5" s="45">
         <f>Magazzino_Cassa!B14</f>
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="H5" s="39"/>
       <c r="I5" s="39"/>
-      <c r="J5" s="42">
+      <c r="J5" s="41">
         <f>Magazzino_Cassa!B12</f>
-        <v>365</v>
+        <v>389</v>
       </c>
       <c r="K5" s="39"/>
       <c r="L5" s="39"/>
@@ -2440,47 +2446,47 @@
       <c r="L6" s="39"/>
     </row>
     <row r="8" spans="1:12" ht="26.75" customHeight="1">
-      <c r="A8" s="41" t="s">
+      <c r="A8" s="40" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="39"/>
       <c r="C8" s="39"/>
-      <c r="D8" s="41" t="s">
+      <c r="D8" s="40" t="s">
         <v>7</v>
       </c>
       <c r="E8" s="39"/>
       <c r="F8" s="39"/>
-      <c r="G8" s="41" t="s">
+      <c r="G8" s="40" t="s">
         <v>8</v>
       </c>
       <c r="H8" s="39"/>
       <c r="I8" s="39"/>
-      <c r="J8" s="41" t="s">
+      <c r="J8" s="40" t="s">
         <v>9</v>
       </c>
       <c r="K8" s="39"/>
       <c r="L8" s="39"/>
     </row>
     <row r="9" spans="1:12" ht="34" customHeight="1">
-      <c r="A9" s="42">
+      <c r="A9" s="41">
         <f>Magazzino_Cassa!B15</f>
         <v>80</v>
       </c>
       <c r="B9" s="39"/>
       <c r="C9" s="39"/>
-      <c r="D9" s="42">
+      <c r="D9" s="41">
         <f>Magazzino_Cassa!B13</f>
-        <v>294.80000000000007</v>
+        <v>308.00000000000011</v>
       </c>
       <c r="E9" s="39"/>
       <c r="F9" s="39"/>
-      <c r="G9" s="45" t="str">
+      <c r="G9" s="42" t="str">
         <f>Magazzino_Cassa!B8&amp;"/"&amp;Parametri!B4</f>
         <v>15/15</v>
       </c>
       <c r="H9" s="39"/>
       <c r="I9" s="39"/>
-      <c r="J9" s="42">
+      <c r="J9" s="41">
         <f>Parametri!B9</f>
         <v>12.3</v>
       </c>
@@ -2502,7 +2508,7 @@
       <c r="L10" s="39"/>
     </row>
     <row r="13" spans="1:12" ht="26.75" customHeight="1">
-      <c r="A13" s="44" t="s">
+      <c r="A13" s="38" t="s">
         <v>10</v>
       </c>
       <c r="B13" s="39"/>
@@ -2510,7 +2516,7 @@
       <c r="D13" s="39"/>
       <c r="E13" s="39"/>
       <c r="F13" s="39"/>
-      <c r="G13" s="44" t="s">
+      <c r="G13" s="38" t="s">
         <v>11</v>
       </c>
       <c r="H13" s="39"/>
@@ -2579,7 +2585,7 @@
       </c>
       <c r="B16" s="4">
         <f>Magazzino_Cassa!B12</f>
-        <v>365</v>
+        <v>389</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>18</v>
@@ -2592,7 +2598,7 @@
       </c>
       <c r="H16" s="5">
         <f>Magazzino_Cassa!B11</f>
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>21</v>
@@ -2620,7 +2626,7 @@
       </c>
       <c r="H17" s="5">
         <f>Magazzino_Cassa!B14</f>
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>21</v>
@@ -2663,7 +2669,7 @@
       </c>
       <c r="B19" s="7">
         <f>Magazzino_Cassa!B16</f>
-        <v>120</v>
+        <v>144</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>34</v>
@@ -2719,7 +2725,7 @@
       </c>
       <c r="B21" s="4">
         <f>Magazzino_Cassa!B18</f>
-        <v>120</v>
+        <v>144</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>18</v>
@@ -2742,7 +2748,7 @@
       </c>
     </row>
     <row r="23" spans="1:12" ht="26.75" customHeight="1">
-      <c r="A23" s="44" t="s">
+      <c r="A23" s="38" t="s">
         <v>46</v>
       </c>
       <c r="B23" s="39"/>
@@ -2783,6 +2789,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A4:C6"/>
+    <mergeCell ref="D4:F6"/>
+    <mergeCell ref="G4:I6"/>
+    <mergeCell ref="J4:L6"/>
     <mergeCell ref="A23:L23"/>
     <mergeCell ref="A8:C10"/>
     <mergeCell ref="D8:F10"/>
@@ -2790,12 +2802,6 @@
     <mergeCell ref="J8:L10"/>
     <mergeCell ref="A13:F13"/>
     <mergeCell ref="G13:L13"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A4:C6"/>
-    <mergeCell ref="D4:F6"/>
-    <mergeCell ref="G4:I6"/>
-    <mergeCell ref="J4:L6"/>
   </mergeCells>
   <conditionalFormatting sqref="B19">
     <cfRule type="expression" dxfId="18" priority="1">
@@ -2813,7 +2819,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:J203"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -7739,7 +7745,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:C103"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="27" customWidth="1"/>
@@ -8574,7 +8580,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="49.75" customHeight="1">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="43" t="s">
         <v>53</v>
       </c>
       <c r="B1" s="39"/>
@@ -8703,7 +8709,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="49.75" customHeight="1">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="43" t="s">
         <v>71</v>
       </c>
       <c r="B1" s="39"/>
@@ -8876,7 +8882,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="49.75" customHeight="1">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="43" t="s">
         <v>91</v>
       </c>
       <c r="B1" s="39"/>
@@ -9413,7 +9419,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="49.75" customHeight="1">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="43" t="s">
         <v>124</v>
       </c>
       <c r="B1" s="39"/>
@@ -13309,7 +13315,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="49.75" customHeight="1">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="43" t="s">
         <v>138</v>
       </c>
       <c r="B1" s="39"/>
@@ -14292,24 +14298,31 @@
       </c>
     </row>
     <row r="31" spans="1:12">
-      <c r="A31" s="14"/>
-      <c r="B31" s="3"/>
+      <c r="A31" s="14" t="s">
+        <v>229</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>121</v>
+      </c>
       <c r="C31" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="D31" s="5"/>
-      <c r="E31" s="13"/>
-      <c r="F31" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="G31" s="4" t="str">
+      <c r="D31" s="5">
+        <v>2</v>
+      </c>
+      <c r="E31" s="13">
+        <v>12</v>
+      </c>
+      <c r="F31" s="4">
+        <v>0</v>
+      </c>
+      <c r="G31" s="4">
         <f>IF(D31="","",D31*Parametri!$B$6)</f>
-        <v/>
-      </c>
-      <c r="H31" s="4" t="str">
+        <v>5.4</v>
+      </c>
+      <c r="H31" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>-5.4</v>
       </c>
       <c r="I31" s="3" t="s">
         <v>147</v>
@@ -14318,29 +14331,39 @@
       <c r="K31" s="3"/>
     </row>
     <row r="32" spans="1:12">
-      <c r="A32" s="14"/>
-      <c r="B32" s="3"/>
+      <c r="A32" s="14" t="s">
+        <v>229</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>230</v>
+      </c>
       <c r="C32" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="D32" s="5"/>
-      <c r="E32" s="13"/>
-      <c r="F32" s="4" t="str">
+      <c r="D32" s="5">
+        <v>2</v>
+      </c>
+      <c r="E32" s="13">
+        <v>12</v>
+      </c>
+      <c r="F32" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="G32" s="4" t="str">
+        <v>24</v>
+      </c>
+      <c r="G32" s="4">
         <f>IF(D32="","",D32*Parametri!$B$6)</f>
-        <v/>
-      </c>
-      <c r="H32" s="4" t="str">
+        <v>5.4</v>
+      </c>
+      <c r="H32" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>18.600000000000001</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="J32" s="3"/>
+      <c r="J32" s="3" t="s">
+        <v>105</v>
+      </c>
       <c r="K32" s="3"/>
     </row>
     <row r="33" spans="1:11">
@@ -21438,7 +21461,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="49.75" customHeight="1">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="43" t="s">
         <v>164</v>
       </c>
       <c r="B1" s="39"/>
@@ -23923,7 +23946,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="49.75" customHeight="1">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="43" t="s">
         <v>170</v>
       </c>
       <c r="B1" s="39"/>
@@ -23933,7 +23956,7 @@
       <c r="F1" s="39"/>
     </row>
     <row r="3" spans="1:11" ht="42.75" customHeight="1">
-      <c r="A3" s="44" t="s">
+      <c r="A3" s="38" t="s">
         <v>171</v>
       </c>
       <c r="B3" s="39"/>
@@ -23941,7 +23964,7 @@
       <c r="D3" s="39"/>
       <c r="E3" s="39"/>
       <c r="F3" s="39"/>
-      <c r="H3" s="44" t="s">
+      <c r="H3" s="38" t="s">
         <v>172</v>
       </c>
       <c r="I3" s="39"/>
@@ -24143,7 +24166,7 @@
       </c>
       <c r="B11" s="5">
         <f>SUM(Vendite_Patch!D4:D303)</f>
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>21</v>
@@ -24167,7 +24190,7 @@
       </c>
       <c r="B12" s="4">
         <f>SUMIFS(Vendite_Patch!F4:F303,Vendite_Patch!I4:I303,"Sì")</f>
-        <v>365</v>
+        <v>389</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>36</v>
@@ -24182,7 +24205,7 @@
       </c>
       <c r="B13" s="4">
         <f>SUMIFS(Vendite_Patch!H4:H303,Vendite_Patch!I4:I303,"Sì")</f>
-        <v>294.80000000000007</v>
+        <v>308.00000000000011</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>36</v>
@@ -24197,7 +24220,7 @@
       </c>
       <c r="B14" s="3">
         <f>B9-B11</f>
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>21</v>
@@ -24227,7 +24250,7 @@
       </c>
       <c r="B16" s="4">
         <f>B6+B12+SUM(Persone_Quote!J4:J18)-B10-B15</f>
-        <v>120</v>
+        <v>144</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>36</v>
@@ -24254,14 +24277,14 @@
       </c>
       <c r="B18" s="4">
         <f>SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$I$4:$I$303,"Sì",Vendite_Patch!$E$4:$E$303,Parametri!$B$8)</f>
-        <v>120</v>
+        <v>144</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="39" customHeight="1">
-      <c r="A19" s="44" t="s">
+      <c r="A19" s="38" t="s">
         <v>186</v>
       </c>
       <c r="B19" s="39"/>
@@ -24405,7 +24428,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="49.75" customHeight="1">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="43" t="s">
         <v>193</v>
       </c>
       <c r="B1" s="39"/>

--- a/calottino_categoria_gestione.xlsx
+++ b/calottino_categoria_gestione.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/angelo.losito/Desktop/Codex cartella Lavoro/Calottino Avionici/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0E9454D-9084-0B4D-9E7A-1C6497B890DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEBF608C-D080-EC48-B518-A7BB560D33B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="19900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="19900" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1528" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1531" uniqueCount="233">
   <si>
     <t>Dashboard calottino di categoria</t>
   </si>
@@ -737,6 +737,12 @@
   <si>
     <t>Manzi</t>
   </si>
+  <si>
+    <t>20/07/2026</t>
+  </si>
+  <si>
+    <t>Fabbiano</t>
+  </si>
 </sst>
 </file>
 
@@ -1146,26 +1152,26 @@
     <xf numFmtId="0" fontId="14" fillId="13" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1756,7 +1762,7 @@
                   <c:v>375</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>389</c:v>
+                  <c:v>401</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>540</c:v>
@@ -2351,7 +2357,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="49.75" customHeight="1">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="38" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="39"/>
@@ -2367,7 +2373,7 @@
       <c r="L1" s="39"/>
     </row>
     <row r="2" spans="1:12" ht="26.75" customHeight="1">
-      <c r="A2" s="44" t="s">
+      <c r="A2" s="40" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="39"/>
@@ -2384,49 +2390,49 @@
     </row>
     <row r="3" spans="1:12" ht="42.75" customHeight="1"/>
     <row r="4" spans="1:12" ht="26.75" customHeight="1">
-      <c r="A4" s="40" t="s">
+      <c r="A4" s="41" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="39"/>
       <c r="C4" s="39"/>
-      <c r="D4" s="40" t="s">
+      <c r="D4" s="41" t="s">
         <v>3</v>
       </c>
       <c r="E4" s="39"/>
       <c r="F4" s="39"/>
-      <c r="G4" s="40" t="s">
+      <c r="G4" s="41" t="s">
         <v>4</v>
       </c>
       <c r="H4" s="39"/>
       <c r="I4" s="39"/>
-      <c r="J4" s="40" t="s">
+      <c r="J4" s="41" t="s">
         <v>5</v>
       </c>
       <c r="K4" s="39"/>
       <c r="L4" s="39"/>
     </row>
     <row r="5" spans="1:12" ht="34" customHeight="1">
-      <c r="A5" s="41">
+      <c r="A5" s="42">
         <f>Magazzino_Cassa!B16</f>
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="B5" s="39"/>
       <c r="C5" s="39"/>
-      <c r="D5" s="41">
+      <c r="D5" s="42">
         <f>Magazzino_Cassa!B6</f>
         <v>375</v>
       </c>
       <c r="E5" s="39"/>
       <c r="F5" s="39"/>
-      <c r="G5" s="45">
+      <c r="G5" s="43">
         <f>Magazzino_Cassa!B14</f>
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H5" s="39"/>
       <c r="I5" s="39"/>
-      <c r="J5" s="41">
+      <c r="J5" s="42">
         <f>Magazzino_Cassa!B12</f>
-        <v>389</v>
+        <v>401</v>
       </c>
       <c r="K5" s="39"/>
       <c r="L5" s="39"/>
@@ -2446,47 +2452,47 @@
       <c r="L6" s="39"/>
     </row>
     <row r="8" spans="1:12" ht="26.75" customHeight="1">
-      <c r="A8" s="40" t="s">
+      <c r="A8" s="41" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="39"/>
       <c r="C8" s="39"/>
-      <c r="D8" s="40" t="s">
+      <c r="D8" s="41" t="s">
         <v>7</v>
       </c>
       <c r="E8" s="39"/>
       <c r="F8" s="39"/>
-      <c r="G8" s="40" t="s">
+      <c r="G8" s="41" t="s">
         <v>8</v>
       </c>
       <c r="H8" s="39"/>
       <c r="I8" s="39"/>
-      <c r="J8" s="40" t="s">
+      <c r="J8" s="41" t="s">
         <v>9</v>
       </c>
       <c r="K8" s="39"/>
       <c r="L8" s="39"/>
     </row>
     <row r="9" spans="1:12" ht="34" customHeight="1">
-      <c r="A9" s="41">
+      <c r="A9" s="42">
         <f>Magazzino_Cassa!B15</f>
         <v>80</v>
       </c>
       <c r="B9" s="39"/>
       <c r="C9" s="39"/>
-      <c r="D9" s="41">
+      <c r="D9" s="42">
         <f>Magazzino_Cassa!B13</f>
-        <v>308.00000000000011</v>
+        <v>317.30000000000013</v>
       </c>
       <c r="E9" s="39"/>
       <c r="F9" s="39"/>
-      <c r="G9" s="42" t="str">
+      <c r="G9" s="45" t="str">
         <f>Magazzino_Cassa!B8&amp;"/"&amp;Parametri!B4</f>
         <v>15/15</v>
       </c>
       <c r="H9" s="39"/>
       <c r="I9" s="39"/>
-      <c r="J9" s="41">
+      <c r="J9" s="42">
         <f>Parametri!B9</f>
         <v>12.3</v>
       </c>
@@ -2508,7 +2514,7 @@
       <c r="L10" s="39"/>
     </row>
     <row r="13" spans="1:12" ht="26.75" customHeight="1">
-      <c r="A13" s="38" t="s">
+      <c r="A13" s="44" t="s">
         <v>10</v>
       </c>
       <c r="B13" s="39"/>
@@ -2516,7 +2522,7 @@
       <c r="D13" s="39"/>
       <c r="E13" s="39"/>
       <c r="F13" s="39"/>
-      <c r="G13" s="38" t="s">
+      <c r="G13" s="44" t="s">
         <v>11</v>
       </c>
       <c r="H13" s="39"/>
@@ -2585,7 +2591,7 @@
       </c>
       <c r="B16" s="4">
         <f>Magazzino_Cassa!B12</f>
-        <v>389</v>
+        <v>401</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>18</v>
@@ -2598,7 +2604,7 @@
       </c>
       <c r="H16" s="5">
         <f>Magazzino_Cassa!B11</f>
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>21</v>
@@ -2626,7 +2632,7 @@
       </c>
       <c r="H17" s="5">
         <f>Magazzino_Cassa!B14</f>
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>21</v>
@@ -2669,7 +2675,7 @@
       </c>
       <c r="B19" s="7">
         <f>Magazzino_Cassa!B16</f>
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>34</v>
@@ -2725,7 +2731,7 @@
       </c>
       <c r="B21" s="4">
         <f>Magazzino_Cassa!B18</f>
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>18</v>
@@ -2748,7 +2754,7 @@
       </c>
     </row>
     <row r="23" spans="1:12" ht="26.75" customHeight="1">
-      <c r="A23" s="38" t="s">
+      <c r="A23" s="44" t="s">
         <v>46</v>
       </c>
       <c r="B23" s="39"/>
@@ -2789,12 +2795,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A4:C6"/>
-    <mergeCell ref="D4:F6"/>
-    <mergeCell ref="G4:I6"/>
-    <mergeCell ref="J4:L6"/>
     <mergeCell ref="A23:L23"/>
     <mergeCell ref="A8:C10"/>
     <mergeCell ref="D8:F10"/>
@@ -2802,6 +2802,12 @@
     <mergeCell ref="J8:L10"/>
     <mergeCell ref="A13:F13"/>
     <mergeCell ref="G13:L13"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A4:C6"/>
+    <mergeCell ref="D4:F6"/>
+    <mergeCell ref="G4:I6"/>
+    <mergeCell ref="J4:L6"/>
   </mergeCells>
   <conditionalFormatting sqref="B19">
     <cfRule type="expression" dxfId="18" priority="1">
@@ -2819,7 +2825,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:J203"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -7745,7 +7751,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:C103"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="27" customWidth="1"/>
@@ -8580,7 +8586,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="49.75" customHeight="1">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="38" t="s">
         <v>53</v>
       </c>
       <c r="B1" s="39"/>
@@ -8709,7 +8715,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="49.75" customHeight="1">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="38" t="s">
         <v>71</v>
       </c>
       <c r="B1" s="39"/>
@@ -8882,7 +8888,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="49.75" customHeight="1">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="38" t="s">
         <v>91</v>
       </c>
       <c r="B1" s="39"/>
@@ -9419,7 +9425,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="49.75" customHeight="1">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="38" t="s">
         <v>124</v>
       </c>
       <c r="B1" s="39"/>
@@ -13315,7 +13321,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="49.75" customHeight="1">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="38" t="s">
         <v>138</v>
       </c>
       <c r="B1" s="39"/>
@@ -14367,29 +14373,39 @@
       <c r="K32" s="3"/>
     </row>
     <row r="33" spans="1:11">
-      <c r="A33" s="14"/>
-      <c r="B33" s="3"/>
+      <c r="A33" s="14" t="s">
+        <v>231</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>232</v>
+      </c>
       <c r="C33" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="D33" s="5"/>
-      <c r="E33" s="13"/>
-      <c r="F33" s="4" t="str">
+      <c r="D33" s="5">
+        <v>1</v>
+      </c>
+      <c r="E33" s="13">
+        <v>12</v>
+      </c>
+      <c r="F33" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="G33" s="4" t="str">
+        <v>12</v>
+      </c>
+      <c r="G33" s="4">
         <f>IF(D33="","",D33*Parametri!$B$6)</f>
-        <v/>
-      </c>
-      <c r="H33" s="4" t="str">
+        <v>2.7</v>
+      </c>
+      <c r="H33" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>9.3000000000000007</v>
       </c>
       <c r="I33" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="J33" s="3"/>
+      <c r="J33" s="3" t="s">
+        <v>105</v>
+      </c>
       <c r="K33" s="3"/>
     </row>
     <row r="34" spans="1:11">
@@ -21461,7 +21477,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="49.75" customHeight="1">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="38" t="s">
         <v>164</v>
       </c>
       <c r="B1" s="39"/>
@@ -23946,7 +23962,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="49.75" customHeight="1">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="38" t="s">
         <v>170</v>
       </c>
       <c r="B1" s="39"/>
@@ -23956,7 +23972,7 @@
       <c r="F1" s="39"/>
     </row>
     <row r="3" spans="1:11" ht="42.75" customHeight="1">
-      <c r="A3" s="38" t="s">
+      <c r="A3" s="44" t="s">
         <v>171</v>
       </c>
       <c r="B3" s="39"/>
@@ -23964,7 +23980,7 @@
       <c r="D3" s="39"/>
       <c r="E3" s="39"/>
       <c r="F3" s="39"/>
-      <c r="H3" s="38" t="s">
+      <c r="H3" s="44" t="s">
         <v>172</v>
       </c>
       <c r="I3" s="39"/>
@@ -24166,7 +24182,7 @@
       </c>
       <c r="B11" s="5">
         <f>SUM(Vendite_Patch!D4:D303)</f>
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>21</v>
@@ -24190,7 +24206,7 @@
       </c>
       <c r="B12" s="4">
         <f>SUMIFS(Vendite_Patch!F4:F303,Vendite_Patch!I4:I303,"Sì")</f>
-        <v>389</v>
+        <v>401</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>36</v>
@@ -24205,7 +24221,7 @@
       </c>
       <c r="B13" s="4">
         <f>SUMIFS(Vendite_Patch!H4:H303,Vendite_Patch!I4:I303,"Sì")</f>
-        <v>308.00000000000011</v>
+        <v>317.30000000000013</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>36</v>
@@ -24220,7 +24236,7 @@
       </c>
       <c r="B14" s="3">
         <f>B9-B11</f>
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>21</v>
@@ -24250,7 +24266,7 @@
       </c>
       <c r="B16" s="4">
         <f>B6+B12+SUM(Persone_Quote!J4:J18)-B10-B15</f>
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>36</v>
@@ -24277,14 +24293,14 @@
       </c>
       <c r="B18" s="4">
         <f>SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$I$4:$I$303,"Sì",Vendite_Patch!$E$4:$E$303,Parametri!$B$8)</f>
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="39" customHeight="1">
-      <c r="A19" s="38" t="s">
+      <c r="A19" s="44" t="s">
         <v>186</v>
       </c>
       <c r="B19" s="39"/>
@@ -24428,7 +24444,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="49.75" customHeight="1">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="38" t="s">
         <v>193</v>
       </c>
       <c r="B1" s="39"/>

--- a/calottino_categoria_gestione.xlsx
+++ b/calottino_categoria_gestione.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/angelo.losito/Desktop/Codex cartella Lavoro/Calottino Avionici/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEBF608C-D080-EC48-B518-A7BB560D33B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAE0F2FC-8794-E841-8A11-539440F0D234}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="19900" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="19900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1531" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1535" uniqueCount="235">
   <si>
     <t>Dashboard calottino di categoria</t>
   </si>
@@ -743,6 +743,12 @@
   <si>
     <t>Fabbiano</t>
   </si>
+  <si>
+    <t>21/09/2026</t>
+  </si>
+  <si>
+    <t>paypal</t>
+  </si>
 </sst>
 </file>
 
@@ -1156,8 +1162,8 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1165,13 +1171,13 @@
     <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1447,35 +1453,6 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="164" formatCode="\€\ #,##0.00"/>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="\€\ #,##0.00"/>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="\€\ #,##0.00"/>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <color rgb="FF0070C0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="\€\ #,##0.00"/>
     </dxf>
     <dxf>
       <font>
@@ -1636,6 +1613,35 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+      <numFmt numFmtId="164" formatCode="\€\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="\€\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="\€\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <color rgb="FF0070C0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="\€\ #,##0.00"/>
     </dxf>
     <dxf>
       <font>
@@ -1762,7 +1768,7 @@
                   <c:v>375</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>401</c:v>
+                  <c:v>551</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>540</c:v>
@@ -2084,63 +2090,63 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="QuoteTable" displayName="QuoteTable" ref="A3:I18" dataDxfId="59">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="QuoteTable" displayName="QuoteTable" ref="A3:I18" dataDxfId="47">
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID" dataDxfId="58"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Nome / Cognome" dataDxfId="57"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Quota dovuta" dataDxfId="56"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Quota pagata" dataDxfId="55"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Saldo" dataDxfId="54">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID" dataDxfId="46"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Nome / Cognome" dataDxfId="45"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Quota dovuta" dataDxfId="44"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Quota pagata" dataDxfId="43"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Saldo" dataDxfId="42">
       <calculatedColumnFormula>D4-C4</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Stato" dataDxfId="53">
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Stato" dataDxfId="41">
       <calculatedColumnFormula>IF(D4&gt;=C4,"Pagata",IF(D4&gt;0,"Parziale","Da pagare"))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Data pagamento" dataDxfId="52"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Metodo" dataDxfId="51"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Note" dataDxfId="50"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Data pagamento" dataDxfId="40"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Metodo" dataDxfId="39"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Note" dataDxfId="38"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="AcquistiPatchTable" displayName="AcquistiPatchTable" ref="A3:I203" dataDxfId="49">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="AcquistiPatchTable" displayName="AcquistiPatchTable" ref="A3:I203" dataDxfId="37">
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Data" dataDxfId="48"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Fornitore" dataDxfId="47"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Lotto / Descrizione" dataDxfId="46"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Quantità" dataDxfId="45"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Costo unitario" dataDxfId="44"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Costo totale" dataDxfId="43"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Pagato da" dataDxfId="42"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Stato pagamento" dataDxfId="41"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Note" dataDxfId="40"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Data" dataDxfId="36"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Fornitore" dataDxfId="35"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Lotto / Descrizione" dataDxfId="34"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Quantità" dataDxfId="33"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Costo unitario" dataDxfId="32"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Costo totale" dataDxfId="31"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Pagato da" dataDxfId="30"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Stato pagamento" dataDxfId="29"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Note" dataDxfId="28"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="VenditePatchTable" displayName="VenditePatchTable" ref="A3:K303" dataDxfId="39">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="VenditePatchTable" displayName="VenditePatchTable" ref="A3:K303" dataDxfId="59">
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Data" dataDxfId="38"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Acquirente" dataDxfId="37"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Descrizione" dataDxfId="36"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Quantità" dataDxfId="35"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Prezzo unitario" dataDxfId="34"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Ricavo" dataDxfId="33">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Data" dataDxfId="58"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Acquirente" dataDxfId="57"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Descrizione" dataDxfId="56"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Quantità" dataDxfId="55"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Prezzo unitario" dataDxfId="54"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Ricavo" dataDxfId="53">
       <calculatedColumnFormula>IF(OR(D4="",E4=""),"",D4*E4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="Costo stimato" dataDxfId="32">
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="Costo stimato" dataDxfId="52">
       <calculatedColumnFormula>IF(D4="","",D4*Parametri!$B$6)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0200-000008000000}" name="Utile lordo" dataDxfId="31">
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0200-000008000000}" name="Utile lordo" dataDxfId="51">
       <calculatedColumnFormula>IF(F4="","",F4-G4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0200-000009000000}" name="Incassato?" dataDxfId="30"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0200-00000A000000}" name="Metodo" dataDxfId="29"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0200-00000B000000}" name="Note" dataDxfId="28"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0200-000009000000}" name="Incassato?" dataDxfId="50"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0200-00000A000000}" name="Metodo" dataDxfId="49"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0200-00000B000000}" name="Note" dataDxfId="48"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2373,7 +2379,7 @@
       <c r="L1" s="39"/>
     </row>
     <row r="2" spans="1:12" ht="26.75" customHeight="1">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="44" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="39"/>
@@ -2414,7 +2420,7 @@
     <row r="5" spans="1:12" ht="34" customHeight="1">
       <c r="A5" s="42">
         <f>Magazzino_Cassa!B16</f>
-        <v>156</v>
+        <v>306</v>
       </c>
       <c r="B5" s="39"/>
       <c r="C5" s="39"/>
@@ -2424,15 +2430,15 @@
       </c>
       <c r="E5" s="39"/>
       <c r="F5" s="39"/>
-      <c r="G5" s="43">
+      <c r="G5" s="45">
         <f>Magazzino_Cassa!B14</f>
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="H5" s="39"/>
       <c r="I5" s="39"/>
       <c r="J5" s="42">
         <f>Magazzino_Cassa!B12</f>
-        <v>401</v>
+        <v>551</v>
       </c>
       <c r="K5" s="39"/>
       <c r="L5" s="39"/>
@@ -2482,11 +2488,11 @@
       <c r="C9" s="39"/>
       <c r="D9" s="42">
         <f>Magazzino_Cassa!B13</f>
-        <v>317.30000000000013</v>
+        <v>440.30000000000013</v>
       </c>
       <c r="E9" s="39"/>
       <c r="F9" s="39"/>
-      <c r="G9" s="45" t="str">
+      <c r="G9" s="43" t="str">
         <f>Magazzino_Cassa!B8&amp;"/"&amp;Parametri!B4</f>
         <v>15/15</v>
       </c>
@@ -2514,7 +2520,7 @@
       <c r="L10" s="39"/>
     </row>
     <row r="13" spans="1:12" ht="26.75" customHeight="1">
-      <c r="A13" s="44" t="s">
+      <c r="A13" s="40" t="s">
         <v>10</v>
       </c>
       <c r="B13" s="39"/>
@@ -2522,7 +2528,7 @@
       <c r="D13" s="39"/>
       <c r="E13" s="39"/>
       <c r="F13" s="39"/>
-      <c r="G13" s="44" t="s">
+      <c r="G13" s="40" t="s">
         <v>11</v>
       </c>
       <c r="H13" s="39"/>
@@ -2591,7 +2597,7 @@
       </c>
       <c r="B16" s="4">
         <f>Magazzino_Cassa!B12</f>
-        <v>401</v>
+        <v>551</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>18</v>
@@ -2604,7 +2610,7 @@
       </c>
       <c r="H16" s="5">
         <f>Magazzino_Cassa!B11</f>
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>21</v>
@@ -2632,7 +2638,7 @@
       </c>
       <c r="H17" s="5">
         <f>Magazzino_Cassa!B14</f>
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>21</v>
@@ -2675,7 +2681,7 @@
       </c>
       <c r="B19" s="7">
         <f>Magazzino_Cassa!B16</f>
-        <v>156</v>
+        <v>306</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>34</v>
@@ -2703,7 +2709,7 @@
       </c>
       <c r="B20" s="4">
         <f>Magazzino_Cassa!B17</f>
-        <v>245</v>
+        <v>395</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>18</v>
@@ -2754,7 +2760,7 @@
       </c>
     </row>
     <row r="23" spans="1:12" ht="26.75" customHeight="1">
-      <c r="A23" s="44" t="s">
+      <c r="A23" s="40" t="s">
         <v>46</v>
       </c>
       <c r="B23" s="39"/>
@@ -2795,6 +2801,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A4:C6"/>
+    <mergeCell ref="D4:F6"/>
+    <mergeCell ref="G4:I6"/>
+    <mergeCell ref="J4:L6"/>
     <mergeCell ref="A23:L23"/>
     <mergeCell ref="A8:C10"/>
     <mergeCell ref="D8:F10"/>
@@ -2802,12 +2814,6 @@
     <mergeCell ref="J8:L10"/>
     <mergeCell ref="A13:F13"/>
     <mergeCell ref="G13:L13"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A4:C6"/>
-    <mergeCell ref="D4:F6"/>
-    <mergeCell ref="G4:I6"/>
-    <mergeCell ref="J4:L6"/>
   </mergeCells>
   <conditionalFormatting sqref="B19">
     <cfRule type="expression" dxfId="18" priority="1">
@@ -2942,18 +2948,20 @@
       </c>
       <c r="D5" s="25">
         <f>IF(B5="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B5))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E5" s="25"/>
       <c r="F5" s="25">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G5" s="28">
         <f>IF(B5="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B5,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
-        <v>0</v>
-      </c>
-      <c r="H5" s="28"/>
+        <v>150</v>
+      </c>
+      <c r="H5" s="28">
+        <v>150</v>
+      </c>
       <c r="I5" s="28">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -14372,7 +14380,7 @@
       </c>
       <c r="K32" s="3"/>
     </row>
-    <row r="33" spans="1:11">
+    <row r="33" spans="1:12">
       <c r="A33" s="14" t="s">
         <v>231</v>
       </c>
@@ -14408,33 +14416,46 @@
       </c>
       <c r="K33" s="3"/>
     </row>
-    <row r="34" spans="1:11">
-      <c r="A34" s="14"/>
-      <c r="B34" s="3"/>
+    <row r="34" spans="1:12">
+      <c r="A34" s="14" t="s">
+        <v>233</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>133</v>
+      </c>
       <c r="C34" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="D34" s="5"/>
-      <c r="E34" s="13"/>
-      <c r="F34" s="4" t="str">
+      <c r="D34" s="5">
+        <v>10</v>
+      </c>
+      <c r="E34" s="13">
+        <v>15</v>
+      </c>
+      <c r="F34" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="G34" s="4" t="str">
+        <v>150</v>
+      </c>
+      <c r="G34" s="4">
         <f>IF(D34="","",D34*Parametri!$B$6)</f>
-        <v/>
-      </c>
-      <c r="H34" s="4" t="str">
+        <v>27</v>
+      </c>
+      <c r="H34" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>123</v>
       </c>
       <c r="I34" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="J34" s="3"/>
+      <c r="J34" s="3" t="s">
+        <v>234</v>
+      </c>
       <c r="K34" s="3"/>
-    </row>
-    <row r="35" spans="1:11">
+      <c r="L34" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12">
       <c r="A35" s="14"/>
       <c r="B35" s="3"/>
       <c r="C35" s="3" t="s">
@@ -14460,7 +14481,7 @@
       <c r="J35" s="3"/>
       <c r="K35" s="3"/>
     </row>
-    <row r="36" spans="1:11">
+    <row r="36" spans="1:12">
       <c r="A36" s="14"/>
       <c r="B36" s="3"/>
       <c r="C36" s="3" t="s">
@@ -14486,7 +14507,7 @@
       <c r="J36" s="3"/>
       <c r="K36" s="3"/>
     </row>
-    <row r="37" spans="1:11">
+    <row r="37" spans="1:12">
       <c r="A37" s="14"/>
       <c r="B37" s="3"/>
       <c r="C37" s="3" t="s">
@@ -14512,7 +14533,7 @@
       <c r="J37" s="3"/>
       <c r="K37" s="3"/>
     </row>
-    <row r="38" spans="1:11">
+    <row r="38" spans="1:12">
       <c r="A38" s="14"/>
       <c r="B38" s="3"/>
       <c r="C38" s="3" t="s">
@@ -14538,7 +14559,7 @@
       <c r="J38" s="3"/>
       <c r="K38" s="3"/>
     </row>
-    <row r="39" spans="1:11">
+    <row r="39" spans="1:12">
       <c r="A39" s="14"/>
       <c r="B39" s="3"/>
       <c r="C39" s="3" t="s">
@@ -14564,7 +14585,7 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
     </row>
-    <row r="40" spans="1:11">
+    <row r="40" spans="1:12">
       <c r="A40" s="14"/>
       <c r="B40" s="3"/>
       <c r="C40" s="3" t="s">
@@ -14590,7 +14611,7 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
     </row>
-    <row r="41" spans="1:11">
+    <row r="41" spans="1:12">
       <c r="A41" s="14"/>
       <c r="B41" s="3"/>
       <c r="C41" s="3" t="s">
@@ -14616,7 +14637,7 @@
       <c r="J41" s="3"/>
       <c r="K41" s="3"/>
     </row>
-    <row r="42" spans="1:11">
+    <row r="42" spans="1:12">
       <c r="A42" s="14"/>
       <c r="B42" s="3"/>
       <c r="C42" s="3" t="s">
@@ -14642,7 +14663,7 @@
       <c r="J42" s="3"/>
       <c r="K42" s="3"/>
     </row>
-    <row r="43" spans="1:11">
+    <row r="43" spans="1:12">
       <c r="A43" s="14"/>
       <c r="B43" s="3"/>
       <c r="C43" s="3" t="s">
@@ -14668,7 +14689,7 @@
       <c r="J43" s="3"/>
       <c r="K43" s="3"/>
     </row>
-    <row r="44" spans="1:11">
+    <row r="44" spans="1:12">
       <c r="A44" s="14"/>
       <c r="B44" s="3"/>
       <c r="C44" s="3" t="s">
@@ -14694,7 +14715,7 @@
       <c r="J44" s="3"/>
       <c r="K44" s="3"/>
     </row>
-    <row r="45" spans="1:11">
+    <row r="45" spans="1:12">
       <c r="A45" s="14"/>
       <c r="B45" s="3"/>
       <c r="C45" s="3" t="s">
@@ -14720,7 +14741,7 @@
       <c r="J45" s="3"/>
       <c r="K45" s="3"/>
     </row>
-    <row r="46" spans="1:11">
+    <row r="46" spans="1:12">
       <c r="A46" s="14"/>
       <c r="B46" s="3"/>
       <c r="C46" s="3" t="s">
@@ -14746,7 +14767,7 @@
       <c r="J46" s="3"/>
       <c r="K46" s="3"/>
     </row>
-    <row r="47" spans="1:11">
+    <row r="47" spans="1:12">
       <c r="A47" s="14"/>
       <c r="B47" s="3"/>
       <c r="C47" s="3" t="s">
@@ -14772,7 +14793,7 @@
       <c r="J47" s="3"/>
       <c r="K47" s="3"/>
     </row>
-    <row r="48" spans="1:11">
+    <row r="48" spans="1:12">
       <c r="A48" s="14"/>
       <c r="B48" s="3"/>
       <c r="C48" s="3" t="s">
@@ -23972,7 +23993,7 @@
       <c r="F1" s="39"/>
     </row>
     <row r="3" spans="1:11" ht="42.75" customHeight="1">
-      <c r="A3" s="44" t="s">
+      <c r="A3" s="40" t="s">
         <v>171</v>
       </c>
       <c r="B3" s="39"/>
@@ -23980,7 +24001,7 @@
       <c r="D3" s="39"/>
       <c r="E3" s="39"/>
       <c r="F3" s="39"/>
-      <c r="H3" s="44" t="s">
+      <c r="H3" s="40" t="s">
         <v>172</v>
       </c>
       <c r="I3" s="39"/>
@@ -24182,7 +24203,7 @@
       </c>
       <c r="B11" s="5">
         <f>SUM(Vendite_Patch!D4:D303)</f>
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>21</v>
@@ -24206,7 +24227,7 @@
       </c>
       <c r="B12" s="4">
         <f>SUMIFS(Vendite_Patch!F4:F303,Vendite_Patch!I4:I303,"Sì")</f>
-        <v>401</v>
+        <v>551</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>36</v>
@@ -24221,7 +24242,7 @@
       </c>
       <c r="B13" s="4">
         <f>SUMIFS(Vendite_Patch!H4:H303,Vendite_Patch!I4:I303,"Sì")</f>
-        <v>317.30000000000013</v>
+        <v>440.30000000000013</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>36</v>
@@ -24236,7 +24257,7 @@
       </c>
       <c r="B14" s="3">
         <f>B9-B11</f>
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>21</v>
@@ -24266,7 +24287,7 @@
       </c>
       <c r="B16" s="4">
         <f>B6+B12+SUM(Persone_Quote!J4:J18)-B10-B15</f>
-        <v>156</v>
+        <v>306</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>36</v>
@@ -24281,7 +24302,7 @@
       </c>
       <c r="B17" s="4">
         <f>SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$I$4:$I$303,"Sì",Vendite_Patch!$E$4:$E$303,Parametri!$B$7)</f>
-        <v>245</v>
+        <v>395</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>36</v>
@@ -24300,7 +24321,7 @@
       </c>
     </row>
     <row r="19" spans="1:6" ht="39" customHeight="1">
-      <c r="A19" s="44" t="s">
+      <c r="A19" s="40" t="s">
         <v>186</v>
       </c>
       <c r="B19" s="39"/>

--- a/calottino_categoria_gestione.xlsx
+++ b/calottino_categoria_gestione.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11020"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/angelo.losito/Desktop/Codex cartella Lavoro/Calottino Avionici/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAE0F2FC-8794-E841-8A11-539440F0D234}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9811235-3AF7-1246-A4AB-564E2A46461C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="19900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="19900" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1535" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1541" uniqueCount="236">
   <si>
     <t>Dashboard calottino di categoria</t>
   </si>
@@ -747,7 +747,10 @@
     <t>21/09/2026</t>
   </si>
   <si>
-    <t>paypal</t>
+    <t>16/10/2026</t>
+  </si>
+  <si>
+    <t>22/10/2026</t>
   </si>
 </sst>
 </file>
@@ -760,7 +763,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -858,6 +861,13 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF111827"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="14">
@@ -1051,7 +1061,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1092,16 +1102,10 @@
     <xf numFmtId="0" fontId="13" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1140,30 +1144,12 @@
     <xf numFmtId="0" fontId="15" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1171,13 +1157,13 @@
     <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1192,11 +1178,103 @@
     <xf numFmtId="0" fontId="12" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="60">
+  <dxfs count="64">
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF111827"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF111827"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF111827"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF111827"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1453,6 +1531,35 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+      <numFmt numFmtId="164" formatCode="\€\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="\€\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="\€\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <font>
+        <u val="none"/>
+        <color rgb="FF0070C0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="\€\ #,##0.00"/>
     </dxf>
     <dxf>
       <font>
@@ -1613,35 +1720,6 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="164" formatCode="\€\ #,##0.00"/>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="\€\ #,##0.00"/>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="\€\ #,##0.00"/>
-    </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <color rgb="FF0070C0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="\€\ #,##0.00"/>
     </dxf>
     <dxf>
       <font>
@@ -1768,7 +1846,7 @@
                   <c:v>375</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>551</c:v>
+                  <c:v>663</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>540</c:v>
@@ -1894,6 +1972,90 @@
             <c:v>Spese</c:v>
           </c:tx>
           <c:dLbls>
+            <c:dLbl>
+              <c:idx val="1"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="0.28812639233651416"/>
+                  <c:y val="0.1206814944990728"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:showLegendKey val="1"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="1"/>
+              <c:showSerName val="1"/>
+              <c:showPercent val="1"/>
+              <c:showBubbleSize val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000003-A014-2841-A481-060E450482C4}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.25050101533304814"/>
+                  <c:y val="2.0225948798727285E-3"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:showLegendKey val="1"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="1"/>
+              <c:showSerName val="1"/>
+              <c:showPercent val="1"/>
+              <c:showBubbleSize val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000002-A014-2841-A481-060E450482C4}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="3"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.285957529271399"/>
+                  <c:y val="8.2926390074781864E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:showLegendKey val="1"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="1"/>
+              <c:showSerName val="1"/>
+              <c:showPercent val="1"/>
+              <c:showBubbleSize val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000001-A014-2841-A481-060E450482C4}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="5"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="0.25527698104903235"/>
+                  <c:y val="3.4384112957836381E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:showLegendKey val="1"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="1"/>
+              <c:showSerName val="1"/>
+              <c:showPercent val="1"/>
+              <c:showBubbleSize val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000000-A014-2841-A481-060E450482C4}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
             <c:spPr>
               <a:noFill/>
               <a:ln>
@@ -2090,79 +2252,79 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="QuoteTable" displayName="QuoteTable" ref="A3:I18" dataDxfId="47">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="QuoteTable" displayName="QuoteTable" ref="A3:I18" dataDxfId="63">
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID" dataDxfId="46"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Nome / Cognome" dataDxfId="45"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Quota dovuta" dataDxfId="44"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Quota pagata" dataDxfId="43"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Saldo" dataDxfId="42">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID" dataDxfId="62"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Nome / Cognome" dataDxfId="61"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Quota dovuta" dataDxfId="60"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Quota pagata" dataDxfId="59"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Saldo" dataDxfId="58">
       <calculatedColumnFormula>D4-C4</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Stato" dataDxfId="41">
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Stato" dataDxfId="57">
       <calculatedColumnFormula>IF(D4&gt;=C4,"Pagata",IF(D4&gt;0,"Parziale","Da pagare"))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Data pagamento" dataDxfId="40"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Metodo" dataDxfId="39"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Note" dataDxfId="38"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Data pagamento" dataDxfId="56"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Metodo" dataDxfId="55"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Note" dataDxfId="54"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="AcquistiPatchTable" displayName="AcquistiPatchTable" ref="A3:I203" dataDxfId="37">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="AcquistiPatchTable" displayName="AcquistiPatchTable" ref="A3:I203" dataDxfId="53">
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Data" dataDxfId="36"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Fornitore" dataDxfId="35"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Lotto / Descrizione" dataDxfId="34"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Quantità" dataDxfId="33"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Costo unitario" dataDxfId="32"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Costo totale" dataDxfId="31"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Pagato da" dataDxfId="30"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Stato pagamento" dataDxfId="29"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Note" dataDxfId="28"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Data" dataDxfId="52"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Fornitore" dataDxfId="51"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Lotto / Descrizione" dataDxfId="50"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Quantità" dataDxfId="49"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Costo unitario" dataDxfId="48"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Costo totale" dataDxfId="47"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Pagato da" dataDxfId="46"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Stato pagamento" dataDxfId="45"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Note" dataDxfId="44"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="VenditePatchTable" displayName="VenditePatchTable" ref="A3:K303" dataDxfId="59">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="VenditePatchTable" displayName="VenditePatchTable" ref="A3:K303" dataDxfId="43">
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Data" dataDxfId="58"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Acquirente" dataDxfId="57"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Descrizione" dataDxfId="56"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Quantità" dataDxfId="55"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Prezzo unitario" dataDxfId="54"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Ricavo" dataDxfId="53">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Data" dataDxfId="42"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Acquirente" dataDxfId="41"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Descrizione" dataDxfId="40"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Quantità" dataDxfId="39"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Prezzo unitario" dataDxfId="38"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Ricavo" dataDxfId="37">
       <calculatedColumnFormula>IF(OR(D4="",E4=""),"",D4*E4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="Costo stimato" dataDxfId="52">
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="Costo stimato" dataDxfId="36">
       <calculatedColumnFormula>IF(D4="","",D4*Parametri!$B$6)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0200-000008000000}" name="Utile lordo" dataDxfId="51">
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0200-000008000000}" name="Utile lordo" dataDxfId="35">
       <calculatedColumnFormula>IF(F4="","",F4-G4)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0200-000009000000}" name="Incassato?" dataDxfId="50"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0200-00000A000000}" name="Metodo" dataDxfId="49"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0200-00000B000000}" name="Note" dataDxfId="48"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0200-000009000000}" name="Incassato?" dataDxfId="34"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0200-00000A000000}" name="Metodo" dataDxfId="33"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0200-00000B000000}" name="Note" dataDxfId="32"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="SpeseCategoriaTable" displayName="SpeseCategoriaTable" ref="A3:H203" dataDxfId="27">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="SpeseCategoriaTable" displayName="SpeseCategoriaTable" ref="A3:H203" dataDxfId="31">
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="Data" dataDxfId="26"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Categoria" dataDxfId="25"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="Descrizione" dataDxfId="24"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="Importo" dataDxfId="23"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="Pagato da" dataDxfId="22"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="Metodo" dataDxfId="21"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0300-000007000000}" name="Approvata?" dataDxfId="20"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0300-000008000000}" name="Note" dataDxfId="19"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="Data" dataDxfId="30"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Categoria" dataDxfId="29"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="Descrizione" dataDxfId="28"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="Importo" dataDxfId="27"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="Pagato da" dataDxfId="26"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="Metodo" dataDxfId="25"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0300-000007000000}" name="Approvata?" dataDxfId="24"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0300-000008000000}" name="Note" dataDxfId="23"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2187,11 +2349,11 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="TabellaVenditoriAffidatari" displayName="TabellaVenditoriAffidatari" ref="A3:C103" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="TabellaVenditoriAffidatari" displayName="TabellaVenditoriAffidatari" ref="A3:C103" totalsRowShown="0" dataDxfId="0">
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="Tipo"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="Nome / Cognome"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="Note"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="Tipo" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="Nome / Cognome" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="Note" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2363,179 +2525,179 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="49.75" customHeight="1">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
-      <c r="J1" s="39"/>
-      <c r="K1" s="39"/>
-      <c r="L1" s="39"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+      <c r="K1" s="31"/>
+      <c r="L1" s="31"/>
     </row>
     <row r="2" spans="1:12" ht="26.75" customHeight="1">
-      <c r="A2" s="44" t="s">
+      <c r="A2" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
-      <c r="I2" s="39"/>
-      <c r="J2" s="39"/>
-      <c r="K2" s="39"/>
-      <c r="L2" s="39"/>
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="31"/>
+      <c r="K2" s="31"/>
+      <c r="L2" s="31"/>
     </row>
     <row r="3" spans="1:12" ht="42.75" customHeight="1"/>
     <row r="4" spans="1:12" ht="26.75" customHeight="1">
-      <c r="A4" s="41" t="s">
+      <c r="A4" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="39"/>
-      <c r="C4" s="39"/>
-      <c r="D4" s="41" t="s">
+      <c r="B4" s="31"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="39"/>
-      <c r="F4" s="39"/>
-      <c r="G4" s="41" t="s">
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="39"/>
-      <c r="I4" s="39"/>
-      <c r="J4" s="41" t="s">
+      <c r="H4" s="31"/>
+      <c r="I4" s="31"/>
+      <c r="J4" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="K4" s="39"/>
-      <c r="L4" s="39"/>
+      <c r="K4" s="31"/>
+      <c r="L4" s="31"/>
     </row>
     <row r="5" spans="1:12" ht="34" customHeight="1">
-      <c r="A5" s="42">
+      <c r="A5" s="34">
         <f>Magazzino_Cassa!B16</f>
-        <v>306</v>
-      </c>
-      <c r="B5" s="39"/>
-      <c r="C5" s="39"/>
-      <c r="D5" s="42">
+        <v>418</v>
+      </c>
+      <c r="B5" s="31"/>
+      <c r="C5" s="31"/>
+      <c r="D5" s="34">
         <f>Magazzino_Cassa!B6</f>
         <v>375</v>
       </c>
-      <c r="E5" s="39"/>
-      <c r="F5" s="39"/>
-      <c r="G5" s="45">
+      <c r="E5" s="31"/>
+      <c r="F5" s="31"/>
+      <c r="G5" s="35">
         <f>Magazzino_Cassa!B14</f>
-        <v>131</v>
-      </c>
-      <c r="H5" s="39"/>
-      <c r="I5" s="39"/>
-      <c r="J5" s="42">
+        <v>120</v>
+      </c>
+      <c r="H5" s="31"/>
+      <c r="I5" s="31"/>
+      <c r="J5" s="34">
         <f>Magazzino_Cassa!B12</f>
-        <v>551</v>
-      </c>
-      <c r="K5" s="39"/>
-      <c r="L5" s="39"/>
+        <v>663</v>
+      </c>
+      <c r="K5" s="31"/>
+      <c r="L5" s="31"/>
     </row>
     <row r="6" spans="1:12">
-      <c r="A6" s="39"/>
-      <c r="B6" s="39"/>
-      <c r="C6" s="39"/>
-      <c r="D6" s="39"/>
-      <c r="E6" s="39"/>
-      <c r="F6" s="39"/>
-      <c r="G6" s="39"/>
-      <c r="H6" s="39"/>
-      <c r="I6" s="39"/>
-      <c r="J6" s="39"/>
-      <c r="K6" s="39"/>
-      <c r="L6" s="39"/>
+      <c r="A6" s="31"/>
+      <c r="B6" s="31"/>
+      <c r="C6" s="31"/>
+      <c r="D6" s="31"/>
+      <c r="E6" s="31"/>
+      <c r="F6" s="31"/>
+      <c r="G6" s="31"/>
+      <c r="H6" s="31"/>
+      <c r="I6" s="31"/>
+      <c r="J6" s="31"/>
+      <c r="K6" s="31"/>
+      <c r="L6" s="31"/>
     </row>
     <row r="8" spans="1:12" ht="26.75" customHeight="1">
-      <c r="A8" s="41" t="s">
+      <c r="A8" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="39"/>
-      <c r="C8" s="39"/>
-      <c r="D8" s="41" t="s">
+      <c r="B8" s="31"/>
+      <c r="C8" s="31"/>
+      <c r="D8" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="39"/>
-      <c r="F8" s="39"/>
-      <c r="G8" s="41" t="s">
+      <c r="E8" s="31"/>
+      <c r="F8" s="31"/>
+      <c r="G8" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="H8" s="39"/>
-      <c r="I8" s="39"/>
-      <c r="J8" s="41" t="s">
+      <c r="H8" s="31"/>
+      <c r="I8" s="31"/>
+      <c r="J8" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="K8" s="39"/>
-      <c r="L8" s="39"/>
+      <c r="K8" s="31"/>
+      <c r="L8" s="31"/>
     </row>
     <row r="9" spans="1:12" ht="34" customHeight="1">
-      <c r="A9" s="42">
+      <c r="A9" s="34">
         <f>Magazzino_Cassa!B15</f>
         <v>80</v>
       </c>
-      <c r="B9" s="39"/>
-      <c r="C9" s="39"/>
-      <c r="D9" s="42">
+      <c r="B9" s="31"/>
+      <c r="C9" s="31"/>
+      <c r="D9" s="34">
         <f>Magazzino_Cassa!B13</f>
-        <v>440.30000000000013</v>
-      </c>
-      <c r="E9" s="39"/>
-      <c r="F9" s="39"/>
-      <c r="G9" s="43" t="str">
+        <v>522.60000000000014</v>
+      </c>
+      <c r="E9" s="31"/>
+      <c r="F9" s="31"/>
+      <c r="G9" s="37" t="str">
         <f>Magazzino_Cassa!B8&amp;"/"&amp;Parametri!B4</f>
         <v>15/15</v>
       </c>
-      <c r="H9" s="39"/>
-      <c r="I9" s="39"/>
-      <c r="J9" s="42">
+      <c r="H9" s="31"/>
+      <c r="I9" s="31"/>
+      <c r="J9" s="34">
         <f>Parametri!B9</f>
         <v>12.3</v>
       </c>
-      <c r="K9" s="39"/>
-      <c r="L9" s="39"/>
+      <c r="K9" s="31"/>
+      <c r="L9" s="31"/>
     </row>
     <row r="10" spans="1:12">
-      <c r="A10" s="39"/>
-      <c r="B10" s="39"/>
-      <c r="C10" s="39"/>
-      <c r="D10" s="39"/>
-      <c r="E10" s="39"/>
-      <c r="F10" s="39"/>
-      <c r="G10" s="39"/>
-      <c r="H10" s="39"/>
-      <c r="I10" s="39"/>
-      <c r="J10" s="39"/>
-      <c r="K10" s="39"/>
-      <c r="L10" s="39"/>
+      <c r="A10" s="31"/>
+      <c r="B10" s="31"/>
+      <c r="C10" s="31"/>
+      <c r="D10" s="31"/>
+      <c r="E10" s="31"/>
+      <c r="F10" s="31"/>
+      <c r="G10" s="31"/>
+      <c r="H10" s="31"/>
+      <c r="I10" s="31"/>
+      <c r="J10" s="31"/>
+      <c r="K10" s="31"/>
+      <c r="L10" s="31"/>
     </row>
     <row r="13" spans="1:12" ht="26.75" customHeight="1">
-      <c r="A13" s="40" t="s">
+      <c r="A13" s="36" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="39"/>
-      <c r="C13" s="39"/>
-      <c r="D13" s="39"/>
-      <c r="E13" s="39"/>
-      <c r="F13" s="39"/>
-      <c r="G13" s="40" t="s">
+      <c r="B13" s="31"/>
+      <c r="C13" s="31"/>
+      <c r="D13" s="31"/>
+      <c r="E13" s="31"/>
+      <c r="F13" s="31"/>
+      <c r="G13" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="H13" s="39"/>
-      <c r="I13" s="39"/>
-      <c r="J13" s="39"/>
-      <c r="K13" s="39"/>
-      <c r="L13" s="39"/>
+      <c r="H13" s="31"/>
+      <c r="I13" s="31"/>
+      <c r="J13" s="31"/>
+      <c r="K13" s="31"/>
+      <c r="L13" s="31"/>
     </row>
     <row r="14" spans="1:12" ht="26.75" customHeight="1">
       <c r="A14" s="2" t="s">
@@ -2597,7 +2759,7 @@
       </c>
       <c r="B16" s="4">
         <f>Magazzino_Cassa!B12</f>
-        <v>551</v>
+        <v>663</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>18</v>
@@ -2610,7 +2772,7 @@
       </c>
       <c r="H16" s="5">
         <f>Magazzino_Cassa!B11</f>
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>21</v>
@@ -2638,7 +2800,7 @@
       </c>
       <c r="H17" s="5">
         <f>Magazzino_Cassa!B14</f>
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>21</v>
@@ -2681,7 +2843,7 @@
       </c>
       <c r="B19" s="7">
         <f>Magazzino_Cassa!B16</f>
-        <v>306</v>
+        <v>418</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>34</v>
@@ -2737,7 +2899,7 @@
       </c>
       <c r="B21" s="4">
         <f>Magazzino_Cassa!B18</f>
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>18</v>
@@ -2760,20 +2922,20 @@
       </c>
     </row>
     <row r="23" spans="1:12" ht="26.75" customHeight="1">
-      <c r="A23" s="40" t="s">
+      <c r="A23" s="36" t="s">
         <v>46</v>
       </c>
-      <c r="B23" s="39"/>
-      <c r="C23" s="39"/>
-      <c r="D23" s="39"/>
-      <c r="E23" s="39"/>
-      <c r="F23" s="39"/>
-      <c r="G23" s="39"/>
-      <c r="H23" s="39"/>
-      <c r="I23" s="39"/>
-      <c r="J23" s="39"/>
-      <c r="K23" s="39"/>
-      <c r="L23" s="39"/>
+      <c r="B23" s="31"/>
+      <c r="C23" s="31"/>
+      <c r="D23" s="31"/>
+      <c r="E23" s="31"/>
+      <c r="F23" s="31"/>
+      <c r="G23" s="31"/>
+      <c r="H23" s="31"/>
+      <c r="I23" s="31"/>
+      <c r="J23" s="31"/>
+      <c r="K23" s="31"/>
+      <c r="L23" s="31"/>
     </row>
     <row r="24" spans="1:12" ht="85.25" customHeight="1">
       <c r="A24" s="6" t="s">
@@ -2801,12 +2963,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A4:C6"/>
-    <mergeCell ref="D4:F6"/>
-    <mergeCell ref="G4:I6"/>
-    <mergeCell ref="J4:L6"/>
     <mergeCell ref="A23:L23"/>
     <mergeCell ref="A8:C10"/>
     <mergeCell ref="D8:F10"/>
@@ -2814,12 +2970,18 @@
     <mergeCell ref="J8:L10"/>
     <mergeCell ref="A13:F13"/>
     <mergeCell ref="G13:L13"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A4:C6"/>
+    <mergeCell ref="D4:F6"/>
+    <mergeCell ref="G4:I6"/>
+    <mergeCell ref="J4:L6"/>
   </mergeCells>
   <conditionalFormatting sqref="B19">
-    <cfRule type="expression" dxfId="18" priority="1">
+    <cfRule type="expression" dxfId="22" priority="1">
       <formula>B19&lt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="17" priority="2">
+    <cfRule type="expression" dxfId="21" priority="2">
       <formula>B19&gt;=0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2831,7 +2993,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:J203"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -2843,32 +3005,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="26" customHeight="1">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="38" t="s">
         <v>207</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
-      <c r="G1" s="46"/>
-      <c r="H1" s="46"/>
-      <c r="I1" s="46"/>
-      <c r="J1" s="46"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="38"/>
     </row>
     <row r="2" spans="1:10" ht="34" customHeight="1">
-      <c r="A2" s="47" t="s">
+      <c r="A2" s="39" t="s">
         <v>208</v>
       </c>
-      <c r="B2" s="47"/>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
-      <c r="I2" s="47"/>
-      <c r="J2" s="47"/>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
+      <c r="I2" s="39"/>
+      <c r="J2" s="39"/>
     </row>
     <row r="3" spans="1:10" ht="38" customHeight="1">
       <c r="A3" s="15" t="s">
@@ -2906,33 +3068,33 @@
       <c r="A4" s="14" t="s">
         <v>224</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="B4" s="16" t="s">
         <v>157</v>
       </c>
-      <c r="C4" s="24">
+      <c r="C4" s="22">
         <v>10</v>
       </c>
-      <c r="D4" s="24">
+      <c r="D4" s="22">
         <f>IF(B4="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B4))</f>
         <v>10</v>
       </c>
-      <c r="E4" s="24"/>
-      <c r="F4" s="24">
+      <c r="E4" s="22"/>
+      <c r="F4" s="22">
         <f t="shared" ref="F4:F35" si="0">IF(B4="","",MAX(C4-D4-E4,0))</f>
         <v>0</v>
       </c>
-      <c r="G4" s="27">
+      <c r="G4" s="25">
         <f>IF(B4="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B4,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v>150</v>
       </c>
-      <c r="H4" s="27">
+      <c r="H4" s="25">
         <v>150</v>
       </c>
-      <c r="I4" s="27">
+      <c r="I4" s="25">
         <f t="shared" ref="I4:I35" si="1">IF(B4="","",MAX(G4-H4,0))</f>
         <v>0</v>
       </c>
-      <c r="J4" s="18" t="s">
+      <c r="J4" s="17" t="s">
         <v>225</v>
       </c>
     </row>
@@ -2940,4785 +3102,4785 @@
       <c r="A5" s="14" t="s">
         <v>224</v>
       </c>
-      <c r="B5" s="20" t="s">
+      <c r="B5" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="C5" s="25">
+      <c r="C5" s="23">
         <v>10</v>
       </c>
-      <c r="D5" s="25">
+      <c r="D5" s="23">
         <f>IF(B5="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B5))</f>
         <v>10</v>
       </c>
-      <c r="E5" s="25"/>
-      <c r="F5" s="25">
+      <c r="E5" s="23"/>
+      <c r="F5" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G5" s="28">
+      <c r="G5" s="26">
         <f>IF(B5="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B5,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v>150</v>
       </c>
-      <c r="H5" s="28">
+      <c r="H5" s="26">
         <v>150</v>
       </c>
-      <c r="I5" s="28">
+      <c r="I5" s="26">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J5" s="21"/>
+      <c r="J5" s="19"/>
     </row>
     <row r="6" spans="1:10" ht="22" customHeight="1">
       <c r="A6" s="14"/>
-      <c r="B6" s="20"/>
-      <c r="C6" s="25"/>
-      <c r="D6" s="25" t="str">
+      <c r="B6" s="18"/>
+      <c r="C6" s="23"/>
+      <c r="D6" s="23" t="str">
         <f>IF(B6="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B6))</f>
         <v/>
       </c>
-      <c r="E6" s="25"/>
-      <c r="F6" s="25" t="str">
+      <c r="E6" s="23"/>
+      <c r="F6" s="23" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G6" s="28" t="str">
+      <c r="G6" s="26" t="str">
         <f>IF(B6="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B6,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H6" s="28"/>
-      <c r="I6" s="28" t="str">
+      <c r="H6" s="26"/>
+      <c r="I6" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J6" s="21"/>
+      <c r="J6" s="19"/>
     </row>
     <row r="7" spans="1:10" ht="22" customHeight="1">
       <c r="A7" s="14"/>
-      <c r="B7" s="20"/>
-      <c r="C7" s="25"/>
-      <c r="D7" s="25" t="str">
+      <c r="B7" s="18"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="23" t="str">
         <f>IF(B7="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B7))</f>
         <v/>
       </c>
-      <c r="E7" s="25"/>
-      <c r="F7" s="25" t="str">
+      <c r="E7" s="23"/>
+      <c r="F7" s="23" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G7" s="28" t="str">
+      <c r="G7" s="26" t="str">
         <f>IF(B7="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B7,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H7" s="28"/>
-      <c r="I7" s="28" t="str">
+      <c r="H7" s="26"/>
+      <c r="I7" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J7" s="21"/>
+      <c r="J7" s="19"/>
     </row>
     <row r="8" spans="1:10" ht="22" customHeight="1">
       <c r="A8" s="14"/>
-      <c r="B8" s="20"/>
-      <c r="C8" s="25"/>
-      <c r="D8" s="25" t="str">
+      <c r="B8" s="18"/>
+      <c r="C8" s="23"/>
+      <c r="D8" s="23" t="str">
         <f>IF(B8="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B8))</f>
         <v/>
       </c>
-      <c r="E8" s="25"/>
-      <c r="F8" s="25" t="str">
+      <c r="E8" s="23"/>
+      <c r="F8" s="23" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G8" s="28" t="str">
+      <c r="G8" s="26" t="str">
         <f>IF(B8="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B8,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H8" s="28"/>
-      <c r="I8" s="28" t="str">
+      <c r="H8" s="26"/>
+      <c r="I8" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J8" s="21"/>
+      <c r="J8" s="19"/>
     </row>
     <row r="9" spans="1:10" ht="22" customHeight="1">
       <c r="A9" s="14"/>
-      <c r="B9" s="20"/>
-      <c r="C9" s="25"/>
-      <c r="D9" s="25" t="str">
+      <c r="B9" s="18"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="23" t="str">
         <f>IF(B9="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B9))</f>
         <v/>
       </c>
-      <c r="E9" s="25"/>
-      <c r="F9" s="25" t="str">
+      <c r="E9" s="23"/>
+      <c r="F9" s="23" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G9" s="28" t="str">
+      <c r="G9" s="26" t="str">
         <f>IF(B9="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B9,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H9" s="28"/>
-      <c r="I9" s="28" t="str">
+      <c r="H9" s="26"/>
+      <c r="I9" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J9" s="21"/>
+      <c r="J9" s="19"/>
     </row>
     <row r="10" spans="1:10" ht="22" customHeight="1">
       <c r="A10" s="14"/>
-      <c r="B10" s="20"/>
-      <c r="C10" s="25"/>
-      <c r="D10" s="25" t="str">
+      <c r="B10" s="18"/>
+      <c r="C10" s="23"/>
+      <c r="D10" s="23" t="str">
         <f>IF(B10="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B10))</f>
         <v/>
       </c>
-      <c r="E10" s="25"/>
-      <c r="F10" s="25" t="str">
+      <c r="E10" s="23"/>
+      <c r="F10" s="23" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G10" s="28" t="str">
+      <c r="G10" s="26" t="str">
         <f>IF(B10="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B10,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H10" s="28"/>
-      <c r="I10" s="28" t="str">
+      <c r="H10" s="26"/>
+      <c r="I10" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J10" s="21"/>
+      <c r="J10" s="19"/>
     </row>
     <row r="11" spans="1:10" ht="22" customHeight="1">
       <c r="A11" s="14"/>
-      <c r="B11" s="20"/>
-      <c r="C11" s="25"/>
-      <c r="D11" s="25" t="str">
+      <c r="B11" s="18"/>
+      <c r="C11" s="23"/>
+      <c r="D11" s="23" t="str">
         <f>IF(B11="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B11))</f>
         <v/>
       </c>
-      <c r="E11" s="25"/>
-      <c r="F11" s="25" t="str">
+      <c r="E11" s="23"/>
+      <c r="F11" s="23" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G11" s="28" t="str">
+      <c r="G11" s="26" t="str">
         <f>IF(B11="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B11,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H11" s="28"/>
-      <c r="I11" s="28" t="str">
+      <c r="H11" s="26"/>
+      <c r="I11" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J11" s="21"/>
+      <c r="J11" s="19"/>
     </row>
     <row r="12" spans="1:10" ht="22" customHeight="1">
       <c r="A12" s="14"/>
-      <c r="B12" s="20"/>
-      <c r="C12" s="25"/>
-      <c r="D12" s="25" t="str">
+      <c r="B12" s="18"/>
+      <c r="C12" s="23"/>
+      <c r="D12" s="23" t="str">
         <f>IF(B12="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B12))</f>
         <v/>
       </c>
-      <c r="E12" s="25"/>
-      <c r="F12" s="25" t="str">
+      <c r="E12" s="23"/>
+      <c r="F12" s="23" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G12" s="28" t="str">
+      <c r="G12" s="26" t="str">
         <f>IF(B12="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B12,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H12" s="28"/>
-      <c r="I12" s="28" t="str">
+      <c r="H12" s="26"/>
+      <c r="I12" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J12" s="21"/>
+      <c r="J12" s="19"/>
     </row>
     <row r="13" spans="1:10" ht="22" customHeight="1">
       <c r="A13" s="14"/>
-      <c r="B13" s="20"/>
-      <c r="C13" s="25"/>
-      <c r="D13" s="25" t="str">
+      <c r="B13" s="18"/>
+      <c r="C13" s="23"/>
+      <c r="D13" s="23" t="str">
         <f>IF(B13="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B13))</f>
         <v/>
       </c>
-      <c r="E13" s="25"/>
-      <c r="F13" s="25" t="str">
+      <c r="E13" s="23"/>
+      <c r="F13" s="23" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G13" s="28" t="str">
+      <c r="G13" s="26" t="str">
         <f>IF(B13="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B13,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H13" s="28"/>
-      <c r="I13" s="28" t="str">
+      <c r="H13" s="26"/>
+      <c r="I13" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J13" s="21"/>
+      <c r="J13" s="19"/>
     </row>
     <row r="14" spans="1:10" ht="22" customHeight="1">
       <c r="A14" s="14"/>
-      <c r="B14" s="20"/>
-      <c r="C14" s="25"/>
-      <c r="D14" s="25" t="str">
+      <c r="B14" s="18"/>
+      <c r="C14" s="23"/>
+      <c r="D14" s="23" t="str">
         <f>IF(B14="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B14))</f>
         <v/>
       </c>
-      <c r="E14" s="25"/>
-      <c r="F14" s="25" t="str">
+      <c r="E14" s="23"/>
+      <c r="F14" s="23" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G14" s="28" t="str">
+      <c r="G14" s="26" t="str">
         <f>IF(B14="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B14,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H14" s="28"/>
-      <c r="I14" s="28" t="str">
+      <c r="H14" s="26"/>
+      <c r="I14" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J14" s="21"/>
+      <c r="J14" s="19"/>
     </row>
     <row r="15" spans="1:10" ht="22" customHeight="1">
       <c r="A15" s="14"/>
-      <c r="B15" s="20"/>
-      <c r="C15" s="25"/>
-      <c r="D15" s="25" t="str">
+      <c r="B15" s="18"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="23" t="str">
         <f>IF(B15="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B15))</f>
         <v/>
       </c>
-      <c r="E15" s="25"/>
-      <c r="F15" s="25" t="str">
+      <c r="E15" s="23"/>
+      <c r="F15" s="23" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G15" s="28" t="str">
+      <c r="G15" s="26" t="str">
         <f>IF(B15="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B15,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H15" s="28"/>
-      <c r="I15" s="28" t="str">
+      <c r="H15" s="26"/>
+      <c r="I15" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J15" s="21"/>
+      <c r="J15" s="19"/>
     </row>
     <row r="16" spans="1:10" ht="22" customHeight="1">
       <c r="A16" s="14"/>
-      <c r="B16" s="20"/>
-      <c r="C16" s="25"/>
-      <c r="D16" s="25" t="str">
+      <c r="B16" s="18"/>
+      <c r="C16" s="23"/>
+      <c r="D16" s="23" t="str">
         <f>IF(B16="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B16))</f>
         <v/>
       </c>
-      <c r="E16" s="25"/>
-      <c r="F16" s="25" t="str">
+      <c r="E16" s="23"/>
+      <c r="F16" s="23" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G16" s="28" t="str">
+      <c r="G16" s="26" t="str">
         <f>IF(B16="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B16,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H16" s="28"/>
-      <c r="I16" s="28" t="str">
+      <c r="H16" s="26"/>
+      <c r="I16" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J16" s="21"/>
+      <c r="J16" s="19"/>
     </row>
     <row r="17" spans="1:10" ht="22" customHeight="1">
       <c r="A17" s="14"/>
-      <c r="B17" s="20"/>
-      <c r="C17" s="25"/>
-      <c r="D17" s="25" t="str">
+      <c r="B17" s="18"/>
+      <c r="C17" s="23"/>
+      <c r="D17" s="23" t="str">
         <f>IF(B17="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B17))</f>
         <v/>
       </c>
-      <c r="E17" s="25"/>
-      <c r="F17" s="25" t="str">
+      <c r="E17" s="23"/>
+      <c r="F17" s="23" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G17" s="28" t="str">
+      <c r="G17" s="26" t="str">
         <f>IF(B17="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B17,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H17" s="28"/>
-      <c r="I17" s="28" t="str">
+      <c r="H17" s="26"/>
+      <c r="I17" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J17" s="21"/>
+      <c r="J17" s="19"/>
     </row>
     <row r="18" spans="1:10" ht="22" customHeight="1">
       <c r="A18" s="14"/>
-      <c r="B18" s="20"/>
-      <c r="C18" s="25"/>
-      <c r="D18" s="25" t="str">
+      <c r="B18" s="18"/>
+      <c r="C18" s="23"/>
+      <c r="D18" s="23" t="str">
         <f>IF(B18="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B18))</f>
         <v/>
       </c>
-      <c r="E18" s="25"/>
-      <c r="F18" s="25" t="str">
+      <c r="E18" s="23"/>
+      <c r="F18" s="23" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G18" s="28" t="str">
+      <c r="G18" s="26" t="str">
         <f>IF(B18="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B18,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H18" s="28"/>
-      <c r="I18" s="28" t="str">
+      <c r="H18" s="26"/>
+      <c r="I18" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J18" s="21"/>
+      <c r="J18" s="19"/>
     </row>
     <row r="19" spans="1:10" ht="22" customHeight="1">
       <c r="A19" s="14"/>
-      <c r="B19" s="20"/>
-      <c r="C19" s="25"/>
-      <c r="D19" s="25" t="str">
+      <c r="B19" s="18"/>
+      <c r="C19" s="23"/>
+      <c r="D19" s="23" t="str">
         <f>IF(B19="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B19))</f>
         <v/>
       </c>
-      <c r="E19" s="25"/>
-      <c r="F19" s="25" t="str">
+      <c r="E19" s="23"/>
+      <c r="F19" s="23" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G19" s="28" t="str">
+      <c r="G19" s="26" t="str">
         <f>IF(B19="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B19,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H19" s="28"/>
-      <c r="I19" s="28" t="str">
+      <c r="H19" s="26"/>
+      <c r="I19" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J19" s="21"/>
+      <c r="J19" s="19"/>
     </row>
     <row r="20" spans="1:10" ht="22" customHeight="1">
       <c r="A20" s="14"/>
-      <c r="B20" s="20"/>
-      <c r="C20" s="25"/>
-      <c r="D20" s="25" t="str">
+      <c r="B20" s="18"/>
+      <c r="C20" s="23"/>
+      <c r="D20" s="23" t="str">
         <f>IF(B20="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B20))</f>
         <v/>
       </c>
-      <c r="E20" s="25"/>
-      <c r="F20" s="25" t="str">
+      <c r="E20" s="23"/>
+      <c r="F20" s="23" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G20" s="28" t="str">
+      <c r="G20" s="26" t="str">
         <f>IF(B20="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B20,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H20" s="28"/>
-      <c r="I20" s="28" t="str">
+      <c r="H20" s="26"/>
+      <c r="I20" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J20" s="21"/>
+      <c r="J20" s="19"/>
     </row>
     <row r="21" spans="1:10" ht="22" customHeight="1">
       <c r="A21" s="14"/>
-      <c r="B21" s="20"/>
-      <c r="C21" s="25"/>
-      <c r="D21" s="25" t="str">
+      <c r="B21" s="18"/>
+      <c r="C21" s="23"/>
+      <c r="D21" s="23" t="str">
         <f>IF(B21="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B21))</f>
         <v/>
       </c>
-      <c r="E21" s="25"/>
-      <c r="F21" s="25" t="str">
+      <c r="E21" s="23"/>
+      <c r="F21" s="23" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G21" s="28" t="str">
+      <c r="G21" s="26" t="str">
         <f>IF(B21="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B21,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H21" s="28"/>
-      <c r="I21" s="28" t="str">
+      <c r="H21" s="26"/>
+      <c r="I21" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J21" s="21"/>
+      <c r="J21" s="19"/>
     </row>
     <row r="22" spans="1:10" ht="22" customHeight="1">
       <c r="A22" s="14"/>
-      <c r="B22" s="20"/>
-      <c r="C22" s="25"/>
-      <c r="D22" s="25" t="str">
+      <c r="B22" s="18"/>
+      <c r="C22" s="23"/>
+      <c r="D22" s="23" t="str">
         <f>IF(B22="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B22))</f>
         <v/>
       </c>
-      <c r="E22" s="25"/>
-      <c r="F22" s="25" t="str">
+      <c r="E22" s="23"/>
+      <c r="F22" s="23" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G22" s="28" t="str">
+      <c r="G22" s="26" t="str">
         <f>IF(B22="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B22,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H22" s="28"/>
-      <c r="I22" s="28" t="str">
+      <c r="H22" s="26"/>
+      <c r="I22" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J22" s="21"/>
+      <c r="J22" s="19"/>
     </row>
     <row r="23" spans="1:10" ht="22" customHeight="1">
       <c r="A23" s="14"/>
-      <c r="B23" s="20"/>
-      <c r="C23" s="25"/>
-      <c r="D23" s="25" t="str">
+      <c r="B23" s="18"/>
+      <c r="C23" s="23"/>
+      <c r="D23" s="23" t="str">
         <f>IF(B23="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B23))</f>
         <v/>
       </c>
-      <c r="E23" s="25"/>
-      <c r="F23" s="25" t="str">
+      <c r="E23" s="23"/>
+      <c r="F23" s="23" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G23" s="28" t="str">
+      <c r="G23" s="26" t="str">
         <f>IF(B23="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B23,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H23" s="28"/>
-      <c r="I23" s="28" t="str">
+      <c r="H23" s="26"/>
+      <c r="I23" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J23" s="21"/>
+      <c r="J23" s="19"/>
     </row>
     <row r="24" spans="1:10" ht="22" customHeight="1">
       <c r="A24" s="14"/>
-      <c r="B24" s="20"/>
-      <c r="C24" s="25"/>
-      <c r="D24" s="25" t="str">
+      <c r="B24" s="18"/>
+      <c r="C24" s="23"/>
+      <c r="D24" s="23" t="str">
         <f>IF(B24="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B24))</f>
         <v/>
       </c>
-      <c r="E24" s="25"/>
-      <c r="F24" s="25" t="str">
+      <c r="E24" s="23"/>
+      <c r="F24" s="23" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G24" s="28" t="str">
+      <c r="G24" s="26" t="str">
         <f>IF(B24="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B24,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H24" s="28"/>
-      <c r="I24" s="28" t="str">
+      <c r="H24" s="26"/>
+      <c r="I24" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J24" s="21"/>
+      <c r="J24" s="19"/>
     </row>
     <row r="25" spans="1:10" ht="22" customHeight="1">
       <c r="A25" s="14"/>
-      <c r="B25" s="20"/>
-      <c r="C25" s="25"/>
-      <c r="D25" s="25" t="str">
+      <c r="B25" s="18"/>
+      <c r="C25" s="23"/>
+      <c r="D25" s="23" t="str">
         <f>IF(B25="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B25))</f>
         <v/>
       </c>
-      <c r="E25" s="25"/>
-      <c r="F25" s="25" t="str">
+      <c r="E25" s="23"/>
+      <c r="F25" s="23" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G25" s="28" t="str">
+      <c r="G25" s="26" t="str">
         <f>IF(B25="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B25,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H25" s="28"/>
-      <c r="I25" s="28" t="str">
+      <c r="H25" s="26"/>
+      <c r="I25" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J25" s="21"/>
+      <c r="J25" s="19"/>
     </row>
     <row r="26" spans="1:10" ht="22" customHeight="1">
       <c r="A26" s="14"/>
-      <c r="B26" s="20"/>
-      <c r="C26" s="25"/>
-      <c r="D26" s="25" t="str">
+      <c r="B26" s="18"/>
+      <c r="C26" s="23"/>
+      <c r="D26" s="23" t="str">
         <f>IF(B26="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B26))</f>
         <v/>
       </c>
-      <c r="E26" s="25"/>
-      <c r="F26" s="25" t="str">
+      <c r="E26" s="23"/>
+      <c r="F26" s="23" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G26" s="28" t="str">
+      <c r="G26" s="26" t="str">
         <f>IF(B26="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B26,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H26" s="28"/>
-      <c r="I26" s="28" t="str">
+      <c r="H26" s="26"/>
+      <c r="I26" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J26" s="21"/>
+      <c r="J26" s="19"/>
     </row>
     <row r="27" spans="1:10" ht="22" customHeight="1">
       <c r="A27" s="14"/>
-      <c r="B27" s="20"/>
-      <c r="C27" s="25"/>
-      <c r="D27" s="25" t="str">
+      <c r="B27" s="18"/>
+      <c r="C27" s="23"/>
+      <c r="D27" s="23" t="str">
         <f>IF(B27="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B27))</f>
         <v/>
       </c>
-      <c r="E27" s="25"/>
-      <c r="F27" s="25" t="str">
+      <c r="E27" s="23"/>
+      <c r="F27" s="23" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G27" s="28" t="str">
+      <c r="G27" s="26" t="str">
         <f>IF(B27="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B27,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H27" s="28"/>
-      <c r="I27" s="28" t="str">
+      <c r="H27" s="26"/>
+      <c r="I27" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J27" s="21"/>
+      <c r="J27" s="19"/>
     </row>
     <row r="28" spans="1:10" ht="22" customHeight="1">
       <c r="A28" s="14"/>
-      <c r="B28" s="20"/>
-      <c r="C28" s="25"/>
-      <c r="D28" s="25" t="str">
+      <c r="B28" s="18"/>
+      <c r="C28" s="23"/>
+      <c r="D28" s="23" t="str">
         <f>IF(B28="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B28))</f>
         <v/>
       </c>
-      <c r="E28" s="25"/>
-      <c r="F28" s="25" t="str">
+      <c r="E28" s="23"/>
+      <c r="F28" s="23" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G28" s="28" t="str">
+      <c r="G28" s="26" t="str">
         <f>IF(B28="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B28,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H28" s="28"/>
-      <c r="I28" s="28" t="str">
+      <c r="H28" s="26"/>
+      <c r="I28" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J28" s="21"/>
+      <c r="J28" s="19"/>
     </row>
     <row r="29" spans="1:10" ht="22" customHeight="1">
       <c r="A29" s="14"/>
-      <c r="B29" s="20"/>
-      <c r="C29" s="25"/>
-      <c r="D29" s="25" t="str">
+      <c r="B29" s="18"/>
+      <c r="C29" s="23"/>
+      <c r="D29" s="23" t="str">
         <f>IF(B29="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B29))</f>
         <v/>
       </c>
-      <c r="E29" s="25"/>
-      <c r="F29" s="25" t="str">
+      <c r="E29" s="23"/>
+      <c r="F29" s="23" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G29" s="28" t="str">
+      <c r="G29" s="26" t="str">
         <f>IF(B29="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B29,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H29" s="28"/>
-      <c r="I29" s="28" t="str">
+      <c r="H29" s="26"/>
+      <c r="I29" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J29" s="21"/>
+      <c r="J29" s="19"/>
     </row>
     <row r="30" spans="1:10" ht="22" customHeight="1">
       <c r="A30" s="14"/>
-      <c r="B30" s="20"/>
-      <c r="C30" s="25"/>
-      <c r="D30" s="25" t="str">
+      <c r="B30" s="18"/>
+      <c r="C30" s="23"/>
+      <c r="D30" s="23" t="str">
         <f>IF(B30="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B30))</f>
         <v/>
       </c>
-      <c r="E30" s="25"/>
-      <c r="F30" s="25" t="str">
+      <c r="E30" s="23"/>
+      <c r="F30" s="23" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G30" s="28" t="str">
+      <c r="G30" s="26" t="str">
         <f>IF(B30="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B30,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H30" s="28"/>
-      <c r="I30" s="28" t="str">
+      <c r="H30" s="26"/>
+      <c r="I30" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J30" s="21"/>
+      <c r="J30" s="19"/>
     </row>
     <row r="31" spans="1:10" ht="22" customHeight="1">
       <c r="A31" s="14"/>
-      <c r="B31" s="20"/>
-      <c r="C31" s="25"/>
-      <c r="D31" s="25" t="str">
+      <c r="B31" s="18"/>
+      <c r="C31" s="23"/>
+      <c r="D31" s="23" t="str">
         <f>IF(B31="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B31))</f>
         <v/>
       </c>
-      <c r="E31" s="25"/>
-      <c r="F31" s="25" t="str">
+      <c r="E31" s="23"/>
+      <c r="F31" s="23" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G31" s="28" t="str">
+      <c r="G31" s="26" t="str">
         <f>IF(B31="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B31,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H31" s="28"/>
-      <c r="I31" s="28" t="str">
+      <c r="H31" s="26"/>
+      <c r="I31" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J31" s="21"/>
+      <c r="J31" s="19"/>
     </row>
     <row r="32" spans="1:10" ht="22" customHeight="1">
       <c r="A32" s="14"/>
-      <c r="B32" s="20"/>
-      <c r="C32" s="25"/>
-      <c r="D32" s="25" t="str">
+      <c r="B32" s="18"/>
+      <c r="C32" s="23"/>
+      <c r="D32" s="23" t="str">
         <f>IF(B32="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B32))</f>
         <v/>
       </c>
-      <c r="E32" s="25"/>
-      <c r="F32" s="25" t="str">
+      <c r="E32" s="23"/>
+      <c r="F32" s="23" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G32" s="28" t="str">
+      <c r="G32" s="26" t="str">
         <f>IF(B32="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B32,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H32" s="28"/>
-      <c r="I32" s="28" t="str">
+      <c r="H32" s="26"/>
+      <c r="I32" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J32" s="21"/>
+      <c r="J32" s="19"/>
     </row>
     <row r="33" spans="1:10" ht="22" customHeight="1">
       <c r="A33" s="14"/>
-      <c r="B33" s="20"/>
-      <c r="C33" s="25"/>
-      <c r="D33" s="25" t="str">
+      <c r="B33" s="18"/>
+      <c r="C33" s="23"/>
+      <c r="D33" s="23" t="str">
         <f>IF(B33="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B33))</f>
         <v/>
       </c>
-      <c r="E33" s="25"/>
-      <c r="F33" s="25" t="str">
+      <c r="E33" s="23"/>
+      <c r="F33" s="23" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G33" s="28" t="str">
+      <c r="G33" s="26" t="str">
         <f>IF(B33="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B33,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H33" s="28"/>
-      <c r="I33" s="28" t="str">
+      <c r="H33" s="26"/>
+      <c r="I33" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J33" s="21"/>
+      <c r="J33" s="19"/>
     </row>
     <row r="34" spans="1:10" ht="22" customHeight="1">
       <c r="A34" s="14"/>
-      <c r="B34" s="20"/>
-      <c r="C34" s="25"/>
-      <c r="D34" s="25" t="str">
+      <c r="B34" s="18"/>
+      <c r="C34" s="23"/>
+      <c r="D34" s="23" t="str">
         <f>IF(B34="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B34))</f>
         <v/>
       </c>
-      <c r="E34" s="25"/>
-      <c r="F34" s="25" t="str">
+      <c r="E34" s="23"/>
+      <c r="F34" s="23" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G34" s="28" t="str">
+      <c r="G34" s="26" t="str">
         <f>IF(B34="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B34,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H34" s="28"/>
-      <c r="I34" s="28" t="str">
+      <c r="H34" s="26"/>
+      <c r="I34" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J34" s="21"/>
+      <c r="J34" s="19"/>
     </row>
     <row r="35" spans="1:10" ht="22" customHeight="1">
       <c r="A35" s="14"/>
-      <c r="B35" s="20"/>
-      <c r="C35" s="25"/>
-      <c r="D35" s="25" t="str">
+      <c r="B35" s="18"/>
+      <c r="C35" s="23"/>
+      <c r="D35" s="23" t="str">
         <f>IF(B35="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B35))</f>
         <v/>
       </c>
-      <c r="E35" s="25"/>
-      <c r="F35" s="25" t="str">
+      <c r="E35" s="23"/>
+      <c r="F35" s="23" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G35" s="28" t="str">
+      <c r="G35" s="26" t="str">
         <f>IF(B35="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B35,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H35" s="28"/>
-      <c r="I35" s="28" t="str">
+      <c r="H35" s="26"/>
+      <c r="I35" s="26" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="J35" s="21"/>
+      <c r="J35" s="19"/>
     </row>
     <row r="36" spans="1:10" ht="22" customHeight="1">
       <c r="A36" s="14"/>
-      <c r="B36" s="20"/>
-      <c r="C36" s="25"/>
-      <c r="D36" s="25" t="str">
+      <c r="B36" s="18"/>
+      <c r="C36" s="23"/>
+      <c r="D36" s="23" t="str">
         <f>IF(B36="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B36))</f>
         <v/>
       </c>
-      <c r="E36" s="25"/>
-      <c r="F36" s="25" t="str">
+      <c r="E36" s="23"/>
+      <c r="F36" s="23" t="str">
         <f t="shared" ref="F36:F67" si="2">IF(B36="","",MAX(C36-D36-E36,0))</f>
         <v/>
       </c>
-      <c r="G36" s="28" t="str">
+      <c r="G36" s="26" t="str">
         <f>IF(B36="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B36,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H36" s="28"/>
-      <c r="I36" s="28" t="str">
+      <c r="H36" s="26"/>
+      <c r="I36" s="26" t="str">
         <f t="shared" ref="I36:I67" si="3">IF(B36="","",MAX(G36-H36,0))</f>
         <v/>
       </c>
-      <c r="J36" s="21"/>
+      <c r="J36" s="19"/>
     </row>
     <row r="37" spans="1:10" ht="22" customHeight="1">
       <c r="A37" s="14"/>
-      <c r="B37" s="20"/>
-      <c r="C37" s="25"/>
-      <c r="D37" s="25" t="str">
+      <c r="B37" s="18"/>
+      <c r="C37" s="23"/>
+      <c r="D37" s="23" t="str">
         <f>IF(B37="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B37))</f>
         <v/>
       </c>
-      <c r="E37" s="25"/>
-      <c r="F37" s="25" t="str">
+      <c r="E37" s="23"/>
+      <c r="F37" s="23" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="G37" s="28" t="str">
+      <c r="G37" s="26" t="str">
         <f>IF(B37="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B37,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H37" s="28"/>
-      <c r="I37" s="28" t="str">
+      <c r="H37" s="26"/>
+      <c r="I37" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J37" s="21"/>
+      <c r="J37" s="19"/>
     </row>
     <row r="38" spans="1:10" ht="22" customHeight="1">
       <c r="A38" s="14"/>
-      <c r="B38" s="20"/>
-      <c r="C38" s="25"/>
-      <c r="D38" s="25" t="str">
+      <c r="B38" s="18"/>
+      <c r="C38" s="23"/>
+      <c r="D38" s="23" t="str">
         <f>IF(B38="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B38))</f>
         <v/>
       </c>
-      <c r="E38" s="25"/>
-      <c r="F38" s="25" t="str">
+      <c r="E38" s="23"/>
+      <c r="F38" s="23" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="G38" s="28" t="str">
+      <c r="G38" s="26" t="str">
         <f>IF(B38="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B38,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H38" s="28"/>
-      <c r="I38" s="28" t="str">
+      <c r="H38" s="26"/>
+      <c r="I38" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J38" s="21"/>
+      <c r="J38" s="19"/>
     </row>
     <row r="39" spans="1:10" ht="22" customHeight="1">
       <c r="A39" s="14"/>
-      <c r="B39" s="20"/>
-      <c r="C39" s="25"/>
-      <c r="D39" s="25" t="str">
+      <c r="B39" s="18"/>
+      <c r="C39" s="23"/>
+      <c r="D39" s="23" t="str">
         <f>IF(B39="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B39))</f>
         <v/>
       </c>
-      <c r="E39" s="25"/>
-      <c r="F39" s="25" t="str">
+      <c r="E39" s="23"/>
+      <c r="F39" s="23" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="G39" s="28" t="str">
+      <c r="G39" s="26" t="str">
         <f>IF(B39="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B39,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H39" s="28"/>
-      <c r="I39" s="28" t="str">
+      <c r="H39" s="26"/>
+      <c r="I39" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J39" s="21"/>
+      <c r="J39" s="19"/>
     </row>
     <row r="40" spans="1:10" ht="22" customHeight="1">
       <c r="A40" s="14"/>
-      <c r="B40" s="20"/>
-      <c r="C40" s="25"/>
-      <c r="D40" s="25" t="str">
+      <c r="B40" s="18"/>
+      <c r="C40" s="23"/>
+      <c r="D40" s="23" t="str">
         <f>IF(B40="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B40))</f>
         <v/>
       </c>
-      <c r="E40" s="25"/>
-      <c r="F40" s="25" t="str">
+      <c r="E40" s="23"/>
+      <c r="F40" s="23" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="G40" s="28" t="str">
+      <c r="G40" s="26" t="str">
         <f>IF(B40="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B40,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H40" s="28"/>
-      <c r="I40" s="28" t="str">
+      <c r="H40" s="26"/>
+      <c r="I40" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J40" s="21"/>
+      <c r="J40" s="19"/>
     </row>
     <row r="41" spans="1:10" ht="22" customHeight="1">
       <c r="A41" s="14"/>
-      <c r="B41" s="20"/>
-      <c r="C41" s="25"/>
-      <c r="D41" s="25" t="str">
+      <c r="B41" s="18"/>
+      <c r="C41" s="23"/>
+      <c r="D41" s="23" t="str">
         <f>IF(B41="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B41))</f>
         <v/>
       </c>
-      <c r="E41" s="25"/>
-      <c r="F41" s="25" t="str">
+      <c r="E41" s="23"/>
+      <c r="F41" s="23" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="G41" s="28" t="str">
+      <c r="G41" s="26" t="str">
         <f>IF(B41="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B41,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H41" s="28"/>
-      <c r="I41" s="28" t="str">
+      <c r="H41" s="26"/>
+      <c r="I41" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J41" s="21"/>
+      <c r="J41" s="19"/>
     </row>
     <row r="42" spans="1:10" ht="22" customHeight="1">
       <c r="A42" s="14"/>
-      <c r="B42" s="20"/>
-      <c r="C42" s="25"/>
-      <c r="D42" s="25" t="str">
+      <c r="B42" s="18"/>
+      <c r="C42" s="23"/>
+      <c r="D42" s="23" t="str">
         <f>IF(B42="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B42))</f>
         <v/>
       </c>
-      <c r="E42" s="25"/>
-      <c r="F42" s="25" t="str">
+      <c r="E42" s="23"/>
+      <c r="F42" s="23" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="G42" s="28" t="str">
+      <c r="G42" s="26" t="str">
         <f>IF(B42="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B42,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H42" s="28"/>
-      <c r="I42" s="28" t="str">
+      <c r="H42" s="26"/>
+      <c r="I42" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J42" s="21"/>
+      <c r="J42" s="19"/>
     </row>
     <row r="43" spans="1:10" ht="22" customHeight="1">
       <c r="A43" s="14"/>
-      <c r="B43" s="20"/>
-      <c r="C43" s="25"/>
-      <c r="D43" s="25" t="str">
+      <c r="B43" s="18"/>
+      <c r="C43" s="23"/>
+      <c r="D43" s="23" t="str">
         <f>IF(B43="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B43))</f>
         <v/>
       </c>
-      <c r="E43" s="25"/>
-      <c r="F43" s="25" t="str">
+      <c r="E43" s="23"/>
+      <c r="F43" s="23" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="G43" s="28" t="str">
+      <c r="G43" s="26" t="str">
         <f>IF(B43="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B43,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H43" s="28"/>
-      <c r="I43" s="28" t="str">
+      <c r="H43" s="26"/>
+      <c r="I43" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J43" s="21"/>
+      <c r="J43" s="19"/>
     </row>
     <row r="44" spans="1:10" ht="22" customHeight="1">
       <c r="A44" s="14"/>
-      <c r="B44" s="20"/>
-      <c r="C44" s="25"/>
-      <c r="D44" s="25" t="str">
+      <c r="B44" s="18"/>
+      <c r="C44" s="23"/>
+      <c r="D44" s="23" t="str">
         <f>IF(B44="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B44))</f>
         <v/>
       </c>
-      <c r="E44" s="25"/>
-      <c r="F44" s="25" t="str">
+      <c r="E44" s="23"/>
+      <c r="F44" s="23" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="G44" s="28" t="str">
+      <c r="G44" s="26" t="str">
         <f>IF(B44="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B44,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H44" s="28"/>
-      <c r="I44" s="28" t="str">
+      <c r="H44" s="26"/>
+      <c r="I44" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J44" s="21"/>
+      <c r="J44" s="19"/>
     </row>
     <row r="45" spans="1:10" ht="22" customHeight="1">
       <c r="A45" s="14"/>
-      <c r="B45" s="20"/>
-      <c r="C45" s="25"/>
-      <c r="D45" s="25" t="str">
+      <c r="B45" s="18"/>
+      <c r="C45" s="23"/>
+      <c r="D45" s="23" t="str">
         <f>IF(B45="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B45))</f>
         <v/>
       </c>
-      <c r="E45" s="25"/>
-      <c r="F45" s="25" t="str">
+      <c r="E45" s="23"/>
+      <c r="F45" s="23" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="G45" s="28" t="str">
+      <c r="G45" s="26" t="str">
         <f>IF(B45="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B45,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H45" s="28"/>
-      <c r="I45" s="28" t="str">
+      <c r="H45" s="26"/>
+      <c r="I45" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J45" s="21"/>
+      <c r="J45" s="19"/>
     </row>
     <row r="46" spans="1:10" ht="22" customHeight="1">
       <c r="A46" s="14"/>
-      <c r="B46" s="20"/>
-      <c r="C46" s="25"/>
-      <c r="D46" s="25" t="str">
+      <c r="B46" s="18"/>
+      <c r="C46" s="23"/>
+      <c r="D46" s="23" t="str">
         <f>IF(B46="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B46))</f>
         <v/>
       </c>
-      <c r="E46" s="25"/>
-      <c r="F46" s="25" t="str">
+      <c r="E46" s="23"/>
+      <c r="F46" s="23" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="G46" s="28" t="str">
+      <c r="G46" s="26" t="str">
         <f>IF(B46="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B46,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H46" s="28"/>
-      <c r="I46" s="28" t="str">
+      <c r="H46" s="26"/>
+      <c r="I46" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J46" s="21"/>
+      <c r="J46" s="19"/>
     </row>
     <row r="47" spans="1:10" ht="22" customHeight="1">
       <c r="A47" s="14"/>
-      <c r="B47" s="20"/>
-      <c r="C47" s="25"/>
-      <c r="D47" s="25" t="str">
+      <c r="B47" s="18"/>
+      <c r="C47" s="23"/>
+      <c r="D47" s="23" t="str">
         <f>IF(B47="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B47))</f>
         <v/>
       </c>
-      <c r="E47" s="25"/>
-      <c r="F47" s="25" t="str">
+      <c r="E47" s="23"/>
+      <c r="F47" s="23" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="G47" s="28" t="str">
+      <c r="G47" s="26" t="str">
         <f>IF(B47="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B47,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H47" s="28"/>
-      <c r="I47" s="28" t="str">
+      <c r="H47" s="26"/>
+      <c r="I47" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J47" s="21"/>
+      <c r="J47" s="19"/>
     </row>
     <row r="48" spans="1:10" ht="22" customHeight="1">
       <c r="A48" s="14"/>
-      <c r="B48" s="20"/>
-      <c r="C48" s="25"/>
-      <c r="D48" s="25" t="str">
+      <c r="B48" s="18"/>
+      <c r="C48" s="23"/>
+      <c r="D48" s="23" t="str">
         <f>IF(B48="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B48))</f>
         <v/>
       </c>
-      <c r="E48" s="25"/>
-      <c r="F48" s="25" t="str">
+      <c r="E48" s="23"/>
+      <c r="F48" s="23" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="G48" s="28" t="str">
+      <c r="G48" s="26" t="str">
         <f>IF(B48="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B48,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H48" s="28"/>
-      <c r="I48" s="28" t="str">
+      <c r="H48" s="26"/>
+      <c r="I48" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J48" s="21"/>
+      <c r="J48" s="19"/>
     </row>
     <row r="49" spans="1:10" ht="22" customHeight="1">
       <c r="A49" s="14"/>
-      <c r="B49" s="20"/>
-      <c r="C49" s="25"/>
-      <c r="D49" s="25" t="str">
+      <c r="B49" s="18"/>
+      <c r="C49" s="23"/>
+      <c r="D49" s="23" t="str">
         <f>IF(B49="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B49))</f>
         <v/>
       </c>
-      <c r="E49" s="25"/>
-      <c r="F49" s="25" t="str">
+      <c r="E49" s="23"/>
+      <c r="F49" s="23" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="G49" s="28" t="str">
+      <c r="G49" s="26" t="str">
         <f>IF(B49="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B49,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H49" s="28"/>
-      <c r="I49" s="28" t="str">
+      <c r="H49" s="26"/>
+      <c r="I49" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J49" s="21"/>
+      <c r="J49" s="19"/>
     </row>
     <row r="50" spans="1:10" ht="22" customHeight="1">
       <c r="A50" s="14"/>
-      <c r="B50" s="20"/>
-      <c r="C50" s="25"/>
-      <c r="D50" s="25" t="str">
+      <c r="B50" s="18"/>
+      <c r="C50" s="23"/>
+      <c r="D50" s="23" t="str">
         <f>IF(B50="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B50))</f>
         <v/>
       </c>
-      <c r="E50" s="25"/>
-      <c r="F50" s="25" t="str">
+      <c r="E50" s="23"/>
+      <c r="F50" s="23" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="G50" s="28" t="str">
+      <c r="G50" s="26" t="str">
         <f>IF(B50="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B50,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H50" s="28"/>
-      <c r="I50" s="28" t="str">
+      <c r="H50" s="26"/>
+      <c r="I50" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J50" s="21"/>
+      <c r="J50" s="19"/>
     </row>
     <row r="51" spans="1:10" ht="22" customHeight="1">
       <c r="A51" s="14"/>
-      <c r="B51" s="20"/>
-      <c r="C51" s="25"/>
-      <c r="D51" s="25" t="str">
+      <c r="B51" s="18"/>
+      <c r="C51" s="23"/>
+      <c r="D51" s="23" t="str">
         <f>IF(B51="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B51))</f>
         <v/>
       </c>
-      <c r="E51" s="25"/>
-      <c r="F51" s="25" t="str">
+      <c r="E51" s="23"/>
+      <c r="F51" s="23" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="G51" s="28" t="str">
+      <c r="G51" s="26" t="str">
         <f>IF(B51="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B51,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H51" s="28"/>
-      <c r="I51" s="28" t="str">
+      <c r="H51" s="26"/>
+      <c r="I51" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J51" s="21"/>
+      <c r="J51" s="19"/>
     </row>
     <row r="52" spans="1:10" ht="22" customHeight="1">
       <c r="A52" s="14"/>
-      <c r="B52" s="20"/>
-      <c r="C52" s="25"/>
-      <c r="D52" s="25" t="str">
+      <c r="B52" s="18"/>
+      <c r="C52" s="23"/>
+      <c r="D52" s="23" t="str">
         <f>IF(B52="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B52))</f>
         <v/>
       </c>
-      <c r="E52" s="25"/>
-      <c r="F52" s="25" t="str">
+      <c r="E52" s="23"/>
+      <c r="F52" s="23" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="G52" s="28" t="str">
+      <c r="G52" s="26" t="str">
         <f>IF(B52="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B52,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H52" s="28"/>
-      <c r="I52" s="28" t="str">
+      <c r="H52" s="26"/>
+      <c r="I52" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J52" s="21"/>
+      <c r="J52" s="19"/>
     </row>
     <row r="53" spans="1:10" ht="22" customHeight="1">
       <c r="A53" s="14"/>
-      <c r="B53" s="20"/>
-      <c r="C53" s="25"/>
-      <c r="D53" s="25" t="str">
+      <c r="B53" s="18"/>
+      <c r="C53" s="23"/>
+      <c r="D53" s="23" t="str">
         <f>IF(B53="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B53))</f>
         <v/>
       </c>
-      <c r="E53" s="25"/>
-      <c r="F53" s="25" t="str">
+      <c r="E53" s="23"/>
+      <c r="F53" s="23" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="G53" s="28" t="str">
+      <c r="G53" s="26" t="str">
         <f>IF(B53="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B53,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H53" s="28"/>
-      <c r="I53" s="28" t="str">
+      <c r="H53" s="26"/>
+      <c r="I53" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J53" s="21"/>
+      <c r="J53" s="19"/>
     </row>
     <row r="54" spans="1:10" ht="22" customHeight="1">
       <c r="A54" s="14"/>
-      <c r="B54" s="20"/>
-      <c r="C54" s="25"/>
-      <c r="D54" s="25" t="str">
+      <c r="B54" s="18"/>
+      <c r="C54" s="23"/>
+      <c r="D54" s="23" t="str">
         <f>IF(B54="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B54))</f>
         <v/>
       </c>
-      <c r="E54" s="25"/>
-      <c r="F54" s="25" t="str">
+      <c r="E54" s="23"/>
+      <c r="F54" s="23" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="G54" s="28" t="str">
+      <c r="G54" s="26" t="str">
         <f>IF(B54="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B54,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H54" s="28"/>
-      <c r="I54" s="28" t="str">
+      <c r="H54" s="26"/>
+      <c r="I54" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J54" s="21"/>
+      <c r="J54" s="19"/>
     </row>
     <row r="55" spans="1:10" ht="22" customHeight="1">
       <c r="A55" s="14"/>
-      <c r="B55" s="20"/>
-      <c r="C55" s="25"/>
-      <c r="D55" s="25" t="str">
+      <c r="B55" s="18"/>
+      <c r="C55" s="23"/>
+      <c r="D55" s="23" t="str">
         <f>IF(B55="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B55))</f>
         <v/>
       </c>
-      <c r="E55" s="25"/>
-      <c r="F55" s="25" t="str">
+      <c r="E55" s="23"/>
+      <c r="F55" s="23" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="G55" s="28" t="str">
+      <c r="G55" s="26" t="str">
         <f>IF(B55="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B55,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H55" s="28"/>
-      <c r="I55" s="28" t="str">
+      <c r="H55" s="26"/>
+      <c r="I55" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J55" s="21"/>
+      <c r="J55" s="19"/>
     </row>
     <row r="56" spans="1:10" ht="22" customHeight="1">
       <c r="A56" s="14"/>
-      <c r="B56" s="20"/>
-      <c r="C56" s="25"/>
-      <c r="D56" s="25" t="str">
+      <c r="B56" s="18"/>
+      <c r="C56" s="23"/>
+      <c r="D56" s="23" t="str">
         <f>IF(B56="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B56))</f>
         <v/>
       </c>
-      <c r="E56" s="25"/>
-      <c r="F56" s="25" t="str">
+      <c r="E56" s="23"/>
+      <c r="F56" s="23" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="G56" s="28" t="str">
+      <c r="G56" s="26" t="str">
         <f>IF(B56="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B56,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H56" s="28"/>
-      <c r="I56" s="28" t="str">
+      <c r="H56" s="26"/>
+      <c r="I56" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J56" s="21"/>
+      <c r="J56" s="19"/>
     </row>
     <row r="57" spans="1:10" ht="22" customHeight="1">
       <c r="A57" s="14"/>
-      <c r="B57" s="20"/>
-      <c r="C57" s="25"/>
-      <c r="D57" s="25" t="str">
+      <c r="B57" s="18"/>
+      <c r="C57" s="23"/>
+      <c r="D57" s="23" t="str">
         <f>IF(B57="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B57))</f>
         <v/>
       </c>
-      <c r="E57" s="25"/>
-      <c r="F57" s="25" t="str">
+      <c r="E57" s="23"/>
+      <c r="F57" s="23" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="G57" s="28" t="str">
+      <c r="G57" s="26" t="str">
         <f>IF(B57="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B57,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H57" s="28"/>
-      <c r="I57" s="28" t="str">
+      <c r="H57" s="26"/>
+      <c r="I57" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J57" s="21"/>
+      <c r="J57" s="19"/>
     </row>
     <row r="58" spans="1:10" ht="22" customHeight="1">
       <c r="A58" s="14"/>
-      <c r="B58" s="20"/>
-      <c r="C58" s="25"/>
-      <c r="D58" s="25" t="str">
+      <c r="B58" s="18"/>
+      <c r="C58" s="23"/>
+      <c r="D58" s="23" t="str">
         <f>IF(B58="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B58))</f>
         <v/>
       </c>
-      <c r="E58" s="25"/>
-      <c r="F58" s="25" t="str">
+      <c r="E58" s="23"/>
+      <c r="F58" s="23" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="G58" s="28" t="str">
+      <c r="G58" s="26" t="str">
         <f>IF(B58="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B58,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H58" s="28"/>
-      <c r="I58" s="28" t="str">
+      <c r="H58" s="26"/>
+      <c r="I58" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J58" s="21"/>
+      <c r="J58" s="19"/>
     </row>
     <row r="59" spans="1:10" ht="22" customHeight="1">
       <c r="A59" s="14"/>
-      <c r="B59" s="20"/>
-      <c r="C59" s="25"/>
-      <c r="D59" s="25" t="str">
+      <c r="B59" s="18"/>
+      <c r="C59" s="23"/>
+      <c r="D59" s="23" t="str">
         <f>IF(B59="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B59))</f>
         <v/>
       </c>
-      <c r="E59" s="25"/>
-      <c r="F59" s="25" t="str">
+      <c r="E59" s="23"/>
+      <c r="F59" s="23" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="G59" s="28" t="str">
+      <c r="G59" s="26" t="str">
         <f>IF(B59="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B59,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H59" s="28"/>
-      <c r="I59" s="28" t="str">
+      <c r="H59" s="26"/>
+      <c r="I59" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J59" s="21"/>
+      <c r="J59" s="19"/>
     </row>
     <row r="60" spans="1:10" ht="22" customHeight="1">
       <c r="A60" s="14"/>
-      <c r="B60" s="20"/>
-      <c r="C60" s="25"/>
-      <c r="D60" s="25" t="str">
+      <c r="B60" s="18"/>
+      <c r="C60" s="23"/>
+      <c r="D60" s="23" t="str">
         <f>IF(B60="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B60))</f>
         <v/>
       </c>
-      <c r="E60" s="25"/>
-      <c r="F60" s="25" t="str">
+      <c r="E60" s="23"/>
+      <c r="F60" s="23" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="G60" s="28" t="str">
+      <c r="G60" s="26" t="str">
         <f>IF(B60="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B60,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H60" s="28"/>
-      <c r="I60" s="28" t="str">
+      <c r="H60" s="26"/>
+      <c r="I60" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J60" s="21"/>
+      <c r="J60" s="19"/>
     </row>
     <row r="61" spans="1:10" ht="22" customHeight="1">
       <c r="A61" s="14"/>
-      <c r="B61" s="20"/>
-      <c r="C61" s="25"/>
-      <c r="D61" s="25" t="str">
+      <c r="B61" s="18"/>
+      <c r="C61" s="23"/>
+      <c r="D61" s="23" t="str">
         <f>IF(B61="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B61))</f>
         <v/>
       </c>
-      <c r="E61" s="25"/>
-      <c r="F61" s="25" t="str">
+      <c r="E61" s="23"/>
+      <c r="F61" s="23" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="G61" s="28" t="str">
+      <c r="G61" s="26" t="str">
         <f>IF(B61="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B61,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H61" s="28"/>
-      <c r="I61" s="28" t="str">
+      <c r="H61" s="26"/>
+      <c r="I61" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J61" s="21"/>
+      <c r="J61" s="19"/>
     </row>
     <row r="62" spans="1:10" ht="22" customHeight="1">
       <c r="A62" s="14"/>
-      <c r="B62" s="20"/>
-      <c r="C62" s="25"/>
-      <c r="D62" s="25" t="str">
+      <c r="B62" s="18"/>
+      <c r="C62" s="23"/>
+      <c r="D62" s="23" t="str">
         <f>IF(B62="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B62))</f>
         <v/>
       </c>
-      <c r="E62" s="25"/>
-      <c r="F62" s="25" t="str">
+      <c r="E62" s="23"/>
+      <c r="F62" s="23" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="G62" s="28" t="str">
+      <c r="G62" s="26" t="str">
         <f>IF(B62="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B62,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H62" s="28"/>
-      <c r="I62" s="28" t="str">
+      <c r="H62" s="26"/>
+      <c r="I62" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J62" s="21"/>
+      <c r="J62" s="19"/>
     </row>
     <row r="63" spans="1:10" ht="22" customHeight="1">
       <c r="A63" s="14"/>
-      <c r="B63" s="20"/>
-      <c r="C63" s="25"/>
-      <c r="D63" s="25" t="str">
+      <c r="B63" s="18"/>
+      <c r="C63" s="23"/>
+      <c r="D63" s="23" t="str">
         <f>IF(B63="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B63))</f>
         <v/>
       </c>
-      <c r="E63" s="25"/>
-      <c r="F63" s="25" t="str">
+      <c r="E63" s="23"/>
+      <c r="F63" s="23" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="G63" s="28" t="str">
+      <c r="G63" s="26" t="str">
         <f>IF(B63="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B63,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H63" s="28"/>
-      <c r="I63" s="28" t="str">
+      <c r="H63" s="26"/>
+      <c r="I63" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J63" s="21"/>
+      <c r="J63" s="19"/>
     </row>
     <row r="64" spans="1:10" ht="22" customHeight="1">
       <c r="A64" s="14"/>
-      <c r="B64" s="20"/>
-      <c r="C64" s="25"/>
-      <c r="D64" s="25" t="str">
+      <c r="B64" s="18"/>
+      <c r="C64" s="23"/>
+      <c r="D64" s="23" t="str">
         <f>IF(B64="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B64))</f>
         <v/>
       </c>
-      <c r="E64" s="25"/>
-      <c r="F64" s="25" t="str">
+      <c r="E64" s="23"/>
+      <c r="F64" s="23" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="G64" s="28" t="str">
+      <c r="G64" s="26" t="str">
         <f>IF(B64="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B64,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H64" s="28"/>
-      <c r="I64" s="28" t="str">
+      <c r="H64" s="26"/>
+      <c r="I64" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J64" s="21"/>
+      <c r="J64" s="19"/>
     </row>
     <row r="65" spans="1:10" ht="22" customHeight="1">
       <c r="A65" s="14"/>
-      <c r="B65" s="20"/>
-      <c r="C65" s="25"/>
-      <c r="D65" s="25" t="str">
+      <c r="B65" s="18"/>
+      <c r="C65" s="23"/>
+      <c r="D65" s="23" t="str">
         <f>IF(B65="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B65))</f>
         <v/>
       </c>
-      <c r="E65" s="25"/>
-      <c r="F65" s="25" t="str">
+      <c r="E65" s="23"/>
+      <c r="F65" s="23" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="G65" s="28" t="str">
+      <c r="G65" s="26" t="str">
         <f>IF(B65="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B65,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H65" s="28"/>
-      <c r="I65" s="28" t="str">
+      <c r="H65" s="26"/>
+      <c r="I65" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J65" s="21"/>
+      <c r="J65" s="19"/>
     </row>
     <row r="66" spans="1:10" ht="22" customHeight="1">
       <c r="A66" s="14"/>
-      <c r="B66" s="20"/>
-      <c r="C66" s="25"/>
-      <c r="D66" s="25" t="str">
+      <c r="B66" s="18"/>
+      <c r="C66" s="23"/>
+      <c r="D66" s="23" t="str">
         <f>IF(B66="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B66))</f>
         <v/>
       </c>
-      <c r="E66" s="25"/>
-      <c r="F66" s="25" t="str">
+      <c r="E66" s="23"/>
+      <c r="F66" s="23" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="G66" s="28" t="str">
+      <c r="G66" s="26" t="str">
         <f>IF(B66="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B66,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H66" s="28"/>
-      <c r="I66" s="28" t="str">
+      <c r="H66" s="26"/>
+      <c r="I66" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J66" s="21"/>
+      <c r="J66" s="19"/>
     </row>
     <row r="67" spans="1:10" ht="22" customHeight="1">
       <c r="A67" s="14"/>
-      <c r="B67" s="20"/>
-      <c r="C67" s="25"/>
-      <c r="D67" s="25" t="str">
+      <c r="B67" s="18"/>
+      <c r="C67" s="23"/>
+      <c r="D67" s="23" t="str">
         <f>IF(B67="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B67))</f>
         <v/>
       </c>
-      <c r="E67" s="25"/>
-      <c r="F67" s="25" t="str">
+      <c r="E67" s="23"/>
+      <c r="F67" s="23" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="G67" s="28" t="str">
+      <c r="G67" s="26" t="str">
         <f>IF(B67="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B67,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H67" s="28"/>
-      <c r="I67" s="28" t="str">
+      <c r="H67" s="26"/>
+      <c r="I67" s="26" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J67" s="21"/>
+      <c r="J67" s="19"/>
     </row>
     <row r="68" spans="1:10" ht="22" customHeight="1">
       <c r="A68" s="14"/>
-      <c r="B68" s="20"/>
-      <c r="C68" s="25"/>
-      <c r="D68" s="25" t="str">
+      <c r="B68" s="18"/>
+      <c r="C68" s="23"/>
+      <c r="D68" s="23" t="str">
         <f>IF(B68="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B68))</f>
         <v/>
       </c>
-      <c r="E68" s="25"/>
-      <c r="F68" s="25" t="str">
+      <c r="E68" s="23"/>
+      <c r="F68" s="23" t="str">
         <f t="shared" ref="F68:F99" si="4">IF(B68="","",MAX(C68-D68-E68,0))</f>
         <v/>
       </c>
-      <c r="G68" s="28" t="str">
+      <c r="G68" s="26" t="str">
         <f>IF(B68="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B68,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H68" s="28"/>
-      <c r="I68" s="28" t="str">
+      <c r="H68" s="26"/>
+      <c r="I68" s="26" t="str">
         <f t="shared" ref="I68:I99" si="5">IF(B68="","",MAX(G68-H68,0))</f>
         <v/>
       </c>
-      <c r="J68" s="21"/>
+      <c r="J68" s="19"/>
     </row>
     <row r="69" spans="1:10" ht="22" customHeight="1">
       <c r="A69" s="14"/>
-      <c r="B69" s="20"/>
-      <c r="C69" s="25"/>
-      <c r="D69" s="25" t="str">
+      <c r="B69" s="18"/>
+      <c r="C69" s="23"/>
+      <c r="D69" s="23" t="str">
         <f>IF(B69="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B69))</f>
         <v/>
       </c>
-      <c r="E69" s="25"/>
-      <c r="F69" s="25" t="str">
+      <c r="E69" s="23"/>
+      <c r="F69" s="23" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="G69" s="28" t="str">
+      <c r="G69" s="26" t="str">
         <f>IF(B69="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B69,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H69" s="28"/>
-      <c r="I69" s="28" t="str">
+      <c r="H69" s="26"/>
+      <c r="I69" s="26" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="J69" s="21"/>
+      <c r="J69" s="19"/>
     </row>
     <row r="70" spans="1:10" ht="22" customHeight="1">
       <c r="A70" s="14"/>
-      <c r="B70" s="20"/>
-      <c r="C70" s="25"/>
-      <c r="D70" s="25" t="str">
+      <c r="B70" s="18"/>
+      <c r="C70" s="23"/>
+      <c r="D70" s="23" t="str">
         <f>IF(B70="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B70))</f>
         <v/>
       </c>
-      <c r="E70" s="25"/>
-      <c r="F70" s="25" t="str">
+      <c r="E70" s="23"/>
+      <c r="F70" s="23" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="G70" s="28" t="str">
+      <c r="G70" s="26" t="str">
         <f>IF(B70="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B70,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H70" s="28"/>
-      <c r="I70" s="28" t="str">
+      <c r="H70" s="26"/>
+      <c r="I70" s="26" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="J70" s="21"/>
+      <c r="J70" s="19"/>
     </row>
     <row r="71" spans="1:10" ht="22" customHeight="1">
       <c r="A71" s="14"/>
-      <c r="B71" s="20"/>
-      <c r="C71" s="25"/>
-      <c r="D71" s="25" t="str">
+      <c r="B71" s="18"/>
+      <c r="C71" s="23"/>
+      <c r="D71" s="23" t="str">
         <f>IF(B71="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B71))</f>
         <v/>
       </c>
-      <c r="E71" s="25"/>
-      <c r="F71" s="25" t="str">
+      <c r="E71" s="23"/>
+      <c r="F71" s="23" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="G71" s="28" t="str">
+      <c r="G71" s="26" t="str">
         <f>IF(B71="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B71,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H71" s="28"/>
-      <c r="I71" s="28" t="str">
+      <c r="H71" s="26"/>
+      <c r="I71" s="26" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="J71" s="21"/>
+      <c r="J71" s="19"/>
     </row>
     <row r="72" spans="1:10" ht="22" customHeight="1">
       <c r="A72" s="14"/>
-      <c r="B72" s="20"/>
-      <c r="C72" s="25"/>
-      <c r="D72" s="25" t="str">
+      <c r="B72" s="18"/>
+      <c r="C72" s="23"/>
+      <c r="D72" s="23" t="str">
         <f>IF(B72="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B72))</f>
         <v/>
       </c>
-      <c r="E72" s="25"/>
-      <c r="F72" s="25" t="str">
+      <c r="E72" s="23"/>
+      <c r="F72" s="23" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="G72" s="28" t="str">
+      <c r="G72" s="26" t="str">
         <f>IF(B72="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B72,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H72" s="28"/>
-      <c r="I72" s="28" t="str">
+      <c r="H72" s="26"/>
+      <c r="I72" s="26" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="J72" s="21"/>
+      <c r="J72" s="19"/>
     </row>
     <row r="73" spans="1:10" ht="22" customHeight="1">
       <c r="A73" s="14"/>
-      <c r="B73" s="20"/>
-      <c r="C73" s="25"/>
-      <c r="D73" s="25" t="str">
+      <c r="B73" s="18"/>
+      <c r="C73" s="23"/>
+      <c r="D73" s="23" t="str">
         <f>IF(B73="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B73))</f>
         <v/>
       </c>
-      <c r="E73" s="25"/>
-      <c r="F73" s="25" t="str">
+      <c r="E73" s="23"/>
+      <c r="F73" s="23" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="G73" s="28" t="str">
+      <c r="G73" s="26" t="str">
         <f>IF(B73="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B73,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H73" s="28"/>
-      <c r="I73" s="28" t="str">
+      <c r="H73" s="26"/>
+      <c r="I73" s="26" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="J73" s="21"/>
+      <c r="J73" s="19"/>
     </row>
     <row r="74" spans="1:10" ht="22" customHeight="1">
       <c r="A74" s="14"/>
-      <c r="B74" s="20"/>
-      <c r="C74" s="25"/>
-      <c r="D74" s="25" t="str">
+      <c r="B74" s="18"/>
+      <c r="C74" s="23"/>
+      <c r="D74" s="23" t="str">
         <f>IF(B74="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B74))</f>
         <v/>
       </c>
-      <c r="E74" s="25"/>
-      <c r="F74" s="25" t="str">
+      <c r="E74" s="23"/>
+      <c r="F74" s="23" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="G74" s="28" t="str">
+      <c r="G74" s="26" t="str">
         <f>IF(B74="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B74,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H74" s="28"/>
-      <c r="I74" s="28" t="str">
+      <c r="H74" s="26"/>
+      <c r="I74" s="26" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="J74" s="21"/>
+      <c r="J74" s="19"/>
     </row>
     <row r="75" spans="1:10" ht="22" customHeight="1">
       <c r="A75" s="14"/>
-      <c r="B75" s="20"/>
-      <c r="C75" s="25"/>
-      <c r="D75" s="25" t="str">
+      <c r="B75" s="18"/>
+      <c r="C75" s="23"/>
+      <c r="D75" s="23" t="str">
         <f>IF(B75="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B75))</f>
         <v/>
       </c>
-      <c r="E75" s="25"/>
-      <c r="F75" s="25" t="str">
+      <c r="E75" s="23"/>
+      <c r="F75" s="23" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="G75" s="28" t="str">
+      <c r="G75" s="26" t="str">
         <f>IF(B75="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B75,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H75" s="28"/>
-      <c r="I75" s="28" t="str">
+      <c r="H75" s="26"/>
+      <c r="I75" s="26" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="J75" s="21"/>
+      <c r="J75" s="19"/>
     </row>
     <row r="76" spans="1:10" ht="22" customHeight="1">
       <c r="A76" s="14"/>
-      <c r="B76" s="20"/>
-      <c r="C76" s="25"/>
-      <c r="D76" s="25" t="str">
+      <c r="B76" s="18"/>
+      <c r="C76" s="23"/>
+      <c r="D76" s="23" t="str">
         <f>IF(B76="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B76))</f>
         <v/>
       </c>
-      <c r="E76" s="25"/>
-      <c r="F76" s="25" t="str">
+      <c r="E76" s="23"/>
+      <c r="F76" s="23" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="G76" s="28" t="str">
+      <c r="G76" s="26" t="str">
         <f>IF(B76="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B76,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H76" s="28"/>
-      <c r="I76" s="28" t="str">
+      <c r="H76" s="26"/>
+      <c r="I76" s="26" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="J76" s="21"/>
+      <c r="J76" s="19"/>
     </row>
     <row r="77" spans="1:10" ht="22" customHeight="1">
       <c r="A77" s="14"/>
-      <c r="B77" s="20"/>
-      <c r="C77" s="25"/>
-      <c r="D77" s="25" t="str">
+      <c r="B77" s="18"/>
+      <c r="C77" s="23"/>
+      <c r="D77" s="23" t="str">
         <f>IF(B77="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B77))</f>
         <v/>
       </c>
-      <c r="E77" s="25"/>
-      <c r="F77" s="25" t="str">
+      <c r="E77" s="23"/>
+      <c r="F77" s="23" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="G77" s="28" t="str">
+      <c r="G77" s="26" t="str">
         <f>IF(B77="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B77,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H77" s="28"/>
-      <c r="I77" s="28" t="str">
+      <c r="H77" s="26"/>
+      <c r="I77" s="26" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="J77" s="21"/>
+      <c r="J77" s="19"/>
     </row>
     <row r="78" spans="1:10" ht="22" customHeight="1">
       <c r="A78" s="14"/>
-      <c r="B78" s="20"/>
-      <c r="C78" s="25"/>
-      <c r="D78" s="25" t="str">
+      <c r="B78" s="18"/>
+      <c r="C78" s="23"/>
+      <c r="D78" s="23" t="str">
         <f>IF(B78="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B78))</f>
         <v/>
       </c>
-      <c r="E78" s="25"/>
-      <c r="F78" s="25" t="str">
+      <c r="E78" s="23"/>
+      <c r="F78" s="23" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="G78" s="28" t="str">
+      <c r="G78" s="26" t="str">
         <f>IF(B78="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B78,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H78" s="28"/>
-      <c r="I78" s="28" t="str">
+      <c r="H78" s="26"/>
+      <c r="I78" s="26" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="J78" s="21"/>
+      <c r="J78" s="19"/>
     </row>
     <row r="79" spans="1:10" ht="22" customHeight="1">
       <c r="A79" s="14"/>
-      <c r="B79" s="20"/>
-      <c r="C79" s="25"/>
-      <c r="D79" s="25" t="str">
+      <c r="B79" s="18"/>
+      <c r="C79" s="23"/>
+      <c r="D79" s="23" t="str">
         <f>IF(B79="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B79))</f>
         <v/>
       </c>
-      <c r="E79" s="25"/>
-      <c r="F79" s="25" t="str">
+      <c r="E79" s="23"/>
+      <c r="F79" s="23" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="G79" s="28" t="str">
+      <c r="G79" s="26" t="str">
         <f>IF(B79="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B79,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H79" s="28"/>
-      <c r="I79" s="28" t="str">
+      <c r="H79" s="26"/>
+      <c r="I79" s="26" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="J79" s="21"/>
+      <c r="J79" s="19"/>
     </row>
     <row r="80" spans="1:10" ht="22" customHeight="1">
       <c r="A80" s="14"/>
-      <c r="B80" s="20"/>
-      <c r="C80" s="25"/>
-      <c r="D80" s="25" t="str">
+      <c r="B80" s="18"/>
+      <c r="C80" s="23"/>
+      <c r="D80" s="23" t="str">
         <f>IF(B80="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B80))</f>
         <v/>
       </c>
-      <c r="E80" s="25"/>
-      <c r="F80" s="25" t="str">
+      <c r="E80" s="23"/>
+      <c r="F80" s="23" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="G80" s="28" t="str">
+      <c r="G80" s="26" t="str">
         <f>IF(B80="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B80,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H80" s="28"/>
-      <c r="I80" s="28" t="str">
+      <c r="H80" s="26"/>
+      <c r="I80" s="26" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="J80" s="21"/>
+      <c r="J80" s="19"/>
     </row>
     <row r="81" spans="1:10" ht="22" customHeight="1">
       <c r="A81" s="14"/>
-      <c r="B81" s="20"/>
-      <c r="C81" s="25"/>
-      <c r="D81" s="25" t="str">
+      <c r="B81" s="18"/>
+      <c r="C81" s="23"/>
+      <c r="D81" s="23" t="str">
         <f>IF(B81="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B81))</f>
         <v/>
       </c>
-      <c r="E81" s="25"/>
-      <c r="F81" s="25" t="str">
+      <c r="E81" s="23"/>
+      <c r="F81" s="23" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="G81" s="28" t="str">
+      <c r="G81" s="26" t="str">
         <f>IF(B81="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B81,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H81" s="28"/>
-      <c r="I81" s="28" t="str">
+      <c r="H81" s="26"/>
+      <c r="I81" s="26" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="J81" s="21"/>
+      <c r="J81" s="19"/>
     </row>
     <row r="82" spans="1:10" ht="22" customHeight="1">
       <c r="A82" s="14"/>
-      <c r="B82" s="20"/>
-      <c r="C82" s="25"/>
-      <c r="D82" s="25" t="str">
+      <c r="B82" s="18"/>
+      <c r="C82" s="23"/>
+      <c r="D82" s="23" t="str">
         <f>IF(B82="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B82))</f>
         <v/>
       </c>
-      <c r="E82" s="25"/>
-      <c r="F82" s="25" t="str">
+      <c r="E82" s="23"/>
+      <c r="F82" s="23" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="G82" s="28" t="str">
+      <c r="G82" s="26" t="str">
         <f>IF(B82="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B82,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H82" s="28"/>
-      <c r="I82" s="28" t="str">
+      <c r="H82" s="26"/>
+      <c r="I82" s="26" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="J82" s="21"/>
+      <c r="J82" s="19"/>
     </row>
     <row r="83" spans="1:10" ht="22" customHeight="1">
       <c r="A83" s="14"/>
-      <c r="B83" s="20"/>
-      <c r="C83" s="25"/>
-      <c r="D83" s="25" t="str">
+      <c r="B83" s="18"/>
+      <c r="C83" s="23"/>
+      <c r="D83" s="23" t="str">
         <f>IF(B83="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B83))</f>
         <v/>
       </c>
-      <c r="E83" s="25"/>
-      <c r="F83" s="25" t="str">
+      <c r="E83" s="23"/>
+      <c r="F83" s="23" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="G83" s="28" t="str">
+      <c r="G83" s="26" t="str">
         <f>IF(B83="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B83,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H83" s="28"/>
-      <c r="I83" s="28" t="str">
+      <c r="H83" s="26"/>
+      <c r="I83" s="26" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="J83" s="21"/>
+      <c r="J83" s="19"/>
     </row>
     <row r="84" spans="1:10" ht="22" customHeight="1">
       <c r="A84" s="14"/>
-      <c r="B84" s="20"/>
-      <c r="C84" s="25"/>
-      <c r="D84" s="25" t="str">
+      <c r="B84" s="18"/>
+      <c r="C84" s="23"/>
+      <c r="D84" s="23" t="str">
         <f>IF(B84="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B84))</f>
         <v/>
       </c>
-      <c r="E84" s="25"/>
-      <c r="F84" s="25" t="str">
+      <c r="E84" s="23"/>
+      <c r="F84" s="23" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="G84" s="28" t="str">
+      <c r="G84" s="26" t="str">
         <f>IF(B84="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B84,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H84" s="28"/>
-      <c r="I84" s="28" t="str">
+      <c r="H84" s="26"/>
+      <c r="I84" s="26" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="J84" s="21"/>
+      <c r="J84" s="19"/>
     </row>
     <row r="85" spans="1:10" ht="22" customHeight="1">
       <c r="A85" s="14"/>
-      <c r="B85" s="20"/>
-      <c r="C85" s="25"/>
-      <c r="D85" s="25" t="str">
+      <c r="B85" s="18"/>
+      <c r="C85" s="23"/>
+      <c r="D85" s="23" t="str">
         <f>IF(B85="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B85))</f>
         <v/>
       </c>
-      <c r="E85" s="25"/>
-      <c r="F85" s="25" t="str">
+      <c r="E85" s="23"/>
+      <c r="F85" s="23" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="G85" s="28" t="str">
+      <c r="G85" s="26" t="str">
         <f>IF(B85="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B85,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H85" s="28"/>
-      <c r="I85" s="28" t="str">
+      <c r="H85" s="26"/>
+      <c r="I85" s="26" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="J85" s="21"/>
+      <c r="J85" s="19"/>
     </row>
     <row r="86" spans="1:10" ht="22" customHeight="1">
       <c r="A86" s="14"/>
-      <c r="B86" s="20"/>
-      <c r="C86" s="25"/>
-      <c r="D86" s="25" t="str">
+      <c r="B86" s="18"/>
+      <c r="C86" s="23"/>
+      <c r="D86" s="23" t="str">
         <f>IF(B86="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B86))</f>
         <v/>
       </c>
-      <c r="E86" s="25"/>
-      <c r="F86" s="25" t="str">
+      <c r="E86" s="23"/>
+      <c r="F86" s="23" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="G86" s="28" t="str">
+      <c r="G86" s="26" t="str">
         <f>IF(B86="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B86,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H86" s="28"/>
-      <c r="I86" s="28" t="str">
+      <c r="H86" s="26"/>
+      <c r="I86" s="26" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="J86" s="21"/>
+      <c r="J86" s="19"/>
     </row>
     <row r="87" spans="1:10" ht="22" customHeight="1">
       <c r="A87" s="14"/>
-      <c r="B87" s="20"/>
-      <c r="C87" s="25"/>
-      <c r="D87" s="25" t="str">
+      <c r="B87" s="18"/>
+      <c r="C87" s="23"/>
+      <c r="D87" s="23" t="str">
         <f>IF(B87="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B87))</f>
         <v/>
       </c>
-      <c r="E87" s="25"/>
-      <c r="F87" s="25" t="str">
+      <c r="E87" s="23"/>
+      <c r="F87" s="23" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="G87" s="28" t="str">
+      <c r="G87" s="26" t="str">
         <f>IF(B87="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B87,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H87" s="28"/>
-      <c r="I87" s="28" t="str">
+      <c r="H87" s="26"/>
+      <c r="I87" s="26" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="J87" s="21"/>
+      <c r="J87" s="19"/>
     </row>
     <row r="88" spans="1:10" ht="22" customHeight="1">
       <c r="A88" s="14"/>
-      <c r="B88" s="20"/>
-      <c r="C88" s="25"/>
-      <c r="D88" s="25" t="str">
+      <c r="B88" s="18"/>
+      <c r="C88" s="23"/>
+      <c r="D88" s="23" t="str">
         <f>IF(B88="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B88))</f>
         <v/>
       </c>
-      <c r="E88" s="25"/>
-      <c r="F88" s="25" t="str">
+      <c r="E88" s="23"/>
+      <c r="F88" s="23" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="G88" s="28" t="str">
+      <c r="G88" s="26" t="str">
         <f>IF(B88="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B88,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H88" s="28"/>
-      <c r="I88" s="28" t="str">
+      <c r="H88" s="26"/>
+      <c r="I88" s="26" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="J88" s="21"/>
+      <c r="J88" s="19"/>
     </row>
     <row r="89" spans="1:10" ht="22" customHeight="1">
       <c r="A89" s="14"/>
-      <c r="B89" s="20"/>
-      <c r="C89" s="25"/>
-      <c r="D89" s="25" t="str">
+      <c r="B89" s="18"/>
+      <c r="C89" s="23"/>
+      <c r="D89" s="23" t="str">
         <f>IF(B89="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B89))</f>
         <v/>
       </c>
-      <c r="E89" s="25"/>
-      <c r="F89" s="25" t="str">
+      <c r="E89" s="23"/>
+      <c r="F89" s="23" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="G89" s="28" t="str">
+      <c r="G89" s="26" t="str">
         <f>IF(B89="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B89,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H89" s="28"/>
-      <c r="I89" s="28" t="str">
+      <c r="H89" s="26"/>
+      <c r="I89" s="26" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="J89" s="21"/>
+      <c r="J89" s="19"/>
     </row>
     <row r="90" spans="1:10" ht="22" customHeight="1">
       <c r="A90" s="14"/>
-      <c r="B90" s="20"/>
-      <c r="C90" s="25"/>
-      <c r="D90" s="25" t="str">
+      <c r="B90" s="18"/>
+      <c r="C90" s="23"/>
+      <c r="D90" s="23" t="str">
         <f>IF(B90="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B90))</f>
         <v/>
       </c>
-      <c r="E90" s="25"/>
-      <c r="F90" s="25" t="str">
+      <c r="E90" s="23"/>
+      <c r="F90" s="23" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="G90" s="28" t="str">
+      <c r="G90" s="26" t="str">
         <f>IF(B90="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B90,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H90" s="28"/>
-      <c r="I90" s="28" t="str">
+      <c r="H90" s="26"/>
+      <c r="I90" s="26" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="J90" s="21"/>
+      <c r="J90" s="19"/>
     </row>
     <row r="91" spans="1:10" ht="22" customHeight="1">
       <c r="A91" s="14"/>
-      <c r="B91" s="20"/>
-      <c r="C91" s="25"/>
-      <c r="D91" s="25" t="str">
+      <c r="B91" s="18"/>
+      <c r="C91" s="23"/>
+      <c r="D91" s="23" t="str">
         <f>IF(B91="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B91))</f>
         <v/>
       </c>
-      <c r="E91" s="25"/>
-      <c r="F91" s="25" t="str">
+      <c r="E91" s="23"/>
+      <c r="F91" s="23" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="G91" s="28" t="str">
+      <c r="G91" s="26" t="str">
         <f>IF(B91="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B91,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H91" s="28"/>
-      <c r="I91" s="28" t="str">
+      <c r="H91" s="26"/>
+      <c r="I91" s="26" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="J91" s="21"/>
+      <c r="J91" s="19"/>
     </row>
     <row r="92" spans="1:10" ht="22" customHeight="1">
       <c r="A92" s="14"/>
-      <c r="B92" s="20"/>
-      <c r="C92" s="25"/>
-      <c r="D92" s="25" t="str">
+      <c r="B92" s="18"/>
+      <c r="C92" s="23"/>
+      <c r="D92" s="23" t="str">
         <f>IF(B92="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B92))</f>
         <v/>
       </c>
-      <c r="E92" s="25"/>
-      <c r="F92" s="25" t="str">
+      <c r="E92" s="23"/>
+      <c r="F92" s="23" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="G92" s="28" t="str">
+      <c r="G92" s="26" t="str">
         <f>IF(B92="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B92,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H92" s="28"/>
-      <c r="I92" s="28" t="str">
+      <c r="H92" s="26"/>
+      <c r="I92" s="26" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="J92" s="21"/>
+      <c r="J92" s="19"/>
     </row>
     <row r="93" spans="1:10" ht="22" customHeight="1">
       <c r="A93" s="14"/>
-      <c r="B93" s="20"/>
-      <c r="C93" s="25"/>
-      <c r="D93" s="25" t="str">
+      <c r="B93" s="18"/>
+      <c r="C93" s="23"/>
+      <c r="D93" s="23" t="str">
         <f>IF(B93="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B93))</f>
         <v/>
       </c>
-      <c r="E93" s="25"/>
-      <c r="F93" s="25" t="str">
+      <c r="E93" s="23"/>
+      <c r="F93" s="23" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="G93" s="28" t="str">
+      <c r="G93" s="26" t="str">
         <f>IF(B93="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B93,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H93" s="28"/>
-      <c r="I93" s="28" t="str">
+      <c r="H93" s="26"/>
+      <c r="I93" s="26" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="J93" s="21"/>
+      <c r="J93" s="19"/>
     </row>
     <row r="94" spans="1:10" ht="22" customHeight="1">
       <c r="A94" s="14"/>
-      <c r="B94" s="20"/>
-      <c r="C94" s="25"/>
-      <c r="D94" s="25" t="str">
+      <c r="B94" s="18"/>
+      <c r="C94" s="23"/>
+      <c r="D94" s="23" t="str">
         <f>IF(B94="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B94))</f>
         <v/>
       </c>
-      <c r="E94" s="25"/>
-      <c r="F94" s="25" t="str">
+      <c r="E94" s="23"/>
+      <c r="F94" s="23" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="G94" s="28" t="str">
+      <c r="G94" s="26" t="str">
         <f>IF(B94="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B94,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H94" s="28"/>
-      <c r="I94" s="28" t="str">
+      <c r="H94" s="26"/>
+      <c r="I94" s="26" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="J94" s="21"/>
+      <c r="J94" s="19"/>
     </row>
     <row r="95" spans="1:10" ht="22" customHeight="1">
       <c r="A95" s="14"/>
-      <c r="B95" s="20"/>
-      <c r="C95" s="25"/>
-      <c r="D95" s="25" t="str">
+      <c r="B95" s="18"/>
+      <c r="C95" s="23"/>
+      <c r="D95" s="23" t="str">
         <f>IF(B95="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B95))</f>
         <v/>
       </c>
-      <c r="E95" s="25"/>
-      <c r="F95" s="25" t="str">
+      <c r="E95" s="23"/>
+      <c r="F95" s="23" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="G95" s="28" t="str">
+      <c r="G95" s="26" t="str">
         <f>IF(B95="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B95,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H95" s="28"/>
-      <c r="I95" s="28" t="str">
+      <c r="H95" s="26"/>
+      <c r="I95" s="26" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="J95" s="21"/>
+      <c r="J95" s="19"/>
     </row>
     <row r="96" spans="1:10" ht="22" customHeight="1">
       <c r="A96" s="14"/>
-      <c r="B96" s="20"/>
-      <c r="C96" s="25"/>
-      <c r="D96" s="25" t="str">
+      <c r="B96" s="18"/>
+      <c r="C96" s="23"/>
+      <c r="D96" s="23" t="str">
         <f>IF(B96="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B96))</f>
         <v/>
       </c>
-      <c r="E96" s="25"/>
-      <c r="F96" s="25" t="str">
+      <c r="E96" s="23"/>
+      <c r="F96" s="23" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="G96" s="28" t="str">
+      <c r="G96" s="26" t="str">
         <f>IF(B96="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B96,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H96" s="28"/>
-      <c r="I96" s="28" t="str">
+      <c r="H96" s="26"/>
+      <c r="I96" s="26" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="J96" s="21"/>
+      <c r="J96" s="19"/>
     </row>
     <row r="97" spans="1:10" ht="22" customHeight="1">
       <c r="A97" s="14"/>
-      <c r="B97" s="20"/>
-      <c r="C97" s="25"/>
-      <c r="D97" s="25" t="str">
+      <c r="B97" s="18"/>
+      <c r="C97" s="23"/>
+      <c r="D97" s="23" t="str">
         <f>IF(B97="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B97))</f>
         <v/>
       </c>
-      <c r="E97" s="25"/>
-      <c r="F97" s="25" t="str">
+      <c r="E97" s="23"/>
+      <c r="F97" s="23" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="G97" s="28" t="str">
+      <c r="G97" s="26" t="str">
         <f>IF(B97="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B97,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H97" s="28"/>
-      <c r="I97" s="28" t="str">
+      <c r="H97" s="26"/>
+      <c r="I97" s="26" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="J97" s="21"/>
+      <c r="J97" s="19"/>
     </row>
     <row r="98" spans="1:10" ht="22" customHeight="1">
       <c r="A98" s="14"/>
-      <c r="B98" s="20"/>
-      <c r="C98" s="25"/>
-      <c r="D98" s="25" t="str">
+      <c r="B98" s="18"/>
+      <c r="C98" s="23"/>
+      <c r="D98" s="23" t="str">
         <f>IF(B98="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B98))</f>
         <v/>
       </c>
-      <c r="E98" s="25"/>
-      <c r="F98" s="25" t="str">
+      <c r="E98" s="23"/>
+      <c r="F98" s="23" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="G98" s="28" t="str">
+      <c r="G98" s="26" t="str">
         <f>IF(B98="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B98,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H98" s="28"/>
-      <c r="I98" s="28" t="str">
+      <c r="H98" s="26"/>
+      <c r="I98" s="26" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="J98" s="21"/>
+      <c r="J98" s="19"/>
     </row>
     <row r="99" spans="1:10" ht="22" customHeight="1">
       <c r="A99" s="14"/>
-      <c r="B99" s="20"/>
-      <c r="C99" s="25"/>
-      <c r="D99" s="25" t="str">
+      <c r="B99" s="18"/>
+      <c r="C99" s="23"/>
+      <c r="D99" s="23" t="str">
         <f>IF(B99="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B99))</f>
         <v/>
       </c>
-      <c r="E99" s="25"/>
-      <c r="F99" s="25" t="str">
+      <c r="E99" s="23"/>
+      <c r="F99" s="23" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="G99" s="28" t="str">
+      <c r="G99" s="26" t="str">
         <f>IF(B99="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B99,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H99" s="28"/>
-      <c r="I99" s="28" t="str">
+      <c r="H99" s="26"/>
+      <c r="I99" s="26" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="J99" s="21"/>
+      <c r="J99" s="19"/>
     </row>
     <row r="100" spans="1:10" ht="22" customHeight="1">
       <c r="A100" s="14"/>
-      <c r="B100" s="20"/>
-      <c r="C100" s="25"/>
-      <c r="D100" s="25" t="str">
+      <c r="B100" s="18"/>
+      <c r="C100" s="23"/>
+      <c r="D100" s="23" t="str">
         <f>IF(B100="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B100))</f>
         <v/>
       </c>
-      <c r="E100" s="25"/>
-      <c r="F100" s="25" t="str">
+      <c r="E100" s="23"/>
+      <c r="F100" s="23" t="str">
         <f t="shared" ref="F100:F131" si="6">IF(B100="","",MAX(C100-D100-E100,0))</f>
         <v/>
       </c>
-      <c r="G100" s="28" t="str">
+      <c r="G100" s="26" t="str">
         <f>IF(B100="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B100,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H100" s="28"/>
-      <c r="I100" s="28" t="str">
+      <c r="H100" s="26"/>
+      <c r="I100" s="26" t="str">
         <f t="shared" ref="I100:I131" si="7">IF(B100="","",MAX(G100-H100,0))</f>
         <v/>
       </c>
-      <c r="J100" s="21"/>
+      <c r="J100" s="19"/>
     </row>
     <row r="101" spans="1:10" ht="22" customHeight="1">
       <c r="A101" s="14"/>
-      <c r="B101" s="20"/>
-      <c r="C101" s="25"/>
-      <c r="D101" s="25" t="str">
+      <c r="B101" s="18"/>
+      <c r="C101" s="23"/>
+      <c r="D101" s="23" t="str">
         <f>IF(B101="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B101))</f>
         <v/>
       </c>
-      <c r="E101" s="25"/>
-      <c r="F101" s="25" t="str">
+      <c r="E101" s="23"/>
+      <c r="F101" s="23" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="G101" s="28" t="str">
+      <c r="G101" s="26" t="str">
         <f>IF(B101="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B101,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H101" s="28"/>
-      <c r="I101" s="28" t="str">
+      <c r="H101" s="26"/>
+      <c r="I101" s="26" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="J101" s="21"/>
+      <c r="J101" s="19"/>
     </row>
     <row r="102" spans="1:10" ht="22" customHeight="1">
       <c r="A102" s="14"/>
-      <c r="B102" s="20"/>
-      <c r="C102" s="25"/>
-      <c r="D102" s="25" t="str">
+      <c r="B102" s="18"/>
+      <c r="C102" s="23"/>
+      <c r="D102" s="23" t="str">
         <f>IF(B102="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B102))</f>
         <v/>
       </c>
-      <c r="E102" s="25"/>
-      <c r="F102" s="25" t="str">
+      <c r="E102" s="23"/>
+      <c r="F102" s="23" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="G102" s="28" t="str">
+      <c r="G102" s="26" t="str">
         <f>IF(B102="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B102,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H102" s="28"/>
-      <c r="I102" s="28" t="str">
+      <c r="H102" s="26"/>
+      <c r="I102" s="26" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="J102" s="21"/>
+      <c r="J102" s="19"/>
     </row>
     <row r="103" spans="1:10" ht="22" customHeight="1">
       <c r="A103" s="14"/>
-      <c r="B103" s="20"/>
-      <c r="C103" s="25"/>
-      <c r="D103" s="25" t="str">
+      <c r="B103" s="18"/>
+      <c r="C103" s="23"/>
+      <c r="D103" s="23" t="str">
         <f>IF(B103="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B103))</f>
         <v/>
       </c>
-      <c r="E103" s="25"/>
-      <c r="F103" s="25" t="str">
+      <c r="E103" s="23"/>
+      <c r="F103" s="23" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="G103" s="28" t="str">
+      <c r="G103" s="26" t="str">
         <f>IF(B103="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B103,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H103" s="28"/>
-      <c r="I103" s="28" t="str">
+      <c r="H103" s="26"/>
+      <c r="I103" s="26" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="J103" s="21"/>
+      <c r="J103" s="19"/>
     </row>
     <row r="104" spans="1:10" ht="22" customHeight="1">
       <c r="A104" s="14"/>
-      <c r="B104" s="20"/>
-      <c r="C104" s="25"/>
-      <c r="D104" s="25" t="str">
+      <c r="B104" s="18"/>
+      <c r="C104" s="23"/>
+      <c r="D104" s="23" t="str">
         <f>IF(B104="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B104))</f>
         <v/>
       </c>
-      <c r="E104" s="25"/>
-      <c r="F104" s="25" t="str">
+      <c r="E104" s="23"/>
+      <c r="F104" s="23" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="G104" s="28" t="str">
+      <c r="G104" s="26" t="str">
         <f>IF(B104="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B104,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H104" s="28"/>
-      <c r="I104" s="28" t="str">
+      <c r="H104" s="26"/>
+      <c r="I104" s="26" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="J104" s="21"/>
+      <c r="J104" s="19"/>
     </row>
     <row r="105" spans="1:10" ht="22" customHeight="1">
       <c r="A105" s="14"/>
-      <c r="B105" s="20"/>
-      <c r="C105" s="25"/>
-      <c r="D105" s="25" t="str">
+      <c r="B105" s="18"/>
+      <c r="C105" s="23"/>
+      <c r="D105" s="23" t="str">
         <f>IF(B105="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B105))</f>
         <v/>
       </c>
-      <c r="E105" s="25"/>
-      <c r="F105" s="25" t="str">
+      <c r="E105" s="23"/>
+      <c r="F105" s="23" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="G105" s="28" t="str">
+      <c r="G105" s="26" t="str">
         <f>IF(B105="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B105,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H105" s="28"/>
-      <c r="I105" s="28" t="str">
+      <c r="H105" s="26"/>
+      <c r="I105" s="26" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="J105" s="21"/>
+      <c r="J105" s="19"/>
     </row>
     <row r="106" spans="1:10" ht="22" customHeight="1">
       <c r="A106" s="14"/>
-      <c r="B106" s="20"/>
-      <c r="C106" s="25"/>
-      <c r="D106" s="25" t="str">
+      <c r="B106" s="18"/>
+      <c r="C106" s="23"/>
+      <c r="D106" s="23" t="str">
         <f>IF(B106="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B106))</f>
         <v/>
       </c>
-      <c r="E106" s="25"/>
-      <c r="F106" s="25" t="str">
+      <c r="E106" s="23"/>
+      <c r="F106" s="23" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="G106" s="28" t="str">
+      <c r="G106" s="26" t="str">
         <f>IF(B106="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B106,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H106" s="28"/>
-      <c r="I106" s="28" t="str">
+      <c r="H106" s="26"/>
+      <c r="I106" s="26" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="J106" s="21"/>
+      <c r="J106" s="19"/>
     </row>
     <row r="107" spans="1:10" ht="22" customHeight="1">
       <c r="A107" s="14"/>
-      <c r="B107" s="20"/>
-      <c r="C107" s="25"/>
-      <c r="D107" s="25" t="str">
+      <c r="B107" s="18"/>
+      <c r="C107" s="23"/>
+      <c r="D107" s="23" t="str">
         <f>IF(B107="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B107))</f>
         <v/>
       </c>
-      <c r="E107" s="25"/>
-      <c r="F107" s="25" t="str">
+      <c r="E107" s="23"/>
+      <c r="F107" s="23" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="G107" s="28" t="str">
+      <c r="G107" s="26" t="str">
         <f>IF(B107="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B107,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H107" s="28"/>
-      <c r="I107" s="28" t="str">
+      <c r="H107" s="26"/>
+      <c r="I107" s="26" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="J107" s="21"/>
+      <c r="J107" s="19"/>
     </row>
     <row r="108" spans="1:10" ht="22" customHeight="1">
       <c r="A108" s="14"/>
-      <c r="B108" s="20"/>
-      <c r="C108" s="25"/>
-      <c r="D108" s="25" t="str">
+      <c r="B108" s="18"/>
+      <c r="C108" s="23"/>
+      <c r="D108" s="23" t="str">
         <f>IF(B108="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B108))</f>
         <v/>
       </c>
-      <c r="E108" s="25"/>
-      <c r="F108" s="25" t="str">
+      <c r="E108" s="23"/>
+      <c r="F108" s="23" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="G108" s="28" t="str">
+      <c r="G108" s="26" t="str">
         <f>IF(B108="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B108,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H108" s="28"/>
-      <c r="I108" s="28" t="str">
+      <c r="H108" s="26"/>
+      <c r="I108" s="26" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="J108" s="21"/>
+      <c r="J108" s="19"/>
     </row>
     <row r="109" spans="1:10" ht="22" customHeight="1">
       <c r="A109" s="14"/>
-      <c r="B109" s="20"/>
-      <c r="C109" s="25"/>
-      <c r="D109" s="25" t="str">
+      <c r="B109" s="18"/>
+      <c r="C109" s="23"/>
+      <c r="D109" s="23" t="str">
         <f>IF(B109="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B109))</f>
         <v/>
       </c>
-      <c r="E109" s="25"/>
-      <c r="F109" s="25" t="str">
+      <c r="E109" s="23"/>
+      <c r="F109" s="23" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="G109" s="28" t="str">
+      <c r="G109" s="26" t="str">
         <f>IF(B109="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B109,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H109" s="28"/>
-      <c r="I109" s="28" t="str">
+      <c r="H109" s="26"/>
+      <c r="I109" s="26" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="J109" s="21"/>
+      <c r="J109" s="19"/>
     </row>
     <row r="110" spans="1:10" ht="22" customHeight="1">
       <c r="A110" s="14"/>
-      <c r="B110" s="20"/>
-      <c r="C110" s="25"/>
-      <c r="D110" s="25" t="str">
+      <c r="B110" s="18"/>
+      <c r="C110" s="23"/>
+      <c r="D110" s="23" t="str">
         <f>IF(B110="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B110))</f>
         <v/>
       </c>
-      <c r="E110" s="25"/>
-      <c r="F110" s="25" t="str">
+      <c r="E110" s="23"/>
+      <c r="F110" s="23" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="G110" s="28" t="str">
+      <c r="G110" s="26" t="str">
         <f>IF(B110="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B110,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H110" s="28"/>
-      <c r="I110" s="28" t="str">
+      <c r="H110" s="26"/>
+      <c r="I110" s="26" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="J110" s="21"/>
+      <c r="J110" s="19"/>
     </row>
     <row r="111" spans="1:10" ht="22" customHeight="1">
       <c r="A111" s="14"/>
-      <c r="B111" s="20"/>
-      <c r="C111" s="25"/>
-      <c r="D111" s="25" t="str">
+      <c r="B111" s="18"/>
+      <c r="C111" s="23"/>
+      <c r="D111" s="23" t="str">
         <f>IF(B111="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B111))</f>
         <v/>
       </c>
-      <c r="E111" s="25"/>
-      <c r="F111" s="25" t="str">
+      <c r="E111" s="23"/>
+      <c r="F111" s="23" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="G111" s="28" t="str">
+      <c r="G111" s="26" t="str">
         <f>IF(B111="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B111,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H111" s="28"/>
-      <c r="I111" s="28" t="str">
+      <c r="H111" s="26"/>
+      <c r="I111" s="26" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="J111" s="21"/>
+      <c r="J111" s="19"/>
     </row>
     <row r="112" spans="1:10" ht="22" customHeight="1">
       <c r="A112" s="14"/>
-      <c r="B112" s="20"/>
-      <c r="C112" s="25"/>
-      <c r="D112" s="25" t="str">
+      <c r="B112" s="18"/>
+      <c r="C112" s="23"/>
+      <c r="D112" s="23" t="str">
         <f>IF(B112="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B112))</f>
         <v/>
       </c>
-      <c r="E112" s="25"/>
-      <c r="F112" s="25" t="str">
+      <c r="E112" s="23"/>
+      <c r="F112" s="23" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="G112" s="28" t="str">
+      <c r="G112" s="26" t="str">
         <f>IF(B112="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B112,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H112" s="28"/>
-      <c r="I112" s="28" t="str">
+      <c r="H112" s="26"/>
+      <c r="I112" s="26" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="J112" s="21"/>
+      <c r="J112" s="19"/>
     </row>
     <row r="113" spans="1:10" ht="22" customHeight="1">
       <c r="A113" s="14"/>
-      <c r="B113" s="20"/>
-      <c r="C113" s="25"/>
-      <c r="D113" s="25" t="str">
+      <c r="B113" s="18"/>
+      <c r="C113" s="23"/>
+      <c r="D113" s="23" t="str">
         <f>IF(B113="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B113))</f>
         <v/>
       </c>
-      <c r="E113" s="25"/>
-      <c r="F113" s="25" t="str">
+      <c r="E113" s="23"/>
+      <c r="F113" s="23" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="G113" s="28" t="str">
+      <c r="G113" s="26" t="str">
         <f>IF(B113="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B113,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H113" s="28"/>
-      <c r="I113" s="28" t="str">
+      <c r="H113" s="26"/>
+      <c r="I113" s="26" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="J113" s="21"/>
+      <c r="J113" s="19"/>
     </row>
     <row r="114" spans="1:10" ht="22" customHeight="1">
       <c r="A114" s="14"/>
-      <c r="B114" s="20"/>
-      <c r="C114" s="25"/>
-      <c r="D114" s="25" t="str">
+      <c r="B114" s="18"/>
+      <c r="C114" s="23"/>
+      <c r="D114" s="23" t="str">
         <f>IF(B114="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B114))</f>
         <v/>
       </c>
-      <c r="E114" s="25"/>
-      <c r="F114" s="25" t="str">
+      <c r="E114" s="23"/>
+      <c r="F114" s="23" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="G114" s="28" t="str">
+      <c r="G114" s="26" t="str">
         <f>IF(B114="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B114,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H114" s="28"/>
-      <c r="I114" s="28" t="str">
+      <c r="H114" s="26"/>
+      <c r="I114" s="26" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="J114" s="21"/>
+      <c r="J114" s="19"/>
     </row>
     <row r="115" spans="1:10" ht="22" customHeight="1">
       <c r="A115" s="14"/>
-      <c r="B115" s="20"/>
-      <c r="C115" s="25"/>
-      <c r="D115" s="25" t="str">
+      <c r="B115" s="18"/>
+      <c r="C115" s="23"/>
+      <c r="D115" s="23" t="str">
         <f>IF(B115="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B115))</f>
         <v/>
       </c>
-      <c r="E115" s="25"/>
-      <c r="F115" s="25" t="str">
+      <c r="E115" s="23"/>
+      <c r="F115" s="23" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="G115" s="28" t="str">
+      <c r="G115" s="26" t="str">
         <f>IF(B115="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B115,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H115" s="28"/>
-      <c r="I115" s="28" t="str">
+      <c r="H115" s="26"/>
+      <c r="I115" s="26" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="J115" s="21"/>
+      <c r="J115" s="19"/>
     </row>
     <row r="116" spans="1:10" ht="22" customHeight="1">
       <c r="A116" s="14"/>
-      <c r="B116" s="20"/>
-      <c r="C116" s="25"/>
-      <c r="D116" s="25" t="str">
+      <c r="B116" s="18"/>
+      <c r="C116" s="23"/>
+      <c r="D116" s="23" t="str">
         <f>IF(B116="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B116))</f>
         <v/>
       </c>
-      <c r="E116" s="25"/>
-      <c r="F116" s="25" t="str">
+      <c r="E116" s="23"/>
+      <c r="F116" s="23" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="G116" s="28" t="str">
+      <c r="G116" s="26" t="str">
         <f>IF(B116="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B116,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H116" s="28"/>
-      <c r="I116" s="28" t="str">
+      <c r="H116" s="26"/>
+      <c r="I116" s="26" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="J116" s="21"/>
+      <c r="J116" s="19"/>
     </row>
     <row r="117" spans="1:10" ht="22" customHeight="1">
       <c r="A117" s="14"/>
-      <c r="B117" s="20"/>
-      <c r="C117" s="25"/>
-      <c r="D117" s="25" t="str">
+      <c r="B117" s="18"/>
+      <c r="C117" s="23"/>
+      <c r="D117" s="23" t="str">
         <f>IF(B117="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B117))</f>
         <v/>
       </c>
-      <c r="E117" s="25"/>
-      <c r="F117" s="25" t="str">
+      <c r="E117" s="23"/>
+      <c r="F117" s="23" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="G117" s="28" t="str">
+      <c r="G117" s="26" t="str">
         <f>IF(B117="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B117,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H117" s="28"/>
-      <c r="I117" s="28" t="str">
+      <c r="H117" s="26"/>
+      <c r="I117" s="26" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="J117" s="21"/>
+      <c r="J117" s="19"/>
     </row>
     <row r="118" spans="1:10" ht="22" customHeight="1">
       <c r="A118" s="14"/>
-      <c r="B118" s="20"/>
-      <c r="C118" s="25"/>
-      <c r="D118" s="25" t="str">
+      <c r="B118" s="18"/>
+      <c r="C118" s="23"/>
+      <c r="D118" s="23" t="str">
         <f>IF(B118="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B118))</f>
         <v/>
       </c>
-      <c r="E118" s="25"/>
-      <c r="F118" s="25" t="str">
+      <c r="E118" s="23"/>
+      <c r="F118" s="23" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="G118" s="28" t="str">
+      <c r="G118" s="26" t="str">
         <f>IF(B118="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B118,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H118" s="28"/>
-      <c r="I118" s="28" t="str">
+      <c r="H118" s="26"/>
+      <c r="I118" s="26" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="J118" s="21"/>
+      <c r="J118" s="19"/>
     </row>
     <row r="119" spans="1:10" ht="22" customHeight="1">
       <c r="A119" s="14"/>
-      <c r="B119" s="20"/>
-      <c r="C119" s="25"/>
-      <c r="D119" s="25" t="str">
+      <c r="B119" s="18"/>
+      <c r="C119" s="23"/>
+      <c r="D119" s="23" t="str">
         <f>IF(B119="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B119))</f>
         <v/>
       </c>
-      <c r="E119" s="25"/>
-      <c r="F119" s="25" t="str">
+      <c r="E119" s="23"/>
+      <c r="F119" s="23" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="G119" s="28" t="str">
+      <c r="G119" s="26" t="str">
         <f>IF(B119="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B119,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H119" s="28"/>
-      <c r="I119" s="28" t="str">
+      <c r="H119" s="26"/>
+      <c r="I119" s="26" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="J119" s="21"/>
+      <c r="J119" s="19"/>
     </row>
     <row r="120" spans="1:10" ht="22" customHeight="1">
       <c r="A120" s="14"/>
-      <c r="B120" s="20"/>
-      <c r="C120" s="25"/>
-      <c r="D120" s="25" t="str">
+      <c r="B120" s="18"/>
+      <c r="C120" s="23"/>
+      <c r="D120" s="23" t="str">
         <f>IF(B120="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B120))</f>
         <v/>
       </c>
-      <c r="E120" s="25"/>
-      <c r="F120" s="25" t="str">
+      <c r="E120" s="23"/>
+      <c r="F120" s="23" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="G120" s="28" t="str">
+      <c r="G120" s="26" t="str">
         <f>IF(B120="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B120,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H120" s="28"/>
-      <c r="I120" s="28" t="str">
+      <c r="H120" s="26"/>
+      <c r="I120" s="26" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="J120" s="21"/>
+      <c r="J120" s="19"/>
     </row>
     <row r="121" spans="1:10" ht="22" customHeight="1">
       <c r="A121" s="14"/>
-      <c r="B121" s="20"/>
-      <c r="C121" s="25"/>
-      <c r="D121" s="25" t="str">
+      <c r="B121" s="18"/>
+      <c r="C121" s="23"/>
+      <c r="D121" s="23" t="str">
         <f>IF(B121="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B121))</f>
         <v/>
       </c>
-      <c r="E121" s="25"/>
-      <c r="F121" s="25" t="str">
+      <c r="E121" s="23"/>
+      <c r="F121" s="23" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="G121" s="28" t="str">
+      <c r="G121" s="26" t="str">
         <f>IF(B121="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B121,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H121" s="28"/>
-      <c r="I121" s="28" t="str">
+      <c r="H121" s="26"/>
+      <c r="I121" s="26" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="J121" s="21"/>
+      <c r="J121" s="19"/>
     </row>
     <row r="122" spans="1:10" ht="22" customHeight="1">
       <c r="A122" s="14"/>
-      <c r="B122" s="20"/>
-      <c r="C122" s="25"/>
-      <c r="D122" s="25" t="str">
+      <c r="B122" s="18"/>
+      <c r="C122" s="23"/>
+      <c r="D122" s="23" t="str">
         <f>IF(B122="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B122))</f>
         <v/>
       </c>
-      <c r="E122" s="25"/>
-      <c r="F122" s="25" t="str">
+      <c r="E122" s="23"/>
+      <c r="F122" s="23" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="G122" s="28" t="str">
+      <c r="G122" s="26" t="str">
         <f>IF(B122="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B122,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H122" s="28"/>
-      <c r="I122" s="28" t="str">
+      <c r="H122" s="26"/>
+      <c r="I122" s="26" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="J122" s="21"/>
+      <c r="J122" s="19"/>
     </row>
     <row r="123" spans="1:10" ht="22" customHeight="1">
       <c r="A123" s="14"/>
-      <c r="B123" s="20"/>
-      <c r="C123" s="25"/>
-      <c r="D123" s="25" t="str">
+      <c r="B123" s="18"/>
+      <c r="C123" s="23"/>
+      <c r="D123" s="23" t="str">
         <f>IF(B123="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B123))</f>
         <v/>
       </c>
-      <c r="E123" s="25"/>
-      <c r="F123" s="25" t="str">
+      <c r="E123" s="23"/>
+      <c r="F123" s="23" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="G123" s="28" t="str">
+      <c r="G123" s="26" t="str">
         <f>IF(B123="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B123,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H123" s="28"/>
-      <c r="I123" s="28" t="str">
+      <c r="H123" s="26"/>
+      <c r="I123" s="26" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="J123" s="21"/>
+      <c r="J123" s="19"/>
     </row>
     <row r="124" spans="1:10" ht="22" customHeight="1">
       <c r="A124" s="14"/>
-      <c r="B124" s="20"/>
-      <c r="C124" s="25"/>
-      <c r="D124" s="25" t="str">
+      <c r="B124" s="18"/>
+      <c r="C124" s="23"/>
+      <c r="D124" s="23" t="str">
         <f>IF(B124="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B124))</f>
         <v/>
       </c>
-      <c r="E124" s="25"/>
-      <c r="F124" s="25" t="str">
+      <c r="E124" s="23"/>
+      <c r="F124" s="23" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="G124" s="28" t="str">
+      <c r="G124" s="26" t="str">
         <f>IF(B124="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B124,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H124" s="28"/>
-      <c r="I124" s="28" t="str">
+      <c r="H124" s="26"/>
+      <c r="I124" s="26" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="J124" s="21"/>
+      <c r="J124" s="19"/>
     </row>
     <row r="125" spans="1:10" ht="22" customHeight="1">
       <c r="A125" s="14"/>
-      <c r="B125" s="20"/>
-      <c r="C125" s="25"/>
-      <c r="D125" s="25" t="str">
+      <c r="B125" s="18"/>
+      <c r="C125" s="23"/>
+      <c r="D125" s="23" t="str">
         <f>IF(B125="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B125))</f>
         <v/>
       </c>
-      <c r="E125" s="25"/>
-      <c r="F125" s="25" t="str">
+      <c r="E125" s="23"/>
+      <c r="F125" s="23" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="G125" s="28" t="str">
+      <c r="G125" s="26" t="str">
         <f>IF(B125="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B125,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H125" s="28"/>
-      <c r="I125" s="28" t="str">
+      <c r="H125" s="26"/>
+      <c r="I125" s="26" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="J125" s="21"/>
+      <c r="J125" s="19"/>
     </row>
     <row r="126" spans="1:10" ht="22" customHeight="1">
       <c r="A126" s="14"/>
-      <c r="B126" s="20"/>
-      <c r="C126" s="25"/>
-      <c r="D126" s="25" t="str">
+      <c r="B126" s="18"/>
+      <c r="C126" s="23"/>
+      <c r="D126" s="23" t="str">
         <f>IF(B126="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B126))</f>
         <v/>
       </c>
-      <c r="E126" s="25"/>
-      <c r="F126" s="25" t="str">
+      <c r="E126" s="23"/>
+      <c r="F126" s="23" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="G126" s="28" t="str">
+      <c r="G126" s="26" t="str">
         <f>IF(B126="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B126,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H126" s="28"/>
-      <c r="I126" s="28" t="str">
+      <c r="H126" s="26"/>
+      <c r="I126" s="26" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="J126" s="21"/>
+      <c r="J126" s="19"/>
     </row>
     <row r="127" spans="1:10" ht="22" customHeight="1">
       <c r="A127" s="14"/>
-      <c r="B127" s="20"/>
-      <c r="C127" s="25"/>
-      <c r="D127" s="25" t="str">
+      <c r="B127" s="18"/>
+      <c r="C127" s="23"/>
+      <c r="D127" s="23" t="str">
         <f>IF(B127="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B127))</f>
         <v/>
       </c>
-      <c r="E127" s="25"/>
-      <c r="F127" s="25" t="str">
+      <c r="E127" s="23"/>
+      <c r="F127" s="23" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="G127" s="28" t="str">
+      <c r="G127" s="26" t="str">
         <f>IF(B127="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B127,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H127" s="28"/>
-      <c r="I127" s="28" t="str">
+      <c r="H127" s="26"/>
+      <c r="I127" s="26" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="J127" s="21"/>
+      <c r="J127" s="19"/>
     </row>
     <row r="128" spans="1:10" ht="22" customHeight="1">
       <c r="A128" s="14"/>
-      <c r="B128" s="20"/>
-      <c r="C128" s="25"/>
-      <c r="D128" s="25" t="str">
+      <c r="B128" s="18"/>
+      <c r="C128" s="23"/>
+      <c r="D128" s="23" t="str">
         <f>IF(B128="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B128))</f>
         <v/>
       </c>
-      <c r="E128" s="25"/>
-      <c r="F128" s="25" t="str">
+      <c r="E128" s="23"/>
+      <c r="F128" s="23" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="G128" s="28" t="str">
+      <c r="G128" s="26" t="str">
         <f>IF(B128="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B128,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H128" s="28"/>
-      <c r="I128" s="28" t="str">
+      <c r="H128" s="26"/>
+      <c r="I128" s="26" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="J128" s="21"/>
+      <c r="J128" s="19"/>
     </row>
     <row r="129" spans="1:10" ht="22" customHeight="1">
       <c r="A129" s="14"/>
-      <c r="B129" s="20"/>
-      <c r="C129" s="25"/>
-      <c r="D129" s="25" t="str">
+      <c r="B129" s="18"/>
+      <c r="C129" s="23"/>
+      <c r="D129" s="23" t="str">
         <f>IF(B129="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B129))</f>
         <v/>
       </c>
-      <c r="E129" s="25"/>
-      <c r="F129" s="25" t="str">
+      <c r="E129" s="23"/>
+      <c r="F129" s="23" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="G129" s="28" t="str">
+      <c r="G129" s="26" t="str">
         <f>IF(B129="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B129,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H129" s="28"/>
-      <c r="I129" s="28" t="str">
+      <c r="H129" s="26"/>
+      <c r="I129" s="26" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="J129" s="21"/>
+      <c r="J129" s="19"/>
     </row>
     <row r="130" spans="1:10" ht="22" customHeight="1">
       <c r="A130" s="14"/>
-      <c r="B130" s="20"/>
-      <c r="C130" s="25"/>
-      <c r="D130" s="25" t="str">
+      <c r="B130" s="18"/>
+      <c r="C130" s="23"/>
+      <c r="D130" s="23" t="str">
         <f>IF(B130="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B130))</f>
         <v/>
       </c>
-      <c r="E130" s="25"/>
-      <c r="F130" s="25" t="str">
+      <c r="E130" s="23"/>
+      <c r="F130" s="23" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="G130" s="28" t="str">
+      <c r="G130" s="26" t="str">
         <f>IF(B130="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B130,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H130" s="28"/>
-      <c r="I130" s="28" t="str">
+      <c r="H130" s="26"/>
+      <c r="I130" s="26" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="J130" s="21"/>
+      <c r="J130" s="19"/>
     </row>
     <row r="131" spans="1:10" ht="22" customHeight="1">
       <c r="A131" s="14"/>
-      <c r="B131" s="20"/>
-      <c r="C131" s="25"/>
-      <c r="D131" s="25" t="str">
+      <c r="B131" s="18"/>
+      <c r="C131" s="23"/>
+      <c r="D131" s="23" t="str">
         <f>IF(B131="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B131))</f>
         <v/>
       </c>
-      <c r="E131" s="25"/>
-      <c r="F131" s="25" t="str">
+      <c r="E131" s="23"/>
+      <c r="F131" s="23" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="G131" s="28" t="str">
+      <c r="G131" s="26" t="str">
         <f>IF(B131="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B131,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H131" s="28"/>
-      <c r="I131" s="28" t="str">
+      <c r="H131" s="26"/>
+      <c r="I131" s="26" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="J131" s="21"/>
+      <c r="J131" s="19"/>
     </row>
     <row r="132" spans="1:10" ht="22" customHeight="1">
       <c r="A132" s="14"/>
-      <c r="B132" s="20"/>
-      <c r="C132" s="25"/>
-      <c r="D132" s="25" t="str">
+      <c r="B132" s="18"/>
+      <c r="C132" s="23"/>
+      <c r="D132" s="23" t="str">
         <f>IF(B132="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B132))</f>
         <v/>
       </c>
-      <c r="E132" s="25"/>
-      <c r="F132" s="25" t="str">
+      <c r="E132" s="23"/>
+      <c r="F132" s="23" t="str">
         <f t="shared" ref="F132:F163" si="8">IF(B132="","",MAX(C132-D132-E132,0))</f>
         <v/>
       </c>
-      <c r="G132" s="28" t="str">
+      <c r="G132" s="26" t="str">
         <f>IF(B132="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B132,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H132" s="28"/>
-      <c r="I132" s="28" t="str">
+      <c r="H132" s="26"/>
+      <c r="I132" s="26" t="str">
         <f t="shared" ref="I132:I163" si="9">IF(B132="","",MAX(G132-H132,0))</f>
         <v/>
       </c>
-      <c r="J132" s="21"/>
+      <c r="J132" s="19"/>
     </row>
     <row r="133" spans="1:10" ht="22" customHeight="1">
       <c r="A133" s="14"/>
-      <c r="B133" s="20"/>
-      <c r="C133" s="25"/>
-      <c r="D133" s="25" t="str">
+      <c r="B133" s="18"/>
+      <c r="C133" s="23"/>
+      <c r="D133" s="23" t="str">
         <f>IF(B133="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B133))</f>
         <v/>
       </c>
-      <c r="E133" s="25"/>
-      <c r="F133" s="25" t="str">
+      <c r="E133" s="23"/>
+      <c r="F133" s="23" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="G133" s="28" t="str">
+      <c r="G133" s="26" t="str">
         <f>IF(B133="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B133,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H133" s="28"/>
-      <c r="I133" s="28" t="str">
+      <c r="H133" s="26"/>
+      <c r="I133" s="26" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="J133" s="21"/>
+      <c r="J133" s="19"/>
     </row>
     <row r="134" spans="1:10" ht="22" customHeight="1">
       <c r="A134" s="14"/>
-      <c r="B134" s="20"/>
-      <c r="C134" s="25"/>
-      <c r="D134" s="25" t="str">
+      <c r="B134" s="18"/>
+      <c r="C134" s="23"/>
+      <c r="D134" s="23" t="str">
         <f>IF(B134="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B134))</f>
         <v/>
       </c>
-      <c r="E134" s="25"/>
-      <c r="F134" s="25" t="str">
+      <c r="E134" s="23"/>
+      <c r="F134" s="23" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="G134" s="28" t="str">
+      <c r="G134" s="26" t="str">
         <f>IF(B134="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B134,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H134" s="28"/>
-      <c r="I134" s="28" t="str">
+      <c r="H134" s="26"/>
+      <c r="I134" s="26" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="J134" s="21"/>
+      <c r="J134" s="19"/>
     </row>
     <row r="135" spans="1:10" ht="22" customHeight="1">
       <c r="A135" s="14"/>
-      <c r="B135" s="20"/>
-      <c r="C135" s="25"/>
-      <c r="D135" s="25" t="str">
+      <c r="B135" s="18"/>
+      <c r="C135" s="23"/>
+      <c r="D135" s="23" t="str">
         <f>IF(B135="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B135))</f>
         <v/>
       </c>
-      <c r="E135" s="25"/>
-      <c r="F135" s="25" t="str">
+      <c r="E135" s="23"/>
+      <c r="F135" s="23" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="G135" s="28" t="str">
+      <c r="G135" s="26" t="str">
         <f>IF(B135="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B135,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H135" s="28"/>
-      <c r="I135" s="28" t="str">
+      <c r="H135" s="26"/>
+      <c r="I135" s="26" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="J135" s="21"/>
+      <c r="J135" s="19"/>
     </row>
     <row r="136" spans="1:10" ht="22" customHeight="1">
       <c r="A136" s="14"/>
-      <c r="B136" s="20"/>
-      <c r="C136" s="25"/>
-      <c r="D136" s="25" t="str">
+      <c r="B136" s="18"/>
+      <c r="C136" s="23"/>
+      <c r="D136" s="23" t="str">
         <f>IF(B136="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B136))</f>
         <v/>
       </c>
-      <c r="E136" s="25"/>
-      <c r="F136" s="25" t="str">
+      <c r="E136" s="23"/>
+      <c r="F136" s="23" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="G136" s="28" t="str">
+      <c r="G136" s="26" t="str">
         <f>IF(B136="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B136,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H136" s="28"/>
-      <c r="I136" s="28" t="str">
+      <c r="H136" s="26"/>
+      <c r="I136" s="26" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="J136" s="21"/>
+      <c r="J136" s="19"/>
     </row>
     <row r="137" spans="1:10" ht="22" customHeight="1">
       <c r="A137" s="14"/>
-      <c r="B137" s="20"/>
-      <c r="C137" s="25"/>
-      <c r="D137" s="25" t="str">
+      <c r="B137" s="18"/>
+      <c r="C137" s="23"/>
+      <c r="D137" s="23" t="str">
         <f>IF(B137="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B137))</f>
         <v/>
       </c>
-      <c r="E137" s="25"/>
-      <c r="F137" s="25" t="str">
+      <c r="E137" s="23"/>
+      <c r="F137" s="23" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="G137" s="28" t="str">
+      <c r="G137" s="26" t="str">
         <f>IF(B137="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B137,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H137" s="28"/>
-      <c r="I137" s="28" t="str">
+      <c r="H137" s="26"/>
+      <c r="I137" s="26" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="J137" s="21"/>
+      <c r="J137" s="19"/>
     </row>
     <row r="138" spans="1:10" ht="22" customHeight="1">
       <c r="A138" s="14"/>
-      <c r="B138" s="20"/>
-      <c r="C138" s="25"/>
-      <c r="D138" s="25" t="str">
+      <c r="B138" s="18"/>
+      <c r="C138" s="23"/>
+      <c r="D138" s="23" t="str">
         <f>IF(B138="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B138))</f>
         <v/>
       </c>
-      <c r="E138" s="25"/>
-      <c r="F138" s="25" t="str">
+      <c r="E138" s="23"/>
+      <c r="F138" s="23" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="G138" s="28" t="str">
+      <c r="G138" s="26" t="str">
         <f>IF(B138="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B138,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H138" s="28"/>
-      <c r="I138" s="28" t="str">
+      <c r="H138" s="26"/>
+      <c r="I138" s="26" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="J138" s="21"/>
+      <c r="J138" s="19"/>
     </row>
     <row r="139" spans="1:10" ht="22" customHeight="1">
       <c r="A139" s="14"/>
-      <c r="B139" s="20"/>
-      <c r="C139" s="25"/>
-      <c r="D139" s="25" t="str">
+      <c r="B139" s="18"/>
+      <c r="C139" s="23"/>
+      <c r="D139" s="23" t="str">
         <f>IF(B139="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B139))</f>
         <v/>
       </c>
-      <c r="E139" s="25"/>
-      <c r="F139" s="25" t="str">
+      <c r="E139" s="23"/>
+      <c r="F139" s="23" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="G139" s="28" t="str">
+      <c r="G139" s="26" t="str">
         <f>IF(B139="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B139,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H139" s="28"/>
-      <c r="I139" s="28" t="str">
+      <c r="H139" s="26"/>
+      <c r="I139" s="26" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="J139" s="21"/>
+      <c r="J139" s="19"/>
     </row>
     <row r="140" spans="1:10" ht="22" customHeight="1">
       <c r="A140" s="14"/>
-      <c r="B140" s="20"/>
-      <c r="C140" s="25"/>
-      <c r="D140" s="25" t="str">
+      <c r="B140" s="18"/>
+      <c r="C140" s="23"/>
+      <c r="D140" s="23" t="str">
         <f>IF(B140="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B140))</f>
         <v/>
       </c>
-      <c r="E140" s="25"/>
-      <c r="F140" s="25" t="str">
+      <c r="E140" s="23"/>
+      <c r="F140" s="23" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="G140" s="28" t="str">
+      <c r="G140" s="26" t="str">
         <f>IF(B140="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B140,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H140" s="28"/>
-      <c r="I140" s="28" t="str">
+      <c r="H140" s="26"/>
+      <c r="I140" s="26" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="J140" s="21"/>
+      <c r="J140" s="19"/>
     </row>
     <row r="141" spans="1:10" ht="22" customHeight="1">
       <c r="A141" s="14"/>
-      <c r="B141" s="20"/>
-      <c r="C141" s="25"/>
-      <c r="D141" s="25" t="str">
+      <c r="B141" s="18"/>
+      <c r="C141" s="23"/>
+      <c r="D141" s="23" t="str">
         <f>IF(B141="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B141))</f>
         <v/>
       </c>
-      <c r="E141" s="25"/>
-      <c r="F141" s="25" t="str">
+      <c r="E141" s="23"/>
+      <c r="F141" s="23" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="G141" s="28" t="str">
+      <c r="G141" s="26" t="str">
         <f>IF(B141="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B141,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H141" s="28"/>
-      <c r="I141" s="28" t="str">
+      <c r="H141" s="26"/>
+      <c r="I141" s="26" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="J141" s="21"/>
+      <c r="J141" s="19"/>
     </row>
     <row r="142" spans="1:10" ht="22" customHeight="1">
       <c r="A142" s="14"/>
-      <c r="B142" s="20"/>
-      <c r="C142" s="25"/>
-      <c r="D142" s="25" t="str">
+      <c r="B142" s="18"/>
+      <c r="C142" s="23"/>
+      <c r="D142" s="23" t="str">
         <f>IF(B142="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B142))</f>
         <v/>
       </c>
-      <c r="E142" s="25"/>
-      <c r="F142" s="25" t="str">
+      <c r="E142" s="23"/>
+      <c r="F142" s="23" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="G142" s="28" t="str">
+      <c r="G142" s="26" t="str">
         <f>IF(B142="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B142,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H142" s="28"/>
-      <c r="I142" s="28" t="str">
+      <c r="H142" s="26"/>
+      <c r="I142" s="26" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="J142" s="21"/>
+      <c r="J142" s="19"/>
     </row>
     <row r="143" spans="1:10" ht="22" customHeight="1">
       <c r="A143" s="14"/>
-      <c r="B143" s="20"/>
-      <c r="C143" s="25"/>
-      <c r="D143" s="25" t="str">
+      <c r="B143" s="18"/>
+      <c r="C143" s="23"/>
+      <c r="D143" s="23" t="str">
         <f>IF(B143="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B143))</f>
         <v/>
       </c>
-      <c r="E143" s="25"/>
-      <c r="F143" s="25" t="str">
+      <c r="E143" s="23"/>
+      <c r="F143" s="23" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="G143" s="28" t="str">
+      <c r="G143" s="26" t="str">
         <f>IF(B143="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B143,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H143" s="28"/>
-      <c r="I143" s="28" t="str">
+      <c r="H143" s="26"/>
+      <c r="I143" s="26" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="J143" s="21"/>
+      <c r="J143" s="19"/>
     </row>
     <row r="144" spans="1:10" ht="22" customHeight="1">
       <c r="A144" s="14"/>
-      <c r="B144" s="20"/>
-      <c r="C144" s="25"/>
-      <c r="D144" s="25" t="str">
+      <c r="B144" s="18"/>
+      <c r="C144" s="23"/>
+      <c r="D144" s="23" t="str">
         <f>IF(B144="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B144))</f>
         <v/>
       </c>
-      <c r="E144" s="25"/>
-      <c r="F144" s="25" t="str">
+      <c r="E144" s="23"/>
+      <c r="F144" s="23" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="G144" s="28" t="str">
+      <c r="G144" s="26" t="str">
         <f>IF(B144="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B144,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H144" s="28"/>
-      <c r="I144" s="28" t="str">
+      <c r="H144" s="26"/>
+      <c r="I144" s="26" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="J144" s="21"/>
+      <c r="J144" s="19"/>
     </row>
     <row r="145" spans="1:10" ht="22" customHeight="1">
       <c r="A145" s="14"/>
-      <c r="B145" s="20"/>
-      <c r="C145" s="25"/>
-      <c r="D145" s="25" t="str">
+      <c r="B145" s="18"/>
+      <c r="C145" s="23"/>
+      <c r="D145" s="23" t="str">
         <f>IF(B145="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B145))</f>
         <v/>
       </c>
-      <c r="E145" s="25"/>
-      <c r="F145" s="25" t="str">
+      <c r="E145" s="23"/>
+      <c r="F145" s="23" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="G145" s="28" t="str">
+      <c r="G145" s="26" t="str">
         <f>IF(B145="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B145,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H145" s="28"/>
-      <c r="I145" s="28" t="str">
+      <c r="H145" s="26"/>
+      <c r="I145" s="26" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="J145" s="21"/>
+      <c r="J145" s="19"/>
     </row>
     <row r="146" spans="1:10" ht="22" customHeight="1">
       <c r="A146" s="14"/>
-      <c r="B146" s="20"/>
-      <c r="C146" s="25"/>
-      <c r="D146" s="25" t="str">
+      <c r="B146" s="18"/>
+      <c r="C146" s="23"/>
+      <c r="D146" s="23" t="str">
         <f>IF(B146="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B146))</f>
         <v/>
       </c>
-      <c r="E146" s="25"/>
-      <c r="F146" s="25" t="str">
+      <c r="E146" s="23"/>
+      <c r="F146" s="23" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="G146" s="28" t="str">
+      <c r="G146" s="26" t="str">
         <f>IF(B146="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B146,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H146" s="28"/>
-      <c r="I146" s="28" t="str">
+      <c r="H146" s="26"/>
+      <c r="I146" s="26" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="J146" s="21"/>
+      <c r="J146" s="19"/>
     </row>
     <row r="147" spans="1:10" ht="22" customHeight="1">
       <c r="A147" s="14"/>
-      <c r="B147" s="20"/>
-      <c r="C147" s="25"/>
-      <c r="D147" s="25" t="str">
+      <c r="B147" s="18"/>
+      <c r="C147" s="23"/>
+      <c r="D147" s="23" t="str">
         <f>IF(B147="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B147))</f>
         <v/>
       </c>
-      <c r="E147" s="25"/>
-      <c r="F147" s="25" t="str">
+      <c r="E147" s="23"/>
+      <c r="F147" s="23" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="G147" s="28" t="str">
+      <c r="G147" s="26" t="str">
         <f>IF(B147="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B147,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H147" s="28"/>
-      <c r="I147" s="28" t="str">
+      <c r="H147" s="26"/>
+      <c r="I147" s="26" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="J147" s="21"/>
+      <c r="J147" s="19"/>
     </row>
     <row r="148" spans="1:10" ht="22" customHeight="1">
       <c r="A148" s="14"/>
-      <c r="B148" s="20"/>
-      <c r="C148" s="25"/>
-      <c r="D148" s="25" t="str">
+      <c r="B148" s="18"/>
+      <c r="C148" s="23"/>
+      <c r="D148" s="23" t="str">
         <f>IF(B148="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B148))</f>
         <v/>
       </c>
-      <c r="E148" s="25"/>
-      <c r="F148" s="25" t="str">
+      <c r="E148" s="23"/>
+      <c r="F148" s="23" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="G148" s="28" t="str">
+      <c r="G148" s="26" t="str">
         <f>IF(B148="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B148,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H148" s="28"/>
-      <c r="I148" s="28" t="str">
+      <c r="H148" s="26"/>
+      <c r="I148" s="26" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="J148" s="21"/>
+      <c r="J148" s="19"/>
     </row>
     <row r="149" spans="1:10" ht="22" customHeight="1">
       <c r="A149" s="14"/>
-      <c r="B149" s="20"/>
-      <c r="C149" s="25"/>
-      <c r="D149" s="25" t="str">
+      <c r="B149" s="18"/>
+      <c r="C149" s="23"/>
+      <c r="D149" s="23" t="str">
         <f>IF(B149="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B149))</f>
         <v/>
       </c>
-      <c r="E149" s="25"/>
-      <c r="F149" s="25" t="str">
+      <c r="E149" s="23"/>
+      <c r="F149" s="23" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="G149" s="28" t="str">
+      <c r="G149" s="26" t="str">
         <f>IF(B149="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B149,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H149" s="28"/>
-      <c r="I149" s="28" t="str">
+      <c r="H149" s="26"/>
+      <c r="I149" s="26" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="J149" s="21"/>
+      <c r="J149" s="19"/>
     </row>
     <row r="150" spans="1:10" ht="22" customHeight="1">
       <c r="A150" s="14"/>
-      <c r="B150" s="20"/>
-      <c r="C150" s="25"/>
-      <c r="D150" s="25" t="str">
+      <c r="B150" s="18"/>
+      <c r="C150" s="23"/>
+      <c r="D150" s="23" t="str">
         <f>IF(B150="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B150))</f>
         <v/>
       </c>
-      <c r="E150" s="25"/>
-      <c r="F150" s="25" t="str">
+      <c r="E150" s="23"/>
+      <c r="F150" s="23" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="G150" s="28" t="str">
+      <c r="G150" s="26" t="str">
         <f>IF(B150="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B150,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H150" s="28"/>
-      <c r="I150" s="28" t="str">
+      <c r="H150" s="26"/>
+      <c r="I150" s="26" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="J150" s="21"/>
+      <c r="J150" s="19"/>
     </row>
     <row r="151" spans="1:10" ht="22" customHeight="1">
       <c r="A151" s="14"/>
-      <c r="B151" s="20"/>
-      <c r="C151" s="25"/>
-      <c r="D151" s="25" t="str">
+      <c r="B151" s="18"/>
+      <c r="C151" s="23"/>
+      <c r="D151" s="23" t="str">
         <f>IF(B151="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B151))</f>
         <v/>
       </c>
-      <c r="E151" s="25"/>
-      <c r="F151" s="25" t="str">
+      <c r="E151" s="23"/>
+      <c r="F151" s="23" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="G151" s="28" t="str">
+      <c r="G151" s="26" t="str">
         <f>IF(B151="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B151,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H151" s="28"/>
-      <c r="I151" s="28" t="str">
+      <c r="H151" s="26"/>
+      <c r="I151" s="26" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="J151" s="21"/>
+      <c r="J151" s="19"/>
     </row>
     <row r="152" spans="1:10" ht="22" customHeight="1">
       <c r="A152" s="14"/>
-      <c r="B152" s="20"/>
-      <c r="C152" s="25"/>
-      <c r="D152" s="25" t="str">
+      <c r="B152" s="18"/>
+      <c r="C152" s="23"/>
+      <c r="D152" s="23" t="str">
         <f>IF(B152="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B152))</f>
         <v/>
       </c>
-      <c r="E152" s="25"/>
-      <c r="F152" s="25" t="str">
+      <c r="E152" s="23"/>
+      <c r="F152" s="23" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="G152" s="28" t="str">
+      <c r="G152" s="26" t="str">
         <f>IF(B152="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B152,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H152" s="28"/>
-      <c r="I152" s="28" t="str">
+      <c r="H152" s="26"/>
+      <c r="I152" s="26" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="J152" s="21"/>
+      <c r="J152" s="19"/>
     </row>
     <row r="153" spans="1:10" ht="22" customHeight="1">
       <c r="A153" s="14"/>
-      <c r="B153" s="20"/>
-      <c r="C153" s="25"/>
-      <c r="D153" s="25" t="str">
+      <c r="B153" s="18"/>
+      <c r="C153" s="23"/>
+      <c r="D153" s="23" t="str">
         <f>IF(B153="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B153))</f>
         <v/>
       </c>
-      <c r="E153" s="25"/>
-      <c r="F153" s="25" t="str">
+      <c r="E153" s="23"/>
+      <c r="F153" s="23" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="G153" s="28" t="str">
+      <c r="G153" s="26" t="str">
         <f>IF(B153="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B153,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H153" s="28"/>
-      <c r="I153" s="28" t="str">
+      <c r="H153" s="26"/>
+      <c r="I153" s="26" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="J153" s="21"/>
+      <c r="J153" s="19"/>
     </row>
     <row r="154" spans="1:10" ht="22" customHeight="1">
       <c r="A154" s="14"/>
-      <c r="B154" s="20"/>
-      <c r="C154" s="25"/>
-      <c r="D154" s="25" t="str">
+      <c r="B154" s="18"/>
+      <c r="C154" s="23"/>
+      <c r="D154" s="23" t="str">
         <f>IF(B154="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B154))</f>
         <v/>
       </c>
-      <c r="E154" s="25"/>
-      <c r="F154" s="25" t="str">
+      <c r="E154" s="23"/>
+      <c r="F154" s="23" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="G154" s="28" t="str">
+      <c r="G154" s="26" t="str">
         <f>IF(B154="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B154,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H154" s="28"/>
-      <c r="I154" s="28" t="str">
+      <c r="H154" s="26"/>
+      <c r="I154" s="26" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="J154" s="21"/>
+      <c r="J154" s="19"/>
     </row>
     <row r="155" spans="1:10" ht="22" customHeight="1">
       <c r="A155" s="14"/>
-      <c r="B155" s="20"/>
-      <c r="C155" s="25"/>
-      <c r="D155" s="25" t="str">
+      <c r="B155" s="18"/>
+      <c r="C155" s="23"/>
+      <c r="D155" s="23" t="str">
         <f>IF(B155="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B155))</f>
         <v/>
       </c>
-      <c r="E155" s="25"/>
-      <c r="F155" s="25" t="str">
+      <c r="E155" s="23"/>
+      <c r="F155" s="23" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="G155" s="28" t="str">
+      <c r="G155" s="26" t="str">
         <f>IF(B155="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B155,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H155" s="28"/>
-      <c r="I155" s="28" t="str">
+      <c r="H155" s="26"/>
+      <c r="I155" s="26" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="J155" s="21"/>
+      <c r="J155" s="19"/>
     </row>
     <row r="156" spans="1:10" ht="22" customHeight="1">
       <c r="A156" s="14"/>
-      <c r="B156" s="20"/>
-      <c r="C156" s="25"/>
-      <c r="D156" s="25" t="str">
+      <c r="B156" s="18"/>
+      <c r="C156" s="23"/>
+      <c r="D156" s="23" t="str">
         <f>IF(B156="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B156))</f>
         <v/>
       </c>
-      <c r="E156" s="25"/>
-      <c r="F156" s="25" t="str">
+      <c r="E156" s="23"/>
+      <c r="F156" s="23" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="G156" s="28" t="str">
+      <c r="G156" s="26" t="str">
         <f>IF(B156="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B156,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H156" s="28"/>
-      <c r="I156" s="28" t="str">
+      <c r="H156" s="26"/>
+      <c r="I156" s="26" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="J156" s="21"/>
+      <c r="J156" s="19"/>
     </row>
     <row r="157" spans="1:10" ht="22" customHeight="1">
       <c r="A157" s="14"/>
-      <c r="B157" s="20"/>
-      <c r="C157" s="25"/>
-      <c r="D157" s="25" t="str">
+      <c r="B157" s="18"/>
+      <c r="C157" s="23"/>
+      <c r="D157" s="23" t="str">
         <f>IF(B157="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B157))</f>
         <v/>
       </c>
-      <c r="E157" s="25"/>
-      <c r="F157" s="25" t="str">
+      <c r="E157" s="23"/>
+      <c r="F157" s="23" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="G157" s="28" t="str">
+      <c r="G157" s="26" t="str">
         <f>IF(B157="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B157,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H157" s="28"/>
-      <c r="I157" s="28" t="str">
+      <c r="H157" s="26"/>
+      <c r="I157" s="26" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="J157" s="21"/>
+      <c r="J157" s="19"/>
     </row>
     <row r="158" spans="1:10" ht="22" customHeight="1">
       <c r="A158" s="14"/>
-      <c r="B158" s="20"/>
-      <c r="C158" s="25"/>
-      <c r="D158" s="25" t="str">
+      <c r="B158" s="18"/>
+      <c r="C158" s="23"/>
+      <c r="D158" s="23" t="str">
         <f>IF(B158="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B158))</f>
         <v/>
       </c>
-      <c r="E158" s="25"/>
-      <c r="F158" s="25" t="str">
+      <c r="E158" s="23"/>
+      <c r="F158" s="23" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="G158" s="28" t="str">
+      <c r="G158" s="26" t="str">
         <f>IF(B158="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B158,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H158" s="28"/>
-      <c r="I158" s="28" t="str">
+      <c r="H158" s="26"/>
+      <c r="I158" s="26" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="J158" s="21"/>
+      <c r="J158" s="19"/>
     </row>
     <row r="159" spans="1:10" ht="22" customHeight="1">
       <c r="A159" s="14"/>
-      <c r="B159" s="20"/>
-      <c r="C159" s="25"/>
-      <c r="D159" s="25" t="str">
+      <c r="B159" s="18"/>
+      <c r="C159" s="23"/>
+      <c r="D159" s="23" t="str">
         <f>IF(B159="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B159))</f>
         <v/>
       </c>
-      <c r="E159" s="25"/>
-      <c r="F159" s="25" t="str">
+      <c r="E159" s="23"/>
+      <c r="F159" s="23" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="G159" s="28" t="str">
+      <c r="G159" s="26" t="str">
         <f>IF(B159="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B159,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H159" s="28"/>
-      <c r="I159" s="28" t="str">
+      <c r="H159" s="26"/>
+      <c r="I159" s="26" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="J159" s="21"/>
+      <c r="J159" s="19"/>
     </row>
     <row r="160" spans="1:10" ht="22" customHeight="1">
       <c r="A160" s="14"/>
-      <c r="B160" s="20"/>
-      <c r="C160" s="25"/>
-      <c r="D160" s="25" t="str">
+      <c r="B160" s="18"/>
+      <c r="C160" s="23"/>
+      <c r="D160" s="23" t="str">
         <f>IF(B160="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B160))</f>
         <v/>
       </c>
-      <c r="E160" s="25"/>
-      <c r="F160" s="25" t="str">
+      <c r="E160" s="23"/>
+      <c r="F160" s="23" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="G160" s="28" t="str">
+      <c r="G160" s="26" t="str">
         <f>IF(B160="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B160,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H160" s="28"/>
-      <c r="I160" s="28" t="str">
+      <c r="H160" s="26"/>
+      <c r="I160" s="26" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="J160" s="21"/>
+      <c r="J160" s="19"/>
     </row>
     <row r="161" spans="1:10" ht="22" customHeight="1">
       <c r="A161" s="14"/>
-      <c r="B161" s="20"/>
-      <c r="C161" s="25"/>
-      <c r="D161" s="25" t="str">
+      <c r="B161" s="18"/>
+      <c r="C161" s="23"/>
+      <c r="D161" s="23" t="str">
         <f>IF(B161="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B161))</f>
         <v/>
       </c>
-      <c r="E161" s="25"/>
-      <c r="F161" s="25" t="str">
+      <c r="E161" s="23"/>
+      <c r="F161" s="23" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="G161" s="28" t="str">
+      <c r="G161" s="26" t="str">
         <f>IF(B161="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B161,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H161" s="28"/>
-      <c r="I161" s="28" t="str">
+      <c r="H161" s="26"/>
+      <c r="I161" s="26" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="J161" s="21"/>
+      <c r="J161" s="19"/>
     </row>
     <row r="162" spans="1:10" ht="22" customHeight="1">
       <c r="A162" s="14"/>
-      <c r="B162" s="20"/>
-      <c r="C162" s="25"/>
-      <c r="D162" s="25" t="str">
+      <c r="B162" s="18"/>
+      <c r="C162" s="23"/>
+      <c r="D162" s="23" t="str">
         <f>IF(B162="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B162))</f>
         <v/>
       </c>
-      <c r="E162" s="25"/>
-      <c r="F162" s="25" t="str">
+      <c r="E162" s="23"/>
+      <c r="F162" s="23" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="G162" s="28" t="str">
+      <c r="G162" s="26" t="str">
         <f>IF(B162="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B162,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H162" s="28"/>
-      <c r="I162" s="28" t="str">
+      <c r="H162" s="26"/>
+      <c r="I162" s="26" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="J162" s="21"/>
+      <c r="J162" s="19"/>
     </row>
     <row r="163" spans="1:10" ht="22" customHeight="1">
       <c r="A163" s="14"/>
-      <c r="B163" s="20"/>
-      <c r="C163" s="25"/>
-      <c r="D163" s="25" t="str">
+      <c r="B163" s="18"/>
+      <c r="C163" s="23"/>
+      <c r="D163" s="23" t="str">
         <f>IF(B163="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B163))</f>
         <v/>
       </c>
-      <c r="E163" s="25"/>
-      <c r="F163" s="25" t="str">
+      <c r="E163" s="23"/>
+      <c r="F163" s="23" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="G163" s="28" t="str">
+      <c r="G163" s="26" t="str">
         <f>IF(B163="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B163,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H163" s="28"/>
-      <c r="I163" s="28" t="str">
+      <c r="H163" s="26"/>
+      <c r="I163" s="26" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="J163" s="21"/>
+      <c r="J163" s="19"/>
     </row>
     <row r="164" spans="1:10" ht="22" customHeight="1">
       <c r="A164" s="14"/>
-      <c r="B164" s="20"/>
-      <c r="C164" s="25"/>
-      <c r="D164" s="25" t="str">
+      <c r="B164" s="18"/>
+      <c r="C164" s="23"/>
+      <c r="D164" s="23" t="str">
         <f>IF(B164="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B164))</f>
         <v/>
       </c>
-      <c r="E164" s="25"/>
-      <c r="F164" s="25" t="str">
+      <c r="E164" s="23"/>
+      <c r="F164" s="23" t="str">
         <f t="shared" ref="F164:F195" si="10">IF(B164="","",MAX(C164-D164-E164,0))</f>
         <v/>
       </c>
-      <c r="G164" s="28" t="str">
+      <c r="G164" s="26" t="str">
         <f>IF(B164="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B164,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H164" s="28"/>
-      <c r="I164" s="28" t="str">
+      <c r="H164" s="26"/>
+      <c r="I164" s="26" t="str">
         <f t="shared" ref="I164:I195" si="11">IF(B164="","",MAX(G164-H164,0))</f>
         <v/>
       </c>
-      <c r="J164" s="21"/>
+      <c r="J164" s="19"/>
     </row>
     <row r="165" spans="1:10" ht="22" customHeight="1">
       <c r="A165" s="14"/>
-      <c r="B165" s="20"/>
-      <c r="C165" s="25"/>
-      <c r="D165" s="25" t="str">
+      <c r="B165" s="18"/>
+      <c r="C165" s="23"/>
+      <c r="D165" s="23" t="str">
         <f>IF(B165="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B165))</f>
         <v/>
       </c>
-      <c r="E165" s="25"/>
-      <c r="F165" s="25" t="str">
+      <c r="E165" s="23"/>
+      <c r="F165" s="23" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="G165" s="28" t="str">
+      <c r="G165" s="26" t="str">
         <f>IF(B165="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B165,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H165" s="28"/>
-      <c r="I165" s="28" t="str">
+      <c r="H165" s="26"/>
+      <c r="I165" s="26" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J165" s="21"/>
+      <c r="J165" s="19"/>
     </row>
     <row r="166" spans="1:10" ht="22" customHeight="1">
       <c r="A166" s="14"/>
-      <c r="B166" s="20"/>
-      <c r="C166" s="25"/>
-      <c r="D166" s="25" t="str">
+      <c r="B166" s="18"/>
+      <c r="C166" s="23"/>
+      <c r="D166" s="23" t="str">
         <f>IF(B166="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B166))</f>
         <v/>
       </c>
-      <c r="E166" s="25"/>
-      <c r="F166" s="25" t="str">
+      <c r="E166" s="23"/>
+      <c r="F166" s="23" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="G166" s="28" t="str">
+      <c r="G166" s="26" t="str">
         <f>IF(B166="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B166,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H166" s="28"/>
-      <c r="I166" s="28" t="str">
+      <c r="H166" s="26"/>
+      <c r="I166" s="26" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J166" s="21"/>
+      <c r="J166" s="19"/>
     </row>
     <row r="167" spans="1:10" ht="22" customHeight="1">
       <c r="A167" s="14"/>
-      <c r="B167" s="20"/>
-      <c r="C167" s="25"/>
-      <c r="D167" s="25" t="str">
+      <c r="B167" s="18"/>
+      <c r="C167" s="23"/>
+      <c r="D167" s="23" t="str">
         <f>IF(B167="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B167))</f>
         <v/>
       </c>
-      <c r="E167" s="25"/>
-      <c r="F167" s="25" t="str">
+      <c r="E167" s="23"/>
+      <c r="F167" s="23" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="G167" s="28" t="str">
+      <c r="G167" s="26" t="str">
         <f>IF(B167="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B167,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H167" s="28"/>
-      <c r="I167" s="28" t="str">
+      <c r="H167" s="26"/>
+      <c r="I167" s="26" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J167" s="21"/>
+      <c r="J167" s="19"/>
     </row>
     <row r="168" spans="1:10" ht="22" customHeight="1">
       <c r="A168" s="14"/>
-      <c r="B168" s="20"/>
-      <c r="C168" s="25"/>
-      <c r="D168" s="25" t="str">
+      <c r="B168" s="18"/>
+      <c r="C168" s="23"/>
+      <c r="D168" s="23" t="str">
         <f>IF(B168="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B168))</f>
         <v/>
       </c>
-      <c r="E168" s="25"/>
-      <c r="F168" s="25" t="str">
+      <c r="E168" s="23"/>
+      <c r="F168" s="23" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="G168" s="28" t="str">
+      <c r="G168" s="26" t="str">
         <f>IF(B168="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B168,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H168" s="28"/>
-      <c r="I168" s="28" t="str">
+      <c r="H168" s="26"/>
+      <c r="I168" s="26" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J168" s="21"/>
+      <c r="J168" s="19"/>
     </row>
     <row r="169" spans="1:10" ht="22" customHeight="1">
       <c r="A169" s="14"/>
-      <c r="B169" s="20"/>
-      <c r="C169" s="25"/>
-      <c r="D169" s="25" t="str">
+      <c r="B169" s="18"/>
+      <c r="C169" s="23"/>
+      <c r="D169" s="23" t="str">
         <f>IF(B169="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B169))</f>
         <v/>
       </c>
-      <c r="E169" s="25"/>
-      <c r="F169" s="25" t="str">
+      <c r="E169" s="23"/>
+      <c r="F169" s="23" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="G169" s="28" t="str">
+      <c r="G169" s="26" t="str">
         <f>IF(B169="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B169,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H169" s="28"/>
-      <c r="I169" s="28" t="str">
+      <c r="H169" s="26"/>
+      <c r="I169" s="26" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J169" s="21"/>
+      <c r="J169" s="19"/>
     </row>
     <row r="170" spans="1:10" ht="22" customHeight="1">
       <c r="A170" s="14"/>
-      <c r="B170" s="20"/>
-      <c r="C170" s="25"/>
-      <c r="D170" s="25" t="str">
+      <c r="B170" s="18"/>
+      <c r="C170" s="23"/>
+      <c r="D170" s="23" t="str">
         <f>IF(B170="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B170))</f>
         <v/>
       </c>
-      <c r="E170" s="25"/>
-      <c r="F170" s="25" t="str">
+      <c r="E170" s="23"/>
+      <c r="F170" s="23" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="G170" s="28" t="str">
+      <c r="G170" s="26" t="str">
         <f>IF(B170="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B170,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H170" s="28"/>
-      <c r="I170" s="28" t="str">
+      <c r="H170" s="26"/>
+      <c r="I170" s="26" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J170" s="21"/>
+      <c r="J170" s="19"/>
     </row>
     <row r="171" spans="1:10" ht="22" customHeight="1">
       <c r="A171" s="14"/>
-      <c r="B171" s="20"/>
-      <c r="C171" s="25"/>
-      <c r="D171" s="25" t="str">
+      <c r="B171" s="18"/>
+      <c r="C171" s="23"/>
+      <c r="D171" s="23" t="str">
         <f>IF(B171="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B171))</f>
         <v/>
       </c>
-      <c r="E171" s="25"/>
-      <c r="F171" s="25" t="str">
+      <c r="E171" s="23"/>
+      <c r="F171" s="23" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="G171" s="28" t="str">
+      <c r="G171" s="26" t="str">
         <f>IF(B171="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B171,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H171" s="28"/>
-      <c r="I171" s="28" t="str">
+      <c r="H171" s="26"/>
+      <c r="I171" s="26" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J171" s="21"/>
+      <c r="J171" s="19"/>
     </row>
     <row r="172" spans="1:10" ht="22" customHeight="1">
       <c r="A172" s="14"/>
-      <c r="B172" s="20"/>
-      <c r="C172" s="25"/>
-      <c r="D172" s="25" t="str">
+      <c r="B172" s="18"/>
+      <c r="C172" s="23"/>
+      <c r="D172" s="23" t="str">
         <f>IF(B172="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B172))</f>
         <v/>
       </c>
-      <c r="E172" s="25"/>
-      <c r="F172" s="25" t="str">
+      <c r="E172" s="23"/>
+      <c r="F172" s="23" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="G172" s="28" t="str">
+      <c r="G172" s="26" t="str">
         <f>IF(B172="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B172,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H172" s="28"/>
-      <c r="I172" s="28" t="str">
+      <c r="H172" s="26"/>
+      <c r="I172" s="26" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J172" s="21"/>
+      <c r="J172" s="19"/>
     </row>
     <row r="173" spans="1:10" ht="22" customHeight="1">
       <c r="A173" s="14"/>
-      <c r="B173" s="20"/>
-      <c r="C173" s="25"/>
-      <c r="D173" s="25" t="str">
+      <c r="B173" s="18"/>
+      <c r="C173" s="23"/>
+      <c r="D173" s="23" t="str">
         <f>IF(B173="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B173))</f>
         <v/>
       </c>
-      <c r="E173" s="25"/>
-      <c r="F173" s="25" t="str">
+      <c r="E173" s="23"/>
+      <c r="F173" s="23" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="G173" s="28" t="str">
+      <c r="G173" s="26" t="str">
         <f>IF(B173="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B173,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H173" s="28"/>
-      <c r="I173" s="28" t="str">
+      <c r="H173" s="26"/>
+      <c r="I173" s="26" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J173" s="21"/>
+      <c r="J173" s="19"/>
     </row>
     <row r="174" spans="1:10" ht="22" customHeight="1">
       <c r="A174" s="14"/>
-      <c r="B174" s="20"/>
-      <c r="C174" s="25"/>
-      <c r="D174" s="25" t="str">
+      <c r="B174" s="18"/>
+      <c r="C174" s="23"/>
+      <c r="D174" s="23" t="str">
         <f>IF(B174="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B174))</f>
         <v/>
       </c>
-      <c r="E174" s="25"/>
-      <c r="F174" s="25" t="str">
+      <c r="E174" s="23"/>
+      <c r="F174" s="23" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="G174" s="28" t="str">
+      <c r="G174" s="26" t="str">
         <f>IF(B174="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B174,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H174" s="28"/>
-      <c r="I174" s="28" t="str">
+      <c r="H174" s="26"/>
+      <c r="I174" s="26" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J174" s="21"/>
+      <c r="J174" s="19"/>
     </row>
     <row r="175" spans="1:10" ht="22" customHeight="1">
       <c r="A175" s="14"/>
-      <c r="B175" s="20"/>
-      <c r="C175" s="25"/>
-      <c r="D175" s="25" t="str">
+      <c r="B175" s="18"/>
+      <c r="C175" s="23"/>
+      <c r="D175" s="23" t="str">
         <f>IF(B175="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B175))</f>
         <v/>
       </c>
-      <c r="E175" s="25"/>
-      <c r="F175" s="25" t="str">
+      <c r="E175" s="23"/>
+      <c r="F175" s="23" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="G175" s="28" t="str">
+      <c r="G175" s="26" t="str">
         <f>IF(B175="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B175,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H175" s="28"/>
-      <c r="I175" s="28" t="str">
+      <c r="H175" s="26"/>
+      <c r="I175" s="26" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J175" s="21"/>
+      <c r="J175" s="19"/>
     </row>
     <row r="176" spans="1:10" ht="22" customHeight="1">
       <c r="A176" s="14"/>
-      <c r="B176" s="20"/>
-      <c r="C176" s="25"/>
-      <c r="D176" s="25" t="str">
+      <c r="B176" s="18"/>
+      <c r="C176" s="23"/>
+      <c r="D176" s="23" t="str">
         <f>IF(B176="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B176))</f>
         <v/>
       </c>
-      <c r="E176" s="25"/>
-      <c r="F176" s="25" t="str">
+      <c r="E176" s="23"/>
+      <c r="F176" s="23" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="G176" s="28" t="str">
+      <c r="G176" s="26" t="str">
         <f>IF(B176="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B176,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H176" s="28"/>
-      <c r="I176" s="28" t="str">
+      <c r="H176" s="26"/>
+      <c r="I176" s="26" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J176" s="21"/>
+      <c r="J176" s="19"/>
     </row>
     <row r="177" spans="1:10" ht="22" customHeight="1">
       <c r="A177" s="14"/>
-      <c r="B177" s="20"/>
-      <c r="C177" s="25"/>
-      <c r="D177" s="25" t="str">
+      <c r="B177" s="18"/>
+      <c r="C177" s="23"/>
+      <c r="D177" s="23" t="str">
         <f>IF(B177="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B177))</f>
         <v/>
       </c>
-      <c r="E177" s="25"/>
-      <c r="F177" s="25" t="str">
+      <c r="E177" s="23"/>
+      <c r="F177" s="23" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="G177" s="28" t="str">
+      <c r="G177" s="26" t="str">
         <f>IF(B177="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B177,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H177" s="28"/>
-      <c r="I177" s="28" t="str">
+      <c r="H177" s="26"/>
+      <c r="I177" s="26" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J177" s="21"/>
+      <c r="J177" s="19"/>
     </row>
     <row r="178" spans="1:10" ht="22" customHeight="1">
       <c r="A178" s="14"/>
-      <c r="B178" s="20"/>
-      <c r="C178" s="25"/>
-      <c r="D178" s="25" t="str">
+      <c r="B178" s="18"/>
+      <c r="C178" s="23"/>
+      <c r="D178" s="23" t="str">
         <f>IF(B178="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B178))</f>
         <v/>
       </c>
-      <c r="E178" s="25"/>
-      <c r="F178" s="25" t="str">
+      <c r="E178" s="23"/>
+      <c r="F178" s="23" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="G178" s="28" t="str">
+      <c r="G178" s="26" t="str">
         <f>IF(B178="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B178,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H178" s="28"/>
-      <c r="I178" s="28" t="str">
+      <c r="H178" s="26"/>
+      <c r="I178" s="26" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J178" s="21"/>
+      <c r="J178" s="19"/>
     </row>
     <row r="179" spans="1:10" ht="22" customHeight="1">
       <c r="A179" s="14"/>
-      <c r="B179" s="20"/>
-      <c r="C179" s="25"/>
-      <c r="D179" s="25" t="str">
+      <c r="B179" s="18"/>
+      <c r="C179" s="23"/>
+      <c r="D179" s="23" t="str">
         <f>IF(B179="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B179))</f>
         <v/>
       </c>
-      <c r="E179" s="25"/>
-      <c r="F179" s="25" t="str">
+      <c r="E179" s="23"/>
+      <c r="F179" s="23" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="G179" s="28" t="str">
+      <c r="G179" s="26" t="str">
         <f>IF(B179="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B179,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H179" s="28"/>
-      <c r="I179" s="28" t="str">
+      <c r="H179" s="26"/>
+      <c r="I179" s="26" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J179" s="21"/>
+      <c r="J179" s="19"/>
     </row>
     <row r="180" spans="1:10" ht="22" customHeight="1">
       <c r="A180" s="14"/>
-      <c r="B180" s="20"/>
-      <c r="C180" s="25"/>
-      <c r="D180" s="25" t="str">
+      <c r="B180" s="18"/>
+      <c r="C180" s="23"/>
+      <c r="D180" s="23" t="str">
         <f>IF(B180="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B180))</f>
         <v/>
       </c>
-      <c r="E180" s="25"/>
-      <c r="F180" s="25" t="str">
+      <c r="E180" s="23"/>
+      <c r="F180" s="23" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="G180" s="28" t="str">
+      <c r="G180" s="26" t="str">
         <f>IF(B180="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B180,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H180" s="28"/>
-      <c r="I180" s="28" t="str">
+      <c r="H180" s="26"/>
+      <c r="I180" s="26" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J180" s="21"/>
+      <c r="J180" s="19"/>
     </row>
     <row r="181" spans="1:10" ht="22" customHeight="1">
       <c r="A181" s="14"/>
-      <c r="B181" s="20"/>
-      <c r="C181" s="25"/>
-      <c r="D181" s="25" t="str">
+      <c r="B181" s="18"/>
+      <c r="C181" s="23"/>
+      <c r="D181" s="23" t="str">
         <f>IF(B181="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B181))</f>
         <v/>
       </c>
-      <c r="E181" s="25"/>
-      <c r="F181" s="25" t="str">
+      <c r="E181" s="23"/>
+      <c r="F181" s="23" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="G181" s="28" t="str">
+      <c r="G181" s="26" t="str">
         <f>IF(B181="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B181,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H181" s="28"/>
-      <c r="I181" s="28" t="str">
+      <c r="H181" s="26"/>
+      <c r="I181" s="26" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J181" s="21"/>
+      <c r="J181" s="19"/>
     </row>
     <row r="182" spans="1:10" ht="22" customHeight="1">
       <c r="A182" s="14"/>
-      <c r="B182" s="20"/>
-      <c r="C182" s="25"/>
-      <c r="D182" s="25" t="str">
+      <c r="B182" s="18"/>
+      <c r="C182" s="23"/>
+      <c r="D182" s="23" t="str">
         <f>IF(B182="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B182))</f>
         <v/>
       </c>
-      <c r="E182" s="25"/>
-      <c r="F182" s="25" t="str">
+      <c r="E182" s="23"/>
+      <c r="F182" s="23" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="G182" s="28" t="str">
+      <c r="G182" s="26" t="str">
         <f>IF(B182="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B182,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H182" s="28"/>
-      <c r="I182" s="28" t="str">
+      <c r="H182" s="26"/>
+      <c r="I182" s="26" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J182" s="21"/>
+      <c r="J182" s="19"/>
     </row>
     <row r="183" spans="1:10" ht="22" customHeight="1">
       <c r="A183" s="14"/>
-      <c r="B183" s="20"/>
-      <c r="C183" s="25"/>
-      <c r="D183" s="25" t="str">
+      <c r="B183" s="18"/>
+      <c r="C183" s="23"/>
+      <c r="D183" s="23" t="str">
         <f>IF(B183="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B183))</f>
         <v/>
       </c>
-      <c r="E183" s="25"/>
-      <c r="F183" s="25" t="str">
+      <c r="E183" s="23"/>
+      <c r="F183" s="23" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="G183" s="28" t="str">
+      <c r="G183" s="26" t="str">
         <f>IF(B183="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B183,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H183" s="28"/>
-      <c r="I183" s="28" t="str">
+      <c r="H183" s="26"/>
+      <c r="I183" s="26" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J183" s="21"/>
+      <c r="J183" s="19"/>
     </row>
     <row r="184" spans="1:10" ht="22" customHeight="1">
       <c r="A184" s="14"/>
-      <c r="B184" s="20"/>
-      <c r="C184" s="25"/>
-      <c r="D184" s="25" t="str">
+      <c r="B184" s="18"/>
+      <c r="C184" s="23"/>
+      <c r="D184" s="23" t="str">
         <f>IF(B184="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B184))</f>
         <v/>
       </c>
-      <c r="E184" s="25"/>
-      <c r="F184" s="25" t="str">
+      <c r="E184" s="23"/>
+      <c r="F184" s="23" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="G184" s="28" t="str">
+      <c r="G184" s="26" t="str">
         <f>IF(B184="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B184,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H184" s="28"/>
-      <c r="I184" s="28" t="str">
+      <c r="H184" s="26"/>
+      <c r="I184" s="26" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J184" s="21"/>
+      <c r="J184" s="19"/>
     </row>
     <row r="185" spans="1:10" ht="22" customHeight="1">
       <c r="A185" s="14"/>
-      <c r="B185" s="20"/>
-      <c r="C185" s="25"/>
-      <c r="D185" s="25" t="str">
+      <c r="B185" s="18"/>
+      <c r="C185" s="23"/>
+      <c r="D185" s="23" t="str">
         <f>IF(B185="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B185))</f>
         <v/>
       </c>
-      <c r="E185" s="25"/>
-      <c r="F185" s="25" t="str">
+      <c r="E185" s="23"/>
+      <c r="F185" s="23" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="G185" s="28" t="str">
+      <c r="G185" s="26" t="str">
         <f>IF(B185="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B185,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H185" s="28"/>
-      <c r="I185" s="28" t="str">
+      <c r="H185" s="26"/>
+      <c r="I185" s="26" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J185" s="21"/>
+      <c r="J185" s="19"/>
     </row>
     <row r="186" spans="1:10" ht="22" customHeight="1">
       <c r="A186" s="14"/>
-      <c r="B186" s="20"/>
-      <c r="C186" s="25"/>
-      <c r="D186" s="25" t="str">
+      <c r="B186" s="18"/>
+      <c r="C186" s="23"/>
+      <c r="D186" s="23" t="str">
         <f>IF(B186="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B186))</f>
         <v/>
       </c>
-      <c r="E186" s="25"/>
-      <c r="F186" s="25" t="str">
+      <c r="E186" s="23"/>
+      <c r="F186" s="23" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="G186" s="28" t="str">
+      <c r="G186" s="26" t="str">
         <f>IF(B186="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B186,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H186" s="28"/>
-      <c r="I186" s="28" t="str">
+      <c r="H186" s="26"/>
+      <c r="I186" s="26" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J186" s="21"/>
+      <c r="J186" s="19"/>
     </row>
     <row r="187" spans="1:10" ht="22" customHeight="1">
       <c r="A187" s="14"/>
-      <c r="B187" s="20"/>
-      <c r="C187" s="25"/>
-      <c r="D187" s="25" t="str">
+      <c r="B187" s="18"/>
+      <c r="C187" s="23"/>
+      <c r="D187" s="23" t="str">
         <f>IF(B187="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B187))</f>
         <v/>
       </c>
-      <c r="E187" s="25"/>
-      <c r="F187" s="25" t="str">
+      <c r="E187" s="23"/>
+      <c r="F187" s="23" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="G187" s="28" t="str">
+      <c r="G187" s="26" t="str">
         <f>IF(B187="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B187,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H187" s="28"/>
-      <c r="I187" s="28" t="str">
+      <c r="H187" s="26"/>
+      <c r="I187" s="26" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J187" s="21"/>
+      <c r="J187" s="19"/>
     </row>
     <row r="188" spans="1:10" ht="22" customHeight="1">
       <c r="A188" s="14"/>
-      <c r="B188" s="20"/>
-      <c r="C188" s="25"/>
-      <c r="D188" s="25" t="str">
+      <c r="B188" s="18"/>
+      <c r="C188" s="23"/>
+      <c r="D188" s="23" t="str">
         <f>IF(B188="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B188))</f>
         <v/>
       </c>
-      <c r="E188" s="25"/>
-      <c r="F188" s="25" t="str">
+      <c r="E188" s="23"/>
+      <c r="F188" s="23" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="G188" s="28" t="str">
+      <c r="G188" s="26" t="str">
         <f>IF(B188="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B188,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H188" s="28"/>
-      <c r="I188" s="28" t="str">
+      <c r="H188" s="26"/>
+      <c r="I188" s="26" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J188" s="21"/>
+      <c r="J188" s="19"/>
     </row>
     <row r="189" spans="1:10" ht="22" customHeight="1">
       <c r="A189" s="14"/>
-      <c r="B189" s="20"/>
-      <c r="C189" s="25"/>
-      <c r="D189" s="25" t="str">
+      <c r="B189" s="18"/>
+      <c r="C189" s="23"/>
+      <c r="D189" s="23" t="str">
         <f>IF(B189="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B189))</f>
         <v/>
       </c>
-      <c r="E189" s="25"/>
-      <c r="F189" s="25" t="str">
+      <c r="E189" s="23"/>
+      <c r="F189" s="23" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="G189" s="28" t="str">
+      <c r="G189" s="26" t="str">
         <f>IF(B189="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B189,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H189" s="28"/>
-      <c r="I189" s="28" t="str">
+      <c r="H189" s="26"/>
+      <c r="I189" s="26" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J189" s="21"/>
+      <c r="J189" s="19"/>
     </row>
     <row r="190" spans="1:10" ht="22" customHeight="1">
       <c r="A190" s="14"/>
-      <c r="B190" s="20"/>
-      <c r="C190" s="25"/>
-      <c r="D190" s="25" t="str">
+      <c r="B190" s="18"/>
+      <c r="C190" s="23"/>
+      <c r="D190" s="23" t="str">
         <f>IF(B190="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B190))</f>
         <v/>
       </c>
-      <c r="E190" s="25"/>
-      <c r="F190" s="25" t="str">
+      <c r="E190" s="23"/>
+      <c r="F190" s="23" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="G190" s="28" t="str">
+      <c r="G190" s="26" t="str">
         <f>IF(B190="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B190,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H190" s="28"/>
-      <c r="I190" s="28" t="str">
+      <c r="H190" s="26"/>
+      <c r="I190" s="26" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J190" s="21"/>
+      <c r="J190" s="19"/>
     </row>
     <row r="191" spans="1:10" ht="22" customHeight="1">
       <c r="A191" s="14"/>
-      <c r="B191" s="20"/>
-      <c r="C191" s="25"/>
-      <c r="D191" s="25" t="str">
+      <c r="B191" s="18"/>
+      <c r="C191" s="23"/>
+      <c r="D191" s="23" t="str">
         <f>IF(B191="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B191))</f>
         <v/>
       </c>
-      <c r="E191" s="25"/>
-      <c r="F191" s="25" t="str">
+      <c r="E191" s="23"/>
+      <c r="F191" s="23" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="G191" s="28" t="str">
+      <c r="G191" s="26" t="str">
         <f>IF(B191="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B191,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H191" s="28"/>
-      <c r="I191" s="28" t="str">
+      <c r="H191" s="26"/>
+      <c r="I191" s="26" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J191" s="21"/>
+      <c r="J191" s="19"/>
     </row>
     <row r="192" spans="1:10" ht="22" customHeight="1">
       <c r="A192" s="14"/>
-      <c r="B192" s="20"/>
-      <c r="C192" s="25"/>
-      <c r="D192" s="25" t="str">
+      <c r="B192" s="18"/>
+      <c r="C192" s="23"/>
+      <c r="D192" s="23" t="str">
         <f>IF(B192="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B192))</f>
         <v/>
       </c>
-      <c r="E192" s="25"/>
-      <c r="F192" s="25" t="str">
+      <c r="E192" s="23"/>
+      <c r="F192" s="23" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="G192" s="28" t="str">
+      <c r="G192" s="26" t="str">
         <f>IF(B192="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B192,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H192" s="28"/>
-      <c r="I192" s="28" t="str">
+      <c r="H192" s="26"/>
+      <c r="I192" s="26" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J192" s="21"/>
+      <c r="J192" s="19"/>
     </row>
     <row r="193" spans="1:10" ht="22" customHeight="1">
       <c r="A193" s="14"/>
-      <c r="B193" s="20"/>
-      <c r="C193" s="25"/>
-      <c r="D193" s="25" t="str">
+      <c r="B193" s="18"/>
+      <c r="C193" s="23"/>
+      <c r="D193" s="23" t="str">
         <f>IF(B193="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B193))</f>
         <v/>
       </c>
-      <c r="E193" s="25"/>
-      <c r="F193" s="25" t="str">
+      <c r="E193" s="23"/>
+      <c r="F193" s="23" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="G193" s="28" t="str">
+      <c r="G193" s="26" t="str">
         <f>IF(B193="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B193,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H193" s="28"/>
-      <c r="I193" s="28" t="str">
+      <c r="H193" s="26"/>
+      <c r="I193" s="26" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J193" s="21"/>
+      <c r="J193" s="19"/>
     </row>
     <row r="194" spans="1:10" ht="22" customHeight="1">
       <c r="A194" s="14"/>
-      <c r="B194" s="20"/>
-      <c r="C194" s="25"/>
-      <c r="D194" s="25" t="str">
+      <c r="B194" s="18"/>
+      <c r="C194" s="23"/>
+      <c r="D194" s="23" t="str">
         <f>IF(B194="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B194))</f>
         <v/>
       </c>
-      <c r="E194" s="25"/>
-      <c r="F194" s="25" t="str">
+      <c r="E194" s="23"/>
+      <c r="F194" s="23" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="G194" s="28" t="str">
+      <c r="G194" s="26" t="str">
         <f>IF(B194="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B194,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H194" s="28"/>
-      <c r="I194" s="28" t="str">
+      <c r="H194" s="26"/>
+      <c r="I194" s="26" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J194" s="21"/>
+      <c r="J194" s="19"/>
     </row>
     <row r="195" spans="1:10" ht="22" customHeight="1">
       <c r="A195" s="14"/>
-      <c r="B195" s="20"/>
-      <c r="C195" s="25"/>
-      <c r="D195" s="25" t="str">
+      <c r="B195" s="18"/>
+      <c r="C195" s="23"/>
+      <c r="D195" s="23" t="str">
         <f>IF(B195="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B195))</f>
         <v/>
       </c>
-      <c r="E195" s="25"/>
-      <c r="F195" s="25" t="str">
+      <c r="E195" s="23"/>
+      <c r="F195" s="23" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="G195" s="28" t="str">
+      <c r="G195" s="26" t="str">
         <f>IF(B195="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B195,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H195" s="28"/>
-      <c r="I195" s="28" t="str">
+      <c r="H195" s="26"/>
+      <c r="I195" s="26" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J195" s="21"/>
+      <c r="J195" s="19"/>
     </row>
     <row r="196" spans="1:10" ht="22" customHeight="1">
       <c r="A196" s="14"/>
-      <c r="B196" s="20"/>
-      <c r="C196" s="25"/>
-      <c r="D196" s="25" t="str">
+      <c r="B196" s="18"/>
+      <c r="C196" s="23"/>
+      <c r="D196" s="23" t="str">
         <f>IF(B196="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B196))</f>
         <v/>
       </c>
-      <c r="E196" s="25"/>
-      <c r="F196" s="25" t="str">
+      <c r="E196" s="23"/>
+      <c r="F196" s="23" t="str">
         <f t="shared" ref="F196:F203" si="12">IF(B196="","",MAX(C196-D196-E196,0))</f>
         <v/>
       </c>
-      <c r="G196" s="28" t="str">
+      <c r="G196" s="26" t="str">
         <f>IF(B196="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B196,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H196" s="28"/>
-      <c r="I196" s="28" t="str">
+      <c r="H196" s="26"/>
+      <c r="I196" s="26" t="str">
         <f t="shared" ref="I196:I203" si="13">IF(B196="","",MAX(G196-H196,0))</f>
         <v/>
       </c>
-      <c r="J196" s="21"/>
+      <c r="J196" s="19"/>
     </row>
     <row r="197" spans="1:10" ht="22" customHeight="1">
       <c r="A197" s="14"/>
-      <c r="B197" s="20"/>
-      <c r="C197" s="25"/>
-      <c r="D197" s="25" t="str">
+      <c r="B197" s="18"/>
+      <c r="C197" s="23"/>
+      <c r="D197" s="23" t="str">
         <f>IF(B197="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B197))</f>
         <v/>
       </c>
-      <c r="E197" s="25"/>
-      <c r="F197" s="25" t="str">
+      <c r="E197" s="23"/>
+      <c r="F197" s="23" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="G197" s="28" t="str">
+      <c r="G197" s="26" t="str">
         <f>IF(B197="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B197,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H197" s="28"/>
-      <c r="I197" s="28" t="str">
+      <c r="H197" s="26"/>
+      <c r="I197" s="26" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="J197" s="21"/>
+      <c r="J197" s="19"/>
     </row>
     <row r="198" spans="1:10" ht="22" customHeight="1">
       <c r="A198" s="14"/>
-      <c r="B198" s="20"/>
-      <c r="C198" s="25"/>
-      <c r="D198" s="25" t="str">
+      <c r="B198" s="18"/>
+      <c r="C198" s="23"/>
+      <c r="D198" s="23" t="str">
         <f>IF(B198="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B198))</f>
         <v/>
       </c>
-      <c r="E198" s="25"/>
-      <c r="F198" s="25" t="str">
+      <c r="E198" s="23"/>
+      <c r="F198" s="23" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="G198" s="28" t="str">
+      <c r="G198" s="26" t="str">
         <f>IF(B198="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B198,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H198" s="28"/>
-      <c r="I198" s="28" t="str">
+      <c r="H198" s="26"/>
+      <c r="I198" s="26" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="J198" s="21"/>
+      <c r="J198" s="19"/>
     </row>
     <row r="199" spans="1:10" ht="22" customHeight="1">
       <c r="A199" s="14"/>
-      <c r="B199" s="20"/>
-      <c r="C199" s="25"/>
-      <c r="D199" s="25" t="str">
+      <c r="B199" s="18"/>
+      <c r="C199" s="23"/>
+      <c r="D199" s="23" t="str">
         <f>IF(B199="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B199))</f>
         <v/>
       </c>
-      <c r="E199" s="25"/>
-      <c r="F199" s="25" t="str">
+      <c r="E199" s="23"/>
+      <c r="F199" s="23" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="G199" s="28" t="str">
+      <c r="G199" s="26" t="str">
         <f>IF(B199="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B199,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H199" s="28"/>
-      <c r="I199" s="28" t="str">
+      <c r="H199" s="26"/>
+      <c r="I199" s="26" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="J199" s="21"/>
+      <c r="J199" s="19"/>
     </row>
     <row r="200" spans="1:10" ht="22" customHeight="1">
       <c r="A200" s="14"/>
-      <c r="B200" s="20"/>
-      <c r="C200" s="25"/>
-      <c r="D200" s="25" t="str">
+      <c r="B200" s="18"/>
+      <c r="C200" s="23"/>
+      <c r="D200" s="23" t="str">
         <f>IF(B200="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B200))</f>
         <v/>
       </c>
-      <c r="E200" s="25"/>
-      <c r="F200" s="25" t="str">
+      <c r="E200" s="23"/>
+      <c r="F200" s="23" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="G200" s="28" t="str">
+      <c r="G200" s="26" t="str">
         <f>IF(B200="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B200,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H200" s="28"/>
-      <c r="I200" s="28" t="str">
+      <c r="H200" s="26"/>
+      <c r="I200" s="26" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="J200" s="21"/>
+      <c r="J200" s="19"/>
     </row>
     <row r="201" spans="1:10" ht="22" customHeight="1">
       <c r="A201" s="14"/>
-      <c r="B201" s="20"/>
-      <c r="C201" s="25"/>
-      <c r="D201" s="25" t="str">
+      <c r="B201" s="18"/>
+      <c r="C201" s="23"/>
+      <c r="D201" s="23" t="str">
         <f>IF(B201="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B201))</f>
         <v/>
       </c>
-      <c r="E201" s="25"/>
-      <c r="F201" s="25" t="str">
+      <c r="E201" s="23"/>
+      <c r="F201" s="23" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="G201" s="28" t="str">
+      <c r="G201" s="26" t="str">
         <f>IF(B201="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B201,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H201" s="28"/>
-      <c r="I201" s="28" t="str">
+      <c r="H201" s="26"/>
+      <c r="I201" s="26" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="J201" s="21"/>
+      <c r="J201" s="19"/>
     </row>
     <row r="202" spans="1:10" ht="22" customHeight="1">
       <c r="A202" s="14"/>
-      <c r="B202" s="20"/>
-      <c r="C202" s="25"/>
-      <c r="D202" s="25" t="str">
+      <c r="B202" s="18"/>
+      <c r="C202" s="23"/>
+      <c r="D202" s="23" t="str">
         <f>IF(B202="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B202))</f>
         <v/>
       </c>
-      <c r="E202" s="25"/>
-      <c r="F202" s="25" t="str">
+      <c r="E202" s="23"/>
+      <c r="F202" s="23" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="G202" s="28" t="str">
+      <c r="G202" s="26" t="str">
         <f>IF(B202="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B202,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H202" s="28"/>
-      <c r="I202" s="28" t="str">
+      <c r="H202" s="26"/>
+      <c r="I202" s="26" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="J202" s="21"/>
+      <c r="J202" s="19"/>
     </row>
     <row r="203" spans="1:10" ht="22" customHeight="1">
       <c r="A203" s="14"/>
-      <c r="B203" s="22"/>
-      <c r="C203" s="26"/>
-      <c r="D203" s="26" t="str">
+      <c r="B203" s="20"/>
+      <c r="C203" s="24"/>
+      <c r="D203" s="24" t="str">
         <f>IF(B203="","",SUMIFS(Vendite_Patch!$D$4:$D$303,Vendite_Patch!$L$4:$L$303,B203))</f>
         <v/>
       </c>
-      <c r="E203" s="26"/>
-      <c r="F203" s="26" t="str">
+      <c r="E203" s="24"/>
+      <c r="F203" s="24" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="G203" s="29" t="str">
+      <c r="G203" s="27" t="str">
         <f>IF(B203="","",SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$L$4:$L$303,B203,Vendite_Patch!$I$4:$I$303,"Sì"))</f>
         <v/>
       </c>
-      <c r="H203" s="29"/>
-      <c r="I203" s="29" t="str">
+      <c r="H203" s="27"/>
+      <c r="I203" s="27" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="J203" s="23"/>
+      <c r="J203" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -7759,7 +7921,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:C103"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="27" customWidth="1"/>
@@ -7767,808 +7929,808 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="27" customHeight="1">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="40" t="s">
         <v>218</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
     </row>
     <row r="2" spans="1:3" ht="38" customHeight="1">
-      <c r="A2" s="49" t="s">
+      <c r="A2" s="41" t="s">
         <v>219</v>
       </c>
-      <c r="B2" s="49"/>
-      <c r="C2" s="49"/>
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
     </row>
     <row r="3" spans="1:3" ht="28" customHeight="1">
-      <c r="A3" s="31" t="s">
+      <c r="A3" s="29" t="s">
         <v>220</v>
       </c>
-      <c r="B3" s="31" t="s">
+      <c r="B3" s="29" t="s">
         <v>93</v>
       </c>
-      <c r="C3" s="31" t="s">
+      <c r="C3" s="29" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="22" customHeight="1">
-      <c r="A4" s="16" t="s">
+      <c r="A4" s="42" t="s">
         <v>221</v>
       </c>
-      <c r="B4" s="17" t="str">
+      <c r="B4" s="43" t="str">
         <f>Persone_Quote!B4</f>
         <v>Capodanno</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="44" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="22" customHeight="1">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="45" t="s">
         <v>221</v>
       </c>
-      <c r="B5" s="20" t="str">
+      <c r="B5" s="46" t="str">
         <f>Persone_Quote!B5</f>
         <v>Caggia</v>
       </c>
-      <c r="C5" s="21" t="s">
+      <c r="C5" s="47" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="22" customHeight="1">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="45" t="s">
         <v>221</v>
       </c>
-      <c r="B6" s="20" t="str">
+      <c r="B6" s="46" t="str">
         <f>Persone_Quote!B6</f>
         <v>Marchesani</v>
       </c>
-      <c r="C6" s="21" t="s">
+      <c r="C6" s="47" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="22" customHeight="1">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="45" t="s">
         <v>221</v>
       </c>
-      <c r="B7" s="20" t="str">
+      <c r="B7" s="46" t="str">
         <f>Persone_Quote!B7</f>
         <v>Zubenko</v>
       </c>
-      <c r="C7" s="21" t="s">
+      <c r="C7" s="47" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="22" customHeight="1">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="45" t="s">
         <v>221</v>
       </c>
-      <c r="B8" s="20" t="str">
+      <c r="B8" s="46" t="str">
         <f>Persone_Quote!B8</f>
         <v>Losito</v>
       </c>
-      <c r="C8" s="21" t="s">
+      <c r="C8" s="47" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="22" customHeight="1">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="45" t="s">
         <v>221</v>
       </c>
-      <c r="B9" s="20" t="str">
+      <c r="B9" s="46" t="str">
         <f>Persone_Quote!B9</f>
         <v>Di Stefano</v>
       </c>
-      <c r="C9" s="21" t="s">
+      <c r="C9" s="47" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="22" customHeight="1">
-      <c r="A10" s="19" t="s">
+      <c r="A10" s="45" t="s">
         <v>221</v>
       </c>
-      <c r="B10" s="20" t="str">
+      <c r="B10" s="46" t="str">
         <f>Persone_Quote!B10</f>
         <v>Palladino</v>
       </c>
-      <c r="C10" s="21" t="s">
+      <c r="C10" s="47" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="22" customHeight="1">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="45" t="s">
         <v>221</v>
       </c>
-      <c r="B11" s="20" t="str">
+      <c r="B11" s="46" t="str">
         <f>Persone_Quote!B11</f>
         <v>Locorotondo</v>
       </c>
-      <c r="C11" s="21" t="s">
+      <c r="C11" s="47" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="22" customHeight="1">
-      <c r="A12" s="19" t="s">
+      <c r="A12" s="45" t="s">
         <v>221</v>
       </c>
-      <c r="B12" s="20" t="str">
+      <c r="B12" s="46" t="str">
         <f>Persone_Quote!B12</f>
         <v>Pertosa</v>
       </c>
-      <c r="C12" s="21" t="s">
+      <c r="C12" s="47" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="22" customHeight="1">
-      <c r="A13" s="19" t="s">
+      <c r="A13" s="45" t="s">
         <v>221</v>
       </c>
-      <c r="B13" s="20" t="str">
+      <c r="B13" s="46" t="str">
         <f>Persone_Quote!B13</f>
         <v>Ottaiano</v>
       </c>
-      <c r="C13" s="21" t="s">
+      <c r="C13" s="47" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="22" customHeight="1">
-      <c r="A14" s="19" t="s">
+      <c r="A14" s="45" t="s">
         <v>221</v>
       </c>
-      <c r="B14" s="20" t="str">
+      <c r="B14" s="46" t="str">
         <f>Persone_Quote!B14</f>
         <v>Fragnito</v>
       </c>
-      <c r="C14" s="21" t="s">
+      <c r="C14" s="47" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="22" customHeight="1">
-      <c r="A15" s="19" t="s">
+      <c r="A15" s="45" t="s">
         <v>221</v>
       </c>
-      <c r="B15" s="20" t="str">
+      <c r="B15" s="46" t="str">
         <f>Persone_Quote!B15</f>
         <v>Murolo</v>
       </c>
-      <c r="C15" s="21" t="s">
+      <c r="C15" s="47" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="22" customHeight="1">
-      <c r="A16" s="19" t="s">
+      <c r="A16" s="45" t="s">
         <v>221</v>
       </c>
-      <c r="B16" s="20" t="str">
+      <c r="B16" s="46" t="str">
         <f>Persone_Quote!B16</f>
         <v>Palma</v>
       </c>
-      <c r="C16" s="21" t="s">
+      <c r="C16" s="47" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="22" customHeight="1">
-      <c r="A17" s="19" t="s">
+      <c r="A17" s="45" t="s">
         <v>221</v>
       </c>
-      <c r="B17" s="20" t="str">
+      <c r="B17" s="46" t="str">
         <f>Persone_Quote!B17</f>
         <v>Babele</v>
       </c>
-      <c r="C17" s="21" t="s">
+      <c r="C17" s="47" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="22" customHeight="1">
-      <c r="A18" s="19" t="s">
+      <c r="A18" s="45" t="s">
         <v>221</v>
       </c>
-      <c r="B18" s="20" t="str">
+      <c r="B18" s="46" t="str">
         <f>Persone_Quote!B18</f>
         <v>Torrente</v>
       </c>
-      <c r="C18" s="21" t="s">
+      <c r="C18" s="47" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="22" customHeight="1">
-      <c r="A19" s="32" t="s">
+      <c r="A19" s="48" t="s">
         <v>223</v>
       </c>
-      <c r="B19" s="33" t="s">
+      <c r="B19" s="49" t="s">
         <v>133</v>
       </c>
-      <c r="C19" s="34"/>
+      <c r="C19" s="50"/>
     </row>
     <row r="20" spans="1:3" ht="22" customHeight="1">
-      <c r="A20" s="32" t="s">
+      <c r="A20" s="48" t="s">
         <v>223</v>
       </c>
-      <c r="B20" s="33" t="s">
+      <c r="B20" s="49" t="s">
         <v>157</v>
       </c>
-      <c r="C20" s="34"/>
+      <c r="C20" s="50"/>
     </row>
     <row r="21" spans="1:3" ht="22" customHeight="1">
-      <c r="A21" s="32" t="s">
+      <c r="A21" s="48" t="s">
         <v>223</v>
       </c>
-      <c r="B21" s="33"/>
-      <c r="C21" s="34"/>
+      <c r="B21" s="49"/>
+      <c r="C21" s="50"/>
     </row>
     <row r="22" spans="1:3" ht="22" customHeight="1">
-      <c r="A22" s="32" t="s">
+      <c r="A22" s="48" t="s">
         <v>223</v>
       </c>
-      <c r="B22" s="33"/>
-      <c r="C22" s="34"/>
+      <c r="B22" s="49"/>
+      <c r="C22" s="50"/>
     </row>
     <row r="23" spans="1:3" ht="22" customHeight="1">
-      <c r="A23" s="32" t="s">
+      <c r="A23" s="48" t="s">
         <v>223</v>
       </c>
-      <c r="B23" s="33"/>
-      <c r="C23" s="34"/>
+      <c r="B23" s="49"/>
+      <c r="C23" s="50"/>
     </row>
     <row r="24" spans="1:3" ht="22" customHeight="1">
-      <c r="A24" s="32" t="s">
+      <c r="A24" s="48" t="s">
         <v>223</v>
       </c>
-      <c r="B24" s="33"/>
-      <c r="C24" s="34"/>
+      <c r="B24" s="49"/>
+      <c r="C24" s="50"/>
     </row>
     <row r="25" spans="1:3" ht="22" customHeight="1">
-      <c r="A25" s="32" t="s">
+      <c r="A25" s="48" t="s">
         <v>223</v>
       </c>
-      <c r="B25" s="33"/>
-      <c r="C25" s="34"/>
+      <c r="B25" s="49"/>
+      <c r="C25" s="50"/>
     </row>
     <row r="26" spans="1:3" ht="22" customHeight="1">
-      <c r="A26" s="32" t="s">
+      <c r="A26" s="48" t="s">
         <v>223</v>
       </c>
-      <c r="B26" s="33"/>
-      <c r="C26" s="34"/>
+      <c r="B26" s="49"/>
+      <c r="C26" s="50"/>
     </row>
     <row r="27" spans="1:3" ht="22" customHeight="1">
-      <c r="A27" s="32" t="s">
+      <c r="A27" s="48" t="s">
         <v>223</v>
       </c>
-      <c r="B27" s="33"/>
-      <c r="C27" s="34"/>
+      <c r="B27" s="49"/>
+      <c r="C27" s="50"/>
     </row>
     <row r="28" spans="1:3" ht="22" customHeight="1">
-      <c r="A28" s="32" t="s">
+      <c r="A28" s="48" t="s">
         <v>223</v>
       </c>
-      <c r="B28" s="33"/>
-      <c r="C28" s="34"/>
+      <c r="B28" s="49"/>
+      <c r="C28" s="50"/>
     </row>
     <row r="29" spans="1:3" ht="22" customHeight="1">
-      <c r="A29" s="32" t="s">
+      <c r="A29" s="48" t="s">
         <v>223</v>
       </c>
-      <c r="B29" s="33"/>
-      <c r="C29" s="34"/>
+      <c r="B29" s="49"/>
+      <c r="C29" s="50"/>
     </row>
     <row r="30" spans="1:3" ht="22" customHeight="1">
-      <c r="A30" s="32" t="s">
+      <c r="A30" s="48" t="s">
         <v>223</v>
       </c>
-      <c r="B30" s="33"/>
-      <c r="C30" s="34"/>
+      <c r="B30" s="49"/>
+      <c r="C30" s="50"/>
     </row>
     <row r="31" spans="1:3" ht="22" customHeight="1">
-      <c r="A31" s="32" t="s">
+      <c r="A31" s="48" t="s">
         <v>223</v>
       </c>
-      <c r="B31" s="33"/>
-      <c r="C31" s="34"/>
+      <c r="B31" s="49"/>
+      <c r="C31" s="50"/>
     </row>
     <row r="32" spans="1:3" ht="22" customHeight="1">
-      <c r="A32" s="32" t="s">
+      <c r="A32" s="48" t="s">
         <v>223</v>
       </c>
-      <c r="B32" s="33"/>
-      <c r="C32" s="34"/>
+      <c r="B32" s="49"/>
+      <c r="C32" s="50"/>
     </row>
     <row r="33" spans="1:3" ht="22" customHeight="1">
-      <c r="A33" s="32" t="s">
+      <c r="A33" s="48" t="s">
         <v>223</v>
       </c>
-      <c r="B33" s="33"/>
-      <c r="C33" s="34"/>
+      <c r="B33" s="49"/>
+      <c r="C33" s="50"/>
     </row>
     <row r="34" spans="1:3" ht="22" customHeight="1">
-      <c r="A34" s="32" t="s">
+      <c r="A34" s="48" t="s">
         <v>223</v>
       </c>
-      <c r="B34" s="33"/>
-      <c r="C34" s="34"/>
+      <c r="B34" s="49"/>
+      <c r="C34" s="50"/>
     </row>
     <row r="35" spans="1:3" ht="22" customHeight="1">
-      <c r="A35" s="32" t="s">
+      <c r="A35" s="48" t="s">
         <v>223</v>
       </c>
-      <c r="B35" s="33"/>
-      <c r="C35" s="34"/>
+      <c r="B35" s="49"/>
+      <c r="C35" s="50"/>
     </row>
     <row r="36" spans="1:3" ht="22" customHeight="1">
-      <c r="A36" s="32" t="s">
+      <c r="A36" s="48" t="s">
         <v>223</v>
       </c>
-      <c r="B36" s="33"/>
-      <c r="C36" s="34"/>
+      <c r="B36" s="49"/>
+      <c r="C36" s="50"/>
     </row>
     <row r="37" spans="1:3" ht="22" customHeight="1">
-      <c r="A37" s="32" t="s">
+      <c r="A37" s="48" t="s">
         <v>223</v>
       </c>
-      <c r="B37" s="33"/>
-      <c r="C37" s="34"/>
+      <c r="B37" s="49"/>
+      <c r="C37" s="50"/>
     </row>
     <row r="38" spans="1:3" ht="22" customHeight="1">
-      <c r="A38" s="32" t="s">
+      <c r="A38" s="48" t="s">
         <v>223</v>
       </c>
-      <c r="B38" s="33"/>
-      <c r="C38" s="34"/>
+      <c r="B38" s="49"/>
+      <c r="C38" s="50"/>
     </row>
     <row r="39" spans="1:3" ht="22" customHeight="1">
-      <c r="A39" s="32" t="s">
+      <c r="A39" s="48" t="s">
         <v>223</v>
       </c>
-      <c r="B39" s="33"/>
-      <c r="C39" s="34"/>
+      <c r="B39" s="49"/>
+      <c r="C39" s="50"/>
     </row>
     <row r="40" spans="1:3" ht="22" customHeight="1">
-      <c r="A40" s="32" t="s">
+      <c r="A40" s="48" t="s">
         <v>223</v>
       </c>
-      <c r="B40" s="33"/>
-      <c r="C40" s="34"/>
+      <c r="B40" s="49"/>
+      <c r="C40" s="50"/>
     </row>
     <row r="41" spans="1:3" ht="22" customHeight="1">
-      <c r="A41" s="32" t="s">
+      <c r="A41" s="48" t="s">
         <v>223</v>
       </c>
-      <c r="B41" s="33"/>
-      <c r="C41" s="34"/>
+      <c r="B41" s="49"/>
+      <c r="C41" s="50"/>
     </row>
     <row r="42" spans="1:3" ht="22" customHeight="1">
-      <c r="A42" s="32" t="s">
+      <c r="A42" s="48" t="s">
         <v>223</v>
       </c>
-      <c r="B42" s="33"/>
-      <c r="C42" s="34"/>
+      <c r="B42" s="49"/>
+      <c r="C42" s="50"/>
     </row>
     <row r="43" spans="1:3" ht="22" customHeight="1">
-      <c r="A43" s="32" t="s">
+      <c r="A43" s="48" t="s">
         <v>223</v>
       </c>
-      <c r="B43" s="33"/>
-      <c r="C43" s="34"/>
+      <c r="B43" s="49"/>
+      <c r="C43" s="50"/>
     </row>
     <row r="44" spans="1:3" ht="22" customHeight="1">
-      <c r="A44" s="32" t="s">
+      <c r="A44" s="48" t="s">
         <v>223</v>
       </c>
-      <c r="B44" s="33"/>
-      <c r="C44" s="34"/>
+      <c r="B44" s="49"/>
+      <c r="C44" s="50"/>
     </row>
     <row r="45" spans="1:3" ht="22" customHeight="1">
-      <c r="A45" s="32" t="s">
+      <c r="A45" s="48" t="s">
         <v>223</v>
       </c>
-      <c r="B45" s="33"/>
-      <c r="C45" s="34"/>
+      <c r="B45" s="49"/>
+      <c r="C45" s="50"/>
     </row>
     <row r="46" spans="1:3" ht="22" customHeight="1">
-      <c r="A46" s="32" t="s">
+      <c r="A46" s="48" t="s">
         <v>223</v>
       </c>
-      <c r="B46" s="33"/>
-      <c r="C46" s="34"/>
+      <c r="B46" s="49"/>
+      <c r="C46" s="50"/>
     </row>
     <row r="47" spans="1:3" ht="22" customHeight="1">
-      <c r="A47" s="32" t="s">
+      <c r="A47" s="48" t="s">
         <v>223</v>
       </c>
-      <c r="B47" s="33"/>
-      <c r="C47" s="34"/>
+      <c r="B47" s="49"/>
+      <c r="C47" s="50"/>
     </row>
     <row r="48" spans="1:3" ht="22" customHeight="1">
-      <c r="A48" s="32" t="s">
+      <c r="A48" s="48" t="s">
         <v>223</v>
       </c>
-      <c r="B48" s="33"/>
-      <c r="C48" s="34"/>
+      <c r="B48" s="49"/>
+      <c r="C48" s="50"/>
     </row>
     <row r="49" spans="1:3" ht="22" customHeight="1">
-      <c r="A49" s="32" t="s">
+      <c r="A49" s="48" t="s">
         <v>223</v>
       </c>
-      <c r="B49" s="33"/>
-      <c r="C49" s="34"/>
+      <c r="B49" s="49"/>
+      <c r="C49" s="50"/>
     </row>
     <row r="50" spans="1:3" ht="22" customHeight="1">
-      <c r="A50" s="32" t="s">
+      <c r="A50" s="48" t="s">
         <v>223</v>
       </c>
-      <c r="B50" s="33"/>
-      <c r="C50" s="34"/>
+      <c r="B50" s="49"/>
+      <c r="C50" s="50"/>
     </row>
     <row r="51" spans="1:3" ht="22" customHeight="1">
-      <c r="A51" s="32" t="s">
+      <c r="A51" s="48" t="s">
         <v>223</v>
       </c>
-      <c r="B51" s="33"/>
-      <c r="C51" s="34"/>
+      <c r="B51" s="49"/>
+      <c r="C51" s="50"/>
     </row>
     <row r="52" spans="1:3" ht="22" customHeight="1">
-      <c r="A52" s="32" t="s">
+      <c r="A52" s="48" t="s">
         <v>223</v>
       </c>
-      <c r="B52" s="33"/>
-      <c r="C52" s="34"/>
+      <c r="B52" s="49"/>
+      <c r="C52" s="50"/>
     </row>
     <row r="53" spans="1:3" ht="22" customHeight="1">
-      <c r="A53" s="32" t="s">
+      <c r="A53" s="48" t="s">
         <v>223</v>
       </c>
-      <c r="B53" s="33"/>
-      <c r="C53" s="34"/>
+      <c r="B53" s="49"/>
+      <c r="C53" s="50"/>
     </row>
     <row r="54" spans="1:3" ht="22" customHeight="1">
-      <c r="A54" s="32" t="s">
+      <c r="A54" s="48" t="s">
         <v>223</v>
       </c>
-      <c r="B54" s="33"/>
-      <c r="C54" s="34"/>
+      <c r="B54" s="49"/>
+      <c r="C54" s="50"/>
     </row>
     <row r="55" spans="1:3" ht="22" customHeight="1">
-      <c r="A55" s="32" t="s">
+      <c r="A55" s="48" t="s">
         <v>223</v>
       </c>
-      <c r="B55" s="33"/>
-      <c r="C55" s="34"/>
+      <c r="B55" s="49"/>
+      <c r="C55" s="50"/>
     </row>
     <row r="56" spans="1:3" ht="22" customHeight="1">
-      <c r="A56" s="32" t="s">
+      <c r="A56" s="48" t="s">
         <v>223</v>
       </c>
-      <c r="B56" s="33"/>
-      <c r="C56" s="34"/>
+      <c r="B56" s="49"/>
+      <c r="C56" s="50"/>
     </row>
     <row r="57" spans="1:3" ht="22" customHeight="1">
-      <c r="A57" s="32" t="s">
+      <c r="A57" s="48" t="s">
         <v>223</v>
       </c>
-      <c r="B57" s="33"/>
-      <c r="C57" s="34"/>
+      <c r="B57" s="49"/>
+      <c r="C57" s="50"/>
     </row>
     <row r="58" spans="1:3" ht="22" customHeight="1">
-      <c r="A58" s="32" t="s">
+      <c r="A58" s="48" t="s">
         <v>223</v>
       </c>
-      <c r="B58" s="33"/>
-      <c r="C58" s="34"/>
+      <c r="B58" s="49"/>
+      <c r="C58" s="50"/>
     </row>
     <row r="59" spans="1:3" ht="22" customHeight="1">
-      <c r="A59" s="32" t="s">
+      <c r="A59" s="48" t="s">
         <v>223</v>
       </c>
-      <c r="B59" s="33"/>
-      <c r="C59" s="34"/>
+      <c r="B59" s="49"/>
+      <c r="C59" s="50"/>
     </row>
     <row r="60" spans="1:3" ht="22" customHeight="1">
-      <c r="A60" s="32" t="s">
+      <c r="A60" s="48" t="s">
         <v>223</v>
       </c>
-      <c r="B60" s="33"/>
-      <c r="C60" s="34"/>
+      <c r="B60" s="49"/>
+      <c r="C60" s="50"/>
     </row>
     <row r="61" spans="1:3" ht="22" customHeight="1">
-      <c r="A61" s="32" t="s">
+      <c r="A61" s="48" t="s">
         <v>223</v>
       </c>
-      <c r="B61" s="33"/>
-      <c r="C61" s="34"/>
+      <c r="B61" s="49"/>
+      <c r="C61" s="50"/>
     </row>
     <row r="62" spans="1:3" ht="22" customHeight="1">
-      <c r="A62" s="32" t="s">
+      <c r="A62" s="48" t="s">
         <v>223</v>
       </c>
-      <c r="B62" s="33"/>
-      <c r="C62" s="34"/>
+      <c r="B62" s="49"/>
+      <c r="C62" s="50"/>
     </row>
     <row r="63" spans="1:3" ht="22" customHeight="1">
-      <c r="A63" s="32" t="s">
+      <c r="A63" s="48" t="s">
         <v>223</v>
       </c>
-      <c r="B63" s="33"/>
-      <c r="C63" s="34"/>
+      <c r="B63" s="49"/>
+      <c r="C63" s="50"/>
     </row>
     <row r="64" spans="1:3" ht="22" customHeight="1">
-      <c r="A64" s="32" t="s">
+      <c r="A64" s="48" t="s">
         <v>223</v>
       </c>
-      <c r="B64" s="33"/>
-      <c r="C64" s="34"/>
+      <c r="B64" s="49"/>
+      <c r="C64" s="50"/>
     </row>
     <row r="65" spans="1:3" ht="22" customHeight="1">
-      <c r="A65" s="32" t="s">
+      <c r="A65" s="48" t="s">
         <v>223</v>
       </c>
-      <c r="B65" s="33"/>
-      <c r="C65" s="34"/>
+      <c r="B65" s="49"/>
+      <c r="C65" s="50"/>
     </row>
     <row r="66" spans="1:3" ht="22" customHeight="1">
-      <c r="A66" s="32" t="s">
+      <c r="A66" s="48" t="s">
         <v>223</v>
       </c>
-      <c r="B66" s="33"/>
-      <c r="C66" s="34"/>
+      <c r="B66" s="49"/>
+      <c r="C66" s="50"/>
     </row>
     <row r="67" spans="1:3" ht="22" customHeight="1">
-      <c r="A67" s="32" t="s">
+      <c r="A67" s="48" t="s">
         <v>223</v>
       </c>
-      <c r="B67" s="33"/>
-      <c r="C67" s="34"/>
+      <c r="B67" s="49"/>
+      <c r="C67" s="50"/>
     </row>
     <row r="68" spans="1:3" ht="22" customHeight="1">
-      <c r="A68" s="32" t="s">
+      <c r="A68" s="48" t="s">
         <v>223</v>
       </c>
-      <c r="B68" s="33"/>
-      <c r="C68" s="34"/>
+      <c r="B68" s="49"/>
+      <c r="C68" s="50"/>
     </row>
     <row r="69" spans="1:3" ht="22" customHeight="1">
-      <c r="A69" s="32" t="s">
+      <c r="A69" s="48" t="s">
         <v>223</v>
       </c>
-      <c r="B69" s="33"/>
-      <c r="C69" s="34"/>
+      <c r="B69" s="49"/>
+      <c r="C69" s="50"/>
     </row>
     <row r="70" spans="1:3" ht="22" customHeight="1">
-      <c r="A70" s="32" t="s">
+      <c r="A70" s="48" t="s">
         <v>223</v>
       </c>
-      <c r="B70" s="33"/>
-      <c r="C70" s="34"/>
+      <c r="B70" s="49"/>
+      <c r="C70" s="50"/>
     </row>
     <row r="71" spans="1:3" ht="22" customHeight="1">
-      <c r="A71" s="32" t="s">
+      <c r="A71" s="48" t="s">
         <v>223</v>
       </c>
-      <c r="B71" s="33"/>
-      <c r="C71" s="34"/>
+      <c r="B71" s="49"/>
+      <c r="C71" s="50"/>
     </row>
     <row r="72" spans="1:3" ht="22" customHeight="1">
-      <c r="A72" s="32" t="s">
+      <c r="A72" s="48" t="s">
         <v>223</v>
       </c>
-      <c r="B72" s="33"/>
-      <c r="C72" s="34"/>
+      <c r="B72" s="49"/>
+      <c r="C72" s="50"/>
     </row>
     <row r="73" spans="1:3" ht="22" customHeight="1">
-      <c r="A73" s="32" t="s">
+      <c r="A73" s="48" t="s">
         <v>223</v>
       </c>
-      <c r="B73" s="33"/>
-      <c r="C73" s="34"/>
+      <c r="B73" s="49"/>
+      <c r="C73" s="50"/>
     </row>
     <row r="74" spans="1:3" ht="22" customHeight="1">
-      <c r="A74" s="32" t="s">
+      <c r="A74" s="48" t="s">
         <v>223</v>
       </c>
-      <c r="B74" s="33"/>
-      <c r="C74" s="34"/>
+      <c r="B74" s="49"/>
+      <c r="C74" s="50"/>
     </row>
     <row r="75" spans="1:3" ht="22" customHeight="1">
-      <c r="A75" s="32" t="s">
+      <c r="A75" s="48" t="s">
         <v>223</v>
       </c>
-      <c r="B75" s="33"/>
-      <c r="C75" s="34"/>
+      <c r="B75" s="49"/>
+      <c r="C75" s="50"/>
     </row>
     <row r="76" spans="1:3" ht="22" customHeight="1">
-      <c r="A76" s="32" t="s">
+      <c r="A76" s="48" t="s">
         <v>223</v>
       </c>
-      <c r="B76" s="33"/>
-      <c r="C76" s="34"/>
+      <c r="B76" s="49"/>
+      <c r="C76" s="50"/>
     </row>
     <row r="77" spans="1:3" ht="22" customHeight="1">
-      <c r="A77" s="32" t="s">
+      <c r="A77" s="48" t="s">
         <v>223</v>
       </c>
-      <c r="B77" s="33"/>
-      <c r="C77" s="34"/>
+      <c r="B77" s="49"/>
+      <c r="C77" s="50"/>
     </row>
     <row r="78" spans="1:3" ht="22" customHeight="1">
-      <c r="A78" s="32" t="s">
+      <c r="A78" s="48" t="s">
         <v>223</v>
       </c>
-      <c r="B78" s="33"/>
-      <c r="C78" s="34"/>
+      <c r="B78" s="49"/>
+      <c r="C78" s="50"/>
     </row>
     <row r="79" spans="1:3" ht="22" customHeight="1">
-      <c r="A79" s="32" t="s">
+      <c r="A79" s="48" t="s">
         <v>223</v>
       </c>
-      <c r="B79" s="33"/>
-      <c r="C79" s="34"/>
+      <c r="B79" s="49"/>
+      <c r="C79" s="50"/>
     </row>
     <row r="80" spans="1:3" ht="22" customHeight="1">
-      <c r="A80" s="32" t="s">
+      <c r="A80" s="48" t="s">
         <v>223</v>
       </c>
-      <c r="B80" s="33"/>
-      <c r="C80" s="34"/>
+      <c r="B80" s="49"/>
+      <c r="C80" s="50"/>
     </row>
     <row r="81" spans="1:3" ht="22" customHeight="1">
-      <c r="A81" s="32" t="s">
+      <c r="A81" s="48" t="s">
         <v>223</v>
       </c>
-      <c r="B81" s="33"/>
-      <c r="C81" s="34"/>
+      <c r="B81" s="49"/>
+      <c r="C81" s="50"/>
     </row>
     <row r="82" spans="1:3" ht="22" customHeight="1">
-      <c r="A82" s="32" t="s">
+      <c r="A82" s="48" t="s">
         <v>223</v>
       </c>
-      <c r="B82" s="33"/>
-      <c r="C82" s="34"/>
+      <c r="B82" s="49"/>
+      <c r="C82" s="50"/>
     </row>
     <row r="83" spans="1:3" ht="22" customHeight="1">
-      <c r="A83" s="32" t="s">
+      <c r="A83" s="48" t="s">
         <v>223</v>
       </c>
-      <c r="B83" s="33"/>
-      <c r="C83" s="34"/>
+      <c r="B83" s="49"/>
+      <c r="C83" s="50"/>
     </row>
     <row r="84" spans="1:3" ht="22" customHeight="1">
-      <c r="A84" s="32" t="s">
+      <c r="A84" s="48" t="s">
         <v>223</v>
       </c>
-      <c r="B84" s="33"/>
-      <c r="C84" s="34"/>
+      <c r="B84" s="49"/>
+      <c r="C84" s="50"/>
     </row>
     <row r="85" spans="1:3" ht="22" customHeight="1">
-      <c r="A85" s="32" t="s">
+      <c r="A85" s="48" t="s">
         <v>223</v>
       </c>
-      <c r="B85" s="33"/>
-      <c r="C85" s="34"/>
+      <c r="B85" s="49"/>
+      <c r="C85" s="50"/>
     </row>
     <row r="86" spans="1:3" ht="22" customHeight="1">
-      <c r="A86" s="32" t="s">
+      <c r="A86" s="48" t="s">
         <v>223</v>
       </c>
-      <c r="B86" s="33"/>
-      <c r="C86" s="34"/>
+      <c r="B86" s="49"/>
+      <c r="C86" s="50"/>
     </row>
     <row r="87" spans="1:3" ht="22" customHeight="1">
-      <c r="A87" s="32" t="s">
+      <c r="A87" s="48" t="s">
         <v>223</v>
       </c>
-      <c r="B87" s="33"/>
-      <c r="C87" s="34"/>
+      <c r="B87" s="49"/>
+      <c r="C87" s="50"/>
     </row>
     <row r="88" spans="1:3" ht="22" customHeight="1">
-      <c r="A88" s="32" t="s">
+      <c r="A88" s="48" t="s">
         <v>223</v>
       </c>
-      <c r="B88" s="33"/>
-      <c r="C88" s="34"/>
+      <c r="B88" s="49"/>
+      <c r="C88" s="50"/>
     </row>
     <row r="89" spans="1:3" ht="22" customHeight="1">
-      <c r="A89" s="32" t="s">
+      <c r="A89" s="48" t="s">
         <v>223</v>
       </c>
-      <c r="B89" s="33"/>
-      <c r="C89" s="34"/>
+      <c r="B89" s="49"/>
+      <c r="C89" s="50"/>
     </row>
     <row r="90" spans="1:3" ht="22" customHeight="1">
-      <c r="A90" s="32" t="s">
+      <c r="A90" s="48" t="s">
         <v>223</v>
       </c>
-      <c r="B90" s="33"/>
-      <c r="C90" s="34"/>
+      <c r="B90" s="49"/>
+      <c r="C90" s="50"/>
     </row>
     <row r="91" spans="1:3" ht="22" customHeight="1">
-      <c r="A91" s="32" t="s">
+      <c r="A91" s="48" t="s">
         <v>223</v>
       </c>
-      <c r="B91" s="33"/>
-      <c r="C91" s="34"/>
+      <c r="B91" s="49"/>
+      <c r="C91" s="50"/>
     </row>
     <row r="92" spans="1:3" ht="22" customHeight="1">
-      <c r="A92" s="32" t="s">
+      <c r="A92" s="48" t="s">
         <v>223</v>
       </c>
-      <c r="B92" s="33"/>
-      <c r="C92" s="34"/>
+      <c r="B92" s="49"/>
+      <c r="C92" s="50"/>
     </row>
     <row r="93" spans="1:3" ht="22" customHeight="1">
-      <c r="A93" s="32" t="s">
+      <c r="A93" s="48" t="s">
         <v>223</v>
       </c>
-      <c r="B93" s="33"/>
-      <c r="C93" s="34"/>
+      <c r="B93" s="49"/>
+      <c r="C93" s="50"/>
     </row>
     <row r="94" spans="1:3" ht="22" customHeight="1">
-      <c r="A94" s="32" t="s">
+      <c r="A94" s="48" t="s">
         <v>223</v>
       </c>
-      <c r="B94" s="33"/>
-      <c r="C94" s="34"/>
+      <c r="B94" s="49"/>
+      <c r="C94" s="50"/>
     </row>
     <row r="95" spans="1:3" ht="22" customHeight="1">
-      <c r="A95" s="32" t="s">
+      <c r="A95" s="48" t="s">
         <v>223</v>
       </c>
-      <c r="B95" s="33"/>
-      <c r="C95" s="34"/>
+      <c r="B95" s="49"/>
+      <c r="C95" s="50"/>
     </row>
     <row r="96" spans="1:3" ht="22" customHeight="1">
-      <c r="A96" s="32" t="s">
+      <c r="A96" s="48" t="s">
         <v>223</v>
       </c>
-      <c r="B96" s="33"/>
-      <c r="C96" s="34"/>
+      <c r="B96" s="49"/>
+      <c r="C96" s="50"/>
     </row>
     <row r="97" spans="1:3" ht="22" customHeight="1">
-      <c r="A97" s="32" t="s">
+      <c r="A97" s="48" t="s">
         <v>223</v>
       </c>
-      <c r="B97" s="33"/>
-      <c r="C97" s="34"/>
+      <c r="B97" s="49"/>
+      <c r="C97" s="50"/>
     </row>
     <row r="98" spans="1:3" ht="22" customHeight="1">
-      <c r="A98" s="32" t="s">
+      <c r="A98" s="48" t="s">
         <v>223</v>
       </c>
-      <c r="B98" s="33"/>
-      <c r="C98" s="34"/>
+      <c r="B98" s="49"/>
+      <c r="C98" s="50"/>
     </row>
     <row r="99" spans="1:3" ht="22" customHeight="1">
-      <c r="A99" s="32" t="s">
+      <c r="A99" s="48" t="s">
         <v>223</v>
       </c>
-      <c r="B99" s="33"/>
-      <c r="C99" s="34"/>
+      <c r="B99" s="49"/>
+      <c r="C99" s="50"/>
     </row>
     <row r="100" spans="1:3" ht="22" customHeight="1">
-      <c r="A100" s="32" t="s">
+      <c r="A100" s="48" t="s">
         <v>223</v>
       </c>
-      <c r="B100" s="33"/>
-      <c r="C100" s="34"/>
+      <c r="B100" s="49"/>
+      <c r="C100" s="50"/>
     </row>
     <row r="101" spans="1:3" ht="22" customHeight="1">
-      <c r="A101" s="32" t="s">
+      <c r="A101" s="48" t="s">
         <v>223</v>
       </c>
-      <c r="B101" s="33"/>
-      <c r="C101" s="34"/>
+      <c r="B101" s="49"/>
+      <c r="C101" s="50"/>
     </row>
     <row r="102" spans="1:3" ht="22" customHeight="1">
-      <c r="A102" s="32" t="s">
+      <c r="A102" s="48" t="s">
         <v>223</v>
       </c>
-      <c r="B102" s="33"/>
-      <c r="C102" s="34"/>
+      <c r="B102" s="49"/>
+      <c r="C102" s="50"/>
     </row>
     <row r="103" spans="1:3" ht="22" customHeight="1">
-      <c r="A103" s="35" t="s">
+      <c r="A103" s="51" t="s">
         <v>223</v>
       </c>
-      <c r="B103" s="36"/>
-      <c r="C103" s="37"/>
+      <c r="B103" s="52"/>
+      <c r="C103" s="53"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -8594,14 +8756,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="49.75" customHeight="1">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
     </row>
     <row r="3" spans="1:6" ht="42.75" customHeight="1">
       <c r="A3" s="2" t="s">
@@ -8692,13 +8854,13 @@
       </c>
     </row>
     <row r="11" spans="1:6" ht="16">
-      <c r="A11" s="30" t="s">
+      <c r="A11" s="28" t="s">
         <v>204</v>
       </c>
-      <c r="B11" s="30" t="s">
+      <c r="B11" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="C11" s="30" t="s">
+      <c r="C11" s="28" t="s">
         <v>70</v>
       </c>
     </row>
@@ -8723,12 +8885,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="49.75" customHeight="1">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="30" t="s">
         <v>71</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
     </row>
     <row r="3" spans="1:4" ht="42.75" customHeight="1">
       <c r="A3" s="2" t="s">
@@ -8896,17 +9058,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="49.75" customHeight="1">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="30" t="s">
         <v>91</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
     </row>
     <row r="3" spans="1:10" ht="42.75" customHeight="1">
       <c r="A3" s="2" t="s">
@@ -9400,13 +9562,13 @@
     <mergeCell ref="A1:I1"/>
   </mergeCells>
   <conditionalFormatting sqref="F4:F18">
-    <cfRule type="expression" dxfId="16" priority="1">
+    <cfRule type="expression" dxfId="20" priority="1">
       <formula>F4="Pagata"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="15" priority="2">
+    <cfRule type="expression" dxfId="19" priority="2">
       <formula>F4="Da pagare"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="14" priority="3">
+    <cfRule type="expression" dxfId="18" priority="3">
       <formula>F4="Parziale"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9433,17 +9595,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="49.75" customHeight="1">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="30" t="s">
         <v>124</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
     </row>
     <row r="3" spans="1:9" ht="42.75" customHeight="1">
       <c r="A3" s="2" t="s">
@@ -13291,13 +13453,13 @@
     <mergeCell ref="A1:I1"/>
   </mergeCells>
   <conditionalFormatting sqref="H4:H203">
-    <cfRule type="expression" dxfId="13" priority="1">
+    <cfRule type="expression" dxfId="17" priority="1">
       <formula>H4="Pagato"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="2">
+    <cfRule type="expression" dxfId="16" priority="2">
       <formula>H4="Da pagare"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="11" priority="3">
+    <cfRule type="expression" dxfId="15" priority="3">
       <formula>H4="Parziale"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13329,19 +13491,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="49.75" customHeight="1">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="30" t="s">
         <v>138</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
-      <c r="J1" s="39"/>
-      <c r="K1" s="39"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+      <c r="K1" s="31"/>
       <c r="L1" t="s">
         <v>205</v>
       </c>
@@ -14448,7 +14610,7 @@
         <v>147</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>234</v>
+        <v>105</v>
       </c>
       <c r="K34" s="3"/>
       <c r="L34" t="s">
@@ -14456,55 +14618,75 @@
       </c>
     </row>
     <row r="35" spans="1:12">
-      <c r="A35" s="14"/>
-      <c r="B35" s="3"/>
+      <c r="A35" s="14" t="s">
+        <v>234</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>156</v>
+      </c>
       <c r="C35" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="D35" s="5"/>
-      <c r="E35" s="13"/>
-      <c r="F35" s="4" t="str">
+      <c r="D35" s="5">
+        <v>10</v>
+      </c>
+      <c r="E35" s="13">
+        <v>10</v>
+      </c>
+      <c r="F35" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="G35" s="4" t="str">
+        <v>100</v>
+      </c>
+      <c r="G35" s="4">
         <f>IF(D35="","",D35*Parametri!$B$6)</f>
-        <v/>
-      </c>
-      <c r="H35" s="4" t="str">
+        <v>27</v>
+      </c>
+      <c r="H35" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>73</v>
       </c>
       <c r="I35" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="J35" s="3"/>
+      <c r="J35" s="3" t="s">
+        <v>105</v>
+      </c>
       <c r="K35" s="3"/>
     </row>
     <row r="36" spans="1:12">
-      <c r="A36" s="14"/>
-      <c r="B36" s="3"/>
+      <c r="A36" s="14" t="s">
+        <v>235</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>123</v>
+      </c>
       <c r="C36" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="D36" s="5"/>
-      <c r="E36" s="13"/>
-      <c r="F36" s="4" t="str">
+      <c r="D36" s="5">
+        <v>1</v>
+      </c>
+      <c r="E36" s="13">
+        <v>12</v>
+      </c>
+      <c r="F36" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="G36" s="4" t="str">
+        <v>12</v>
+      </c>
+      <c r="G36" s="4">
         <f>IF(D36="","",D36*Parametri!$B$6)</f>
-        <v/>
-      </c>
-      <c r="H36" s="4" t="str">
+        <v>2.7</v>
+      </c>
+      <c r="H36" s="4">
         <f t="shared" si="0"/>
-        <v/>
+        <v>9.3000000000000007</v>
       </c>
       <c r="I36" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="J36" s="3"/>
+      <c r="J36" s="3" t="s">
+        <v>105</v>
+      </c>
       <c r="K36" s="3"/>
     </row>
     <row r="37" spans="1:12">
@@ -21454,10 +21636,10 @@
     <mergeCell ref="A1:K1"/>
   </mergeCells>
   <conditionalFormatting sqref="I4:I303">
-    <cfRule type="expression" dxfId="10" priority="1">
+    <cfRule type="expression" dxfId="14" priority="1">
       <formula>I4="Sì"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="2">
+    <cfRule type="expression" dxfId="13" priority="2">
       <formula>I4="No"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -21498,16 +21680,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="49.75" customHeight="1">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="30" t="s">
         <v>164</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1">
       <c r="A3" s="2" t="s">
@@ -23952,10 +24134,10 @@
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <conditionalFormatting sqref="G4:G203">
-    <cfRule type="expression" dxfId="8" priority="1">
+    <cfRule type="expression" dxfId="12" priority="1">
       <formula>G4="Sì"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="7" priority="2">
+    <cfRule type="expression" dxfId="11" priority="2">
       <formula>G4="No"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -23983,30 +24165,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="49.75" customHeight="1">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="30" t="s">
         <v>170</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
     </row>
     <row r="3" spans="1:11" ht="42.75" customHeight="1">
-      <c r="A3" s="40" t="s">
+      <c r="A3" s="36" t="s">
         <v>171</v>
       </c>
-      <c r="B3" s="39"/>
-      <c r="C3" s="39"/>
-      <c r="D3" s="39"/>
-      <c r="E3" s="39"/>
-      <c r="F3" s="39"/>
-      <c r="H3" s="40" t="s">
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="31"/>
+      <c r="H3" s="36" t="s">
         <v>172</v>
       </c>
-      <c r="I3" s="39"/>
-      <c r="J3" s="39"/>
-      <c r="K3" s="39"/>
+      <c r="I3" s="31"/>
+      <c r="J3" s="31"/>
+      <c r="K3" s="31"/>
     </row>
     <row r="4" spans="1:11" ht="16">
       <c r="A4" s="6" t="s">
@@ -24203,7 +24385,7 @@
       </c>
       <c r="B11" s="5">
         <f>SUM(Vendite_Patch!D4:D303)</f>
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>21</v>
@@ -24227,7 +24409,7 @@
       </c>
       <c r="B12" s="4">
         <f>SUMIFS(Vendite_Patch!F4:F303,Vendite_Patch!I4:I303,"Sì")</f>
-        <v>551</v>
+        <v>663</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>36</v>
@@ -24242,7 +24424,7 @@
       </c>
       <c r="B13" s="4">
         <f>SUMIFS(Vendite_Patch!H4:H303,Vendite_Patch!I4:I303,"Sì")</f>
-        <v>440.30000000000013</v>
+        <v>522.60000000000014</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>36</v>
@@ -24257,7 +24439,7 @@
       </c>
       <c r="B14" s="3">
         <f>B9-B11</f>
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>21</v>
@@ -24287,7 +24469,7 @@
       </c>
       <c r="B16" s="4">
         <f>B6+B12+SUM(Persone_Quote!J4:J18)-B10-B15</f>
-        <v>306</v>
+        <v>418</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>36</v>
@@ -24314,21 +24496,21 @@
       </c>
       <c r="B18" s="4">
         <f>SUMIFS(Vendite_Patch!$F$4:$F$303,Vendite_Patch!$I$4:$I$303,"Sì",Vendite_Patch!$E$4:$E$303,Parametri!$B$8)</f>
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="39" customHeight="1">
-      <c r="A19" s="40" t="s">
+      <c r="A19" s="36" t="s">
         <v>186</v>
       </c>
-      <c r="B19" s="39"/>
-      <c r="C19" s="39"/>
-      <c r="D19" s="39"/>
-      <c r="E19" s="39"/>
-      <c r="F19" s="39"/>
+      <c r="B19" s="31"/>
+      <c r="C19" s="31"/>
+      <c r="D19" s="31"/>
+      <c r="E19" s="31"/>
+      <c r="F19" s="31"/>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="3" t="s">
@@ -24418,31 +24600,31 @@
     <mergeCell ref="H3:K3"/>
   </mergeCells>
   <conditionalFormatting sqref="B14">
-    <cfRule type="expression" dxfId="6" priority="5">
+    <cfRule type="expression" dxfId="10" priority="5">
       <formula>B14&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B16">
-    <cfRule type="expression" dxfId="5" priority="6">
+    <cfRule type="expression" dxfId="9" priority="6">
       <formula>B16&lt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="7">
+    <cfRule type="expression" dxfId="8" priority="7">
       <formula>B16&gt;=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B18">
-    <cfRule type="expression" dxfId="3" priority="1">
+    <cfRule type="expression" dxfId="7" priority="1">
       <formula>B18&lt;0</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="2">
+    <cfRule type="expression" dxfId="6" priority="2">
       <formula>B18&gt;=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B20">
-    <cfRule type="expression" dxfId="1" priority="3">
+    <cfRule type="expression" dxfId="5" priority="3">
       <formula>LEFT(B20,2)="Sì"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="4">
+    <cfRule type="expression" dxfId="4" priority="4">
       <formula>B20="No"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -24465,12 +24647,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="49.75" customHeight="1">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="30" t="s">
         <v>193</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
     </row>
     <row r="3" spans="1:5" ht="42.75" customHeight="1">
       <c r="A3" s="2" t="s">
